--- a/output/resultado_resumen_final.xlsx
+++ b/output/resultado_resumen_final.xlsx
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -436,16 +436,16 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H2">
-        <v>1.073</v>
+        <v>1.08</v>
       </c>
       <c r="I2">
-        <v>4.528</v>
+        <v>3.892</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -462,16 +462,16 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <v>0.004</v>
       </c>
       <c r="H3">
-        <v>1.084</v>
+        <v>1.087</v>
       </c>
       <c r="I3">
-        <v>4.05</v>
+        <v>3.782</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -479,7 +479,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -488,19 +488,19 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>6.991233280203802</v>
+        <v>7.24705987828718</v>
       </c>
       <c r="G4">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H4">
-        <v>1.039</v>
+        <v>1.05</v>
       </c>
       <c r="I4">
-        <v>2.596</v>
+        <v>2.239</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -508,7 +508,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -517,16 +517,16 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H5">
-        <v>1.073</v>
+        <v>1.08</v>
       </c>
       <c r="I5">
-        <v>4.528</v>
+        <v>3.892</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -534,7 +534,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -543,16 +543,16 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>0.004</v>
       </c>
       <c r="H6">
-        <v>1.084</v>
+        <v>1.087</v>
       </c>
       <c r="I6">
-        <v>4.05</v>
+        <v>3.782</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -569,19 +569,19 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7">
-        <v>6.991233280203802</v>
+        <v>7.24705987828718</v>
       </c>
       <c r="G7">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H7">
-        <v>1.039</v>
+        <v>1.05</v>
       </c>
       <c r="I7">
-        <v>2.596</v>
+        <v>2.239</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -598,16 +598,16 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H8">
-        <v>1.073</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
-        <v>4.528</v>
+        <v>3.892</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -624,16 +624,16 @@
         <v>13</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9">
         <v>0.004</v>
       </c>
       <c r="H9">
-        <v>1.084</v>
+        <v>1.087</v>
       </c>
       <c r="I9">
-        <v>4.05</v>
+        <v>3.782</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -650,19 +650,19 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>6.991233280203802</v>
+        <v>7.24705987828718</v>
       </c>
       <c r="G10">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H10">
-        <v>1.039</v>
+        <v>1.05</v>
       </c>
       <c r="I10">
-        <v>2.596</v>
+        <v>2.239</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -670,7 +670,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -679,16 +679,16 @@
         <v>12</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G11">
         <v>0.002</v>
       </c>
       <c r="H11">
-        <v>1.057</v>
+        <v>1.075</v>
       </c>
       <c r="I11">
-        <v>4.563</v>
+        <v>4.279</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -705,16 +705,16 @@
         <v>13</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H12">
-        <v>1.059</v>
+        <v>1.124</v>
       </c>
       <c r="I12">
-        <v>3.734</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
       <c r="B13">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -731,19 +731,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F13">
-        <v>7.004033666926235</v>
+        <v>9.851477532794901</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="H13">
-        <v>1.025</v>
+        <v>1.045</v>
       </c>
       <c r="I13">
-        <v>2.773</v>
+        <v>3.229</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B14">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -760,16 +760,16 @@
         <v>12</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14">
         <v>0.002</v>
       </c>
       <c r="H14">
-        <v>1.057</v>
+        <v>1.075</v>
       </c>
       <c r="I14">
-        <v>4.563</v>
+        <v>4.279</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -777,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="B15">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -786,16 +786,16 @@
         <v>13</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H15">
-        <v>1.059</v>
+        <v>1.124</v>
       </c>
       <c r="I15">
-        <v>3.734</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -803,7 +803,7 @@
         <v>2</v>
       </c>
       <c r="B16">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -812,19 +812,19 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16">
-        <v>7.004033666926235</v>
+        <v>9.851477532794901</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="H16">
-        <v>1.025</v>
+        <v>1.045</v>
       </c>
       <c r="I16">
-        <v>2.773</v>
+        <v>3.229</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="B17">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -841,16 +841,16 @@
         <v>12</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>0.002</v>
       </c>
       <c r="H17">
-        <v>1.057</v>
+        <v>1.075</v>
       </c>
       <c r="I17">
-        <v>4.563</v>
+        <v>4.279</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -858,7 +858,7 @@
         <v>2</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -867,16 +867,16 @@
         <v>13</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H18">
-        <v>1.059</v>
+        <v>1.124</v>
       </c>
       <c r="I18">
-        <v>3.734</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -884,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="B19">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -893,19 +893,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>7.004033666926235</v>
+        <v>9.851477532794901</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="H19">
-        <v>1.025</v>
+        <v>1.045</v>
       </c>
       <c r="I19">
-        <v>2.773</v>
+        <v>3.229</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
@@ -925,13 +925,13 @@
         <v>2</v>
       </c>
       <c r="G20">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H20">
-        <v>1.053</v>
+        <v>1.115</v>
       </c>
       <c r="I20">
-        <v>4.57</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -939,7 +939,7 @@
         <v>3</v>
       </c>
       <c r="B21">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
@@ -951,13 +951,13 @@
         <v>2</v>
       </c>
       <c r="G21">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H21">
-        <v>1.089</v>
+        <v>1.165</v>
       </c>
       <c r="I21">
-        <v>4.478</v>
+        <v>8.244</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -965,7 +965,7 @@
         <v>3</v>
       </c>
       <c r="B22">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -974,19 +974,19 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F22">
-        <v>7.002622792504699</v>
+        <v>14.57762604402895</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="H22">
-        <v>0.998</v>
+        <v>1.057</v>
       </c>
       <c r="I22">
-        <v>4.003</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -994,7 +994,7 @@
         <v>3</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -1006,13 +1006,13 @@
         <v>2</v>
       </c>
       <c r="G23">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H23">
-        <v>1.053</v>
+        <v>1.115</v>
       </c>
       <c r="I23">
-        <v>4.57</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1020,7 +1020,7 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -1032,13 +1032,13 @@
         <v>2</v>
       </c>
       <c r="G24">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H24">
-        <v>1.089</v>
+        <v>1.165</v>
       </c>
       <c r="I24">
-        <v>4.478</v>
+        <v>8.244</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1046,7 +1046,7 @@
         <v>3</v>
       </c>
       <c r="B25">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -1055,19 +1055,19 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>7.002622792504699</v>
+        <v>14.57762604402895</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="H25">
-        <v>0.998</v>
+        <v>1.057</v>
       </c>
       <c r="I25">
-        <v>4.003</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1075,7 +1075,7 @@
         <v>3</v>
       </c>
       <c r="B26">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1087,13 +1087,13 @@
         <v>2</v>
       </c>
       <c r="G26">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H26">
-        <v>1.053</v>
+        <v>1.115</v>
       </c>
       <c r="I26">
-        <v>4.57</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1101,7 +1101,7 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1113,13 +1113,13 @@
         <v>2</v>
       </c>
       <c r="G27">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H27">
-        <v>1.089</v>
+        <v>1.165</v>
       </c>
       <c r="I27">
-        <v>4.478</v>
+        <v>8.244</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1127,7 +1127,7 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1136,19 +1136,19 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F28">
-        <v>7.002622792504699</v>
+        <v>14.57762604402895</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="H28">
-        <v>0.998</v>
+        <v>1.057</v>
       </c>
       <c r="I28">
-        <v>4.003</v>
+        <v>3.758</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1156,7 +1156,7 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1165,16 +1165,16 @@
         <v>12</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H29">
-        <v>1.069</v>
+        <v>1.082</v>
       </c>
       <c r="I29">
-        <v>4.379</v>
+        <v>7.886</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1182,7 +1182,7 @@
         <v>4</v>
       </c>
       <c r="B30">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1194,13 +1194,13 @@
         <v>2</v>
       </c>
       <c r="G30">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H30">
-        <v>1.086</v>
+        <v>1.154</v>
       </c>
       <c r="I30">
-        <v>4.217</v>
+        <v>9.166</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="B31">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1217,19 +1217,19 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>6.98302594845595</v>
+        <v>13.97165487492945</v>
       </c>
       <c r="G31">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="H31">
-        <v>1.051</v>
+        <v>1.045</v>
       </c>
       <c r="I31">
-        <v>2.812</v>
+        <v>3.735</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1237,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
@@ -1246,16 +1246,16 @@
         <v>12</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H32">
-        <v>1.069</v>
+        <v>1.082</v>
       </c>
       <c r="I32">
-        <v>4.379</v>
+        <v>7.886</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1263,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="B33">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
@@ -1275,13 +1275,13 @@
         <v>2</v>
       </c>
       <c r="G33">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H33">
-        <v>1.086</v>
+        <v>1.154</v>
       </c>
       <c r="I33">
-        <v>4.217</v>
+        <v>9.166</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1289,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="B34">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -1298,19 +1298,19 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>6.98302594845595</v>
+        <v>13.97165487492945</v>
       </c>
       <c r="G34">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="H34">
-        <v>1.051</v>
+        <v>1.045</v>
       </c>
       <c r="I34">
-        <v>2.812</v>
+        <v>3.735</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1318,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="B35">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -1327,16 +1327,16 @@
         <v>12</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H35">
-        <v>1.069</v>
+        <v>1.082</v>
       </c>
       <c r="I35">
-        <v>4.379</v>
+        <v>7.886</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1344,7 +1344,7 @@
         <v>4</v>
       </c>
       <c r="B36">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
@@ -1356,13 +1356,13 @@
         <v>2</v>
       </c>
       <c r="G36">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H36">
-        <v>1.086</v>
+        <v>1.154</v>
       </c>
       <c r="I36">
-        <v>4.217</v>
+        <v>9.166</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1370,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -1379,19 +1379,19 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>6.98302594845595</v>
+        <v>13.97165487492945</v>
       </c>
       <c r="G37">
-        <v>0.002</v>
+        <v>-0.003</v>
       </c>
       <c r="H37">
-        <v>1.051</v>
+        <v>1.045</v>
       </c>
       <c r="I37">
-        <v>2.812</v>
+        <v>3.735</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1399,7 +1399,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1408,16 +1408,16 @@
         <v>12</v>
       </c>
       <c r="E38">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G38">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H38">
-        <v>1.064</v>
+        <v>1.081</v>
       </c>
       <c r="I38">
-        <v>2.805</v>
+        <v>5.524</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="B39">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1437,13 +1437,13 @@
         <v>2</v>
       </c>
       <c r="G39">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H39">
         <v>1.085</v>
       </c>
       <c r="I39">
-        <v>3.834</v>
+        <v>5.316</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1451,7 +1451,7 @@
         <v>5</v>
       </c>
       <c r="B40">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
@@ -1460,19 +1460,19 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>6.989012772364849</v>
+        <v>8.380744769816141</v>
       </c>
       <c r="G40">
-        <v>0.004</v>
+        <v>-0</v>
       </c>
       <c r="H40">
-        <v>1.054</v>
+        <v>1.037</v>
       </c>
       <c r="I40">
-        <v>2.59</v>
+        <v>3.861</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1480,7 +1480,7 @@
         <v>5</v>
       </c>
       <c r="B41">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
@@ -1489,16 +1489,16 @@
         <v>12</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G41">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H41">
-        <v>1.064</v>
+        <v>1.081</v>
       </c>
       <c r="I41">
-        <v>2.805</v>
+        <v>5.524</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1506,7 +1506,7 @@
         <v>5</v>
       </c>
       <c r="B42">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
@@ -1518,13 +1518,13 @@
         <v>2</v>
       </c>
       <c r="G42">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H42">
         <v>1.085</v>
       </c>
       <c r="I42">
-        <v>3.834</v>
+        <v>5.316</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1532,7 +1532,7 @@
         <v>5</v>
       </c>
       <c r="B43">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
@@ -1541,19 +1541,19 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43">
-        <v>6.989012772364849</v>
+        <v>8.380744769816141</v>
       </c>
       <c r="G43">
-        <v>0.004</v>
+        <v>-0</v>
       </c>
       <c r="H43">
-        <v>1.054</v>
+        <v>1.037</v>
       </c>
       <c r="I43">
-        <v>2.59</v>
+        <v>3.861</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="B44">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
@@ -1570,16 +1570,16 @@
         <v>12</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H44">
-        <v>1.064</v>
+        <v>1.081</v>
       </c>
       <c r="I44">
-        <v>2.805</v>
+        <v>5.524</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="B45">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
@@ -1599,13 +1599,13 @@
         <v>2</v>
       </c>
       <c r="G45">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H45">
         <v>1.085</v>
       </c>
       <c r="I45">
-        <v>3.834</v>
+        <v>5.316</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1613,7 +1613,7 @@
         <v>5</v>
       </c>
       <c r="B46">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1622,19 +1622,19 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>6.989012772364849</v>
+        <v>8.380744769816141</v>
       </c>
       <c r="G46">
-        <v>0.004</v>
+        <v>-0</v>
       </c>
       <c r="H46">
-        <v>1.054</v>
+        <v>1.037</v>
       </c>
       <c r="I46">
-        <v>2.59</v>
+        <v>3.861</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1642,7 +1642,7 @@
         <v>6</v>
       </c>
       <c r="B47">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1651,16 +1651,16 @@
         <v>12</v>
       </c>
       <c r="E47">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H47">
-        <v>1.064</v>
+        <v>1.111</v>
       </c>
       <c r="I47">
-        <v>2.519</v>
+        <v>9.715999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1668,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="B48">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -1680,13 +1680,13 @@
         <v>2</v>
       </c>
       <c r="G48">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H48">
-        <v>1.083</v>
+        <v>1.173</v>
       </c>
       <c r="I48">
-        <v>4.438</v>
+        <v>9.194000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1694,7 +1694,7 @@
         <v>6</v>
       </c>
       <c r="B49">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1703,19 +1703,19 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F49">
-        <v>6.975167114337117</v>
+        <v>14.4181549479407</v>
       </c>
       <c r="G49">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="H49">
-        <v>1.056</v>
+        <v>1.06</v>
       </c>
       <c r="I49">
-        <v>2.428</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -1723,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="B50">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -1732,16 +1732,16 @@
         <v>12</v>
       </c>
       <c r="E50">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G50">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H50">
-        <v>1.064</v>
+        <v>1.111</v>
       </c>
       <c r="I50">
-        <v>2.519</v>
+        <v>9.715999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -1749,7 +1749,7 @@
         <v>6</v>
       </c>
       <c r="B51">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -1761,13 +1761,13 @@
         <v>2</v>
       </c>
       <c r="G51">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H51">
-        <v>1.083</v>
+        <v>1.173</v>
       </c>
       <c r="I51">
-        <v>4.438</v>
+        <v>9.194000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -1775,7 +1775,7 @@
         <v>6</v>
       </c>
       <c r="B52">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -1784,19 +1784,19 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F52">
-        <v>6.975167114337117</v>
+        <v>14.4181549479407</v>
       </c>
       <c r="G52">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="H52">
-        <v>1.056</v>
+        <v>1.06</v>
       </c>
       <c r="I52">
-        <v>2.428</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -1804,7 +1804,7 @@
         <v>6</v>
       </c>
       <c r="B53">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
@@ -1813,16 +1813,16 @@
         <v>12</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H53">
-        <v>1.064</v>
+        <v>1.111</v>
       </c>
       <c r="I53">
-        <v>2.519</v>
+        <v>9.715999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -1830,7 +1830,7 @@
         <v>6</v>
       </c>
       <c r="B54">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
@@ -1842,13 +1842,13 @@
         <v>2</v>
       </c>
       <c r="G54">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H54">
-        <v>1.083</v>
+        <v>1.173</v>
       </c>
       <c r="I54">
-        <v>4.438</v>
+        <v>9.194000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -1856,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="B55">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
@@ -1865,19 +1865,19 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F55">
-        <v>6.975167114337117</v>
+        <v>14.4181549479407</v>
       </c>
       <c r="G55">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="H55">
-        <v>1.056</v>
+        <v>1.06</v>
       </c>
       <c r="I55">
-        <v>2.428</v>
+        <v>3.274</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -1885,7 +1885,7 @@
         <v>7</v>
       </c>
       <c r="B56">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
@@ -1897,13 +1897,13 @@
         <v>2</v>
       </c>
       <c r="G56">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H56">
-        <v>1.071</v>
+        <v>1.087</v>
       </c>
       <c r="I56">
-        <v>4.374</v>
+        <v>6.778</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -1911,7 +1911,7 @@
         <v>7</v>
       </c>
       <c r="B57">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
@@ -1923,13 +1923,13 @@
         <v>2</v>
       </c>
       <c r="G57">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H57">
-        <v>1.073</v>
+        <v>1.112</v>
       </c>
       <c r="I57">
-        <v>4.242</v>
+        <v>6.574</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
       <c r="B58">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
@@ -1946,19 +1946,19 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58">
-        <v>6.984129907238213</v>
+        <v>10.15579714509119</v>
       </c>
       <c r="G58">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H58">
-        <v>1.041</v>
+        <v>1.031</v>
       </c>
       <c r="I58">
-        <v>2.628</v>
+        <v>4.681</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -1966,7 +1966,7 @@
         <v>7</v>
       </c>
       <c r="B59">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
@@ -1978,13 +1978,13 @@
         <v>2</v>
       </c>
       <c r="G59">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H59">
-        <v>1.071</v>
+        <v>1.087</v>
       </c>
       <c r="I59">
-        <v>4.374</v>
+        <v>6.778</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -1992,7 +1992,7 @@
         <v>7</v>
       </c>
       <c r="B60">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C60" t="s">
         <v>10</v>
@@ -2004,13 +2004,13 @@
         <v>2</v>
       </c>
       <c r="G60">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H60">
-        <v>1.073</v>
+        <v>1.112</v>
       </c>
       <c r="I60">
-        <v>4.242</v>
+        <v>6.574</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2018,7 +2018,7 @@
         <v>7</v>
       </c>
       <c r="B61">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C61" t="s">
         <v>10</v>
@@ -2027,19 +2027,19 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F61">
-        <v>6.984129907238213</v>
+        <v>10.15579714509119</v>
       </c>
       <c r="G61">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H61">
-        <v>1.041</v>
+        <v>1.031</v>
       </c>
       <c r="I61">
-        <v>2.628</v>
+        <v>4.681</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2047,7 +2047,7 @@
         <v>7</v>
       </c>
       <c r="B62">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
@@ -2059,13 +2059,13 @@
         <v>2</v>
       </c>
       <c r="G62">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H62">
-        <v>1.071</v>
+        <v>1.087</v>
       </c>
       <c r="I62">
-        <v>4.374</v>
+        <v>6.778</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="B63">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
@@ -2085,13 +2085,13 @@
         <v>2</v>
       </c>
       <c r="G63">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H63">
-        <v>1.073</v>
+        <v>1.112</v>
       </c>
       <c r="I63">
-        <v>4.242</v>
+        <v>6.574</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2099,7 +2099,7 @@
         <v>7</v>
       </c>
       <c r="B64">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
@@ -2108,19 +2108,19 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>6.984129907238213</v>
+        <v>10.15579714509119</v>
       </c>
       <c r="G64">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H64">
-        <v>1.041</v>
+        <v>1.031</v>
       </c>
       <c r="I64">
-        <v>2.628</v>
+        <v>4.681</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2128,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="B65">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
@@ -2137,16 +2137,16 @@
         <v>12</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H65">
-        <v>1.061</v>
+        <v>1.073</v>
       </c>
       <c r="I65">
-        <v>2.803</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2154,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="B66">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
@@ -2166,13 +2166,13 @@
         <v>2</v>
       </c>
       <c r="G66">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H66">
-        <v>1.079</v>
+        <v>1.091</v>
       </c>
       <c r="I66">
-        <v>4.061</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2180,7 +2180,7 @@
         <v>8</v>
       </c>
       <c r="B67">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
@@ -2189,19 +2189,19 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>7.002346183676972</v>
+        <v>8.390488438364949</v>
       </c>
       <c r="G67">
         <v>0.002</v>
       </c>
       <c r="H67">
-        <v>1.045</v>
+        <v>1.059</v>
       </c>
       <c r="I67">
-        <v>2.924</v>
+        <v>4.224</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2209,7 +2209,7 @@
         <v>8</v>
       </c>
       <c r="B68">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C68" t="s">
         <v>10</v>
@@ -2218,16 +2218,16 @@
         <v>12</v>
       </c>
       <c r="E68">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G68">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H68">
-        <v>1.061</v>
+        <v>1.073</v>
       </c>
       <c r="I68">
-        <v>2.803</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2235,7 +2235,7 @@
         <v>8</v>
       </c>
       <c r="B69">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
@@ -2247,13 +2247,13 @@
         <v>2</v>
       </c>
       <c r="G69">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H69">
-        <v>1.079</v>
+        <v>1.091</v>
       </c>
       <c r="I69">
-        <v>4.061</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2261,7 +2261,7 @@
         <v>8</v>
       </c>
       <c r="B70">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
@@ -2270,19 +2270,19 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70">
-        <v>7.002346183676972</v>
+        <v>8.390488438364949</v>
       </c>
       <c r="G70">
         <v>0.002</v>
       </c>
       <c r="H70">
-        <v>1.045</v>
+        <v>1.059</v>
       </c>
       <c r="I70">
-        <v>2.924</v>
+        <v>4.224</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2290,7 +2290,7 @@
         <v>8</v>
       </c>
       <c r="B71">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -2299,16 +2299,16 @@
         <v>12</v>
       </c>
       <c r="E71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H71">
-        <v>1.061</v>
+        <v>1.073</v>
       </c>
       <c r="I71">
-        <v>2.803</v>
+        <v>5.428</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2316,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="B72">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -2328,13 +2328,13 @@
         <v>2</v>
       </c>
       <c r="G72">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H72">
-        <v>1.079</v>
+        <v>1.091</v>
       </c>
       <c r="I72">
-        <v>4.061</v>
+        <v>4.756</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2342,7 +2342,7 @@
         <v>8</v>
       </c>
       <c r="B73">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -2351,19 +2351,19 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>7.002346183676972</v>
+        <v>8.390488438364949</v>
       </c>
       <c r="G73">
         <v>0.002</v>
       </c>
       <c r="H73">
-        <v>1.045</v>
+        <v>1.059</v>
       </c>
       <c r="I73">
-        <v>2.924</v>
+        <v>4.224</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2371,7 +2371,7 @@
         <v>9</v>
       </c>
       <c r="B74">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
@@ -2386,10 +2386,10 @@
         <v>0.003</v>
       </c>
       <c r="H74">
-        <v>1.066</v>
+        <v>1.086</v>
       </c>
       <c r="I74">
-        <v>4.543</v>
+        <v>4.793</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2397,7 +2397,7 @@
         <v>9</v>
       </c>
       <c r="B75">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
@@ -2412,10 +2412,10 @@
         <v>0.004</v>
       </c>
       <c r="H75">
-        <v>1.101</v>
+        <v>1.1</v>
       </c>
       <c r="I75">
-        <v>4.019</v>
+        <v>4.763</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2423,7 +2423,7 @@
         <v>9</v>
       </c>
       <c r="B76">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C76" t="s">
         <v>9</v>
@@ -2432,19 +2432,19 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>6.98045813360795</v>
+        <v>7.394710106675184</v>
       </c>
       <c r="G76">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H76">
-        <v>1.049</v>
+        <v>1.047</v>
       </c>
       <c r="I76">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2452,7 +2452,7 @@
         <v>9</v>
       </c>
       <c r="B77">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C77" t="s">
         <v>10</v>
@@ -2467,10 +2467,10 @@
         <v>0.003</v>
       </c>
       <c r="H77">
-        <v>1.066</v>
+        <v>1.086</v>
       </c>
       <c r="I77">
-        <v>4.543</v>
+        <v>4.793</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2478,7 +2478,7 @@
         <v>9</v>
       </c>
       <c r="B78">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
@@ -2493,10 +2493,10 @@
         <v>0.004</v>
       </c>
       <c r="H78">
-        <v>1.101</v>
+        <v>1.1</v>
       </c>
       <c r="I78">
-        <v>4.019</v>
+        <v>4.763</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2504,7 +2504,7 @@
         <v>9</v>
       </c>
       <c r="B79">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
@@ -2513,19 +2513,19 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>6.98045813360795</v>
+        <v>7.394710106675184</v>
       </c>
       <c r="G79">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H79">
-        <v>1.049</v>
+        <v>1.047</v>
       </c>
       <c r="I79">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2533,7 +2533,7 @@
         <v>9</v>
       </c>
       <c r="B80">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -2548,10 +2548,10 @@
         <v>0.003</v>
       </c>
       <c r="H80">
-        <v>1.066</v>
+        <v>1.086</v>
       </c>
       <c r="I80">
-        <v>4.543</v>
+        <v>4.793</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2559,7 +2559,7 @@
         <v>9</v>
       </c>
       <c r="B81">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -2574,10 +2574,10 @@
         <v>0.004</v>
       </c>
       <c r="H81">
-        <v>1.101</v>
+        <v>1.1</v>
       </c>
       <c r="I81">
-        <v>4.019</v>
+        <v>4.763</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
       <c r="B82">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -2594,19 +2594,19 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F82">
-        <v>6.98045813360795</v>
+        <v>7.394710106675184</v>
       </c>
       <c r="G82">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H82">
-        <v>1.049</v>
+        <v>1.047</v>
       </c>
       <c r="I82">
-        <v>2.4</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -2614,7 +2614,7 @@
         <v>10</v>
       </c>
       <c r="B83">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
@@ -2626,13 +2626,13 @@
         <v>2</v>
       </c>
       <c r="G83">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H83">
-        <v>1.091</v>
+        <v>1.095</v>
       </c>
       <c r="I83">
-        <v>4.472</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -2640,7 +2640,7 @@
         <v>10</v>
       </c>
       <c r="B84">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C84" t="s">
         <v>9</v>
@@ -2652,13 +2652,13 @@
         <v>2</v>
       </c>
       <c r="G84">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H84">
-        <v>1.086</v>
+        <v>1.161</v>
       </c>
       <c r="I84">
-        <v>4.431</v>
+        <v>9.224</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -2666,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="B85">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
@@ -2675,19 +2675,19 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F85">
-        <v>7.000622057062256</v>
+        <v>15.02334732593209</v>
       </c>
       <c r="G85">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H85">
-        <v>1.054</v>
+        <v>1.061</v>
       </c>
       <c r="I85">
-        <v>3.148</v>
+        <v>3.047</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -2695,7 +2695,7 @@
         <v>10</v>
       </c>
       <c r="B86">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
@@ -2707,13 +2707,13 @@
         <v>2</v>
       </c>
       <c r="G86">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H86">
-        <v>1.091</v>
+        <v>1.095</v>
       </c>
       <c r="I86">
-        <v>4.472</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -2721,7 +2721,7 @@
         <v>10</v>
       </c>
       <c r="B87">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
@@ -2733,13 +2733,13 @@
         <v>2</v>
       </c>
       <c r="G87">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H87">
-        <v>1.086</v>
+        <v>1.161</v>
       </c>
       <c r="I87">
-        <v>4.431</v>
+        <v>9.224</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="B88">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
@@ -2756,19 +2756,19 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F88">
-        <v>7.000622057062256</v>
+        <v>15.02334732593209</v>
       </c>
       <c r="G88">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H88">
-        <v>1.054</v>
+        <v>1.061</v>
       </c>
       <c r="I88">
-        <v>3.148</v>
+        <v>3.047</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -2776,7 +2776,7 @@
         <v>10</v>
       </c>
       <c r="B89">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -2788,13 +2788,13 @@
         <v>2</v>
       </c>
       <c r="G89">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H89">
-        <v>1.091</v>
+        <v>1.095</v>
       </c>
       <c r="I89">
-        <v>4.472</v>
+        <v>10.196</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -2802,7 +2802,7 @@
         <v>10</v>
       </c>
       <c r="B90">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -2814,13 +2814,13 @@
         <v>2</v>
       </c>
       <c r="G90">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H90">
-        <v>1.086</v>
+        <v>1.161</v>
       </c>
       <c r="I90">
-        <v>4.431</v>
+        <v>9.224</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="B91">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -2837,19 +2837,19 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F91">
-        <v>7.000622057062256</v>
+        <v>15.02334732593209</v>
       </c>
       <c r="G91">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H91">
-        <v>1.054</v>
+        <v>1.061</v>
       </c>
       <c r="I91">
-        <v>3.148</v>
+        <v>3.047</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -2857,7 +2857,7 @@
         <v>11</v>
       </c>
       <c r="B92">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
@@ -2866,16 +2866,16 @@
         <v>12</v>
       </c>
       <c r="E92">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G92">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H92">
-        <v>1.067</v>
+        <v>1.1</v>
       </c>
       <c r="I92">
-        <v>2.327</v>
+        <v>6.033</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -2883,7 +2883,7 @@
         <v>11</v>
       </c>
       <c r="B93">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
@@ -2895,13 +2895,13 @@
         <v>2</v>
       </c>
       <c r="G93">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H93">
-        <v>1.077</v>
+        <v>1.112</v>
       </c>
       <c r="I93">
-        <v>3.847</v>
+        <v>7.274</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -2909,7 +2909,7 @@
         <v>11</v>
       </c>
       <c r="B94">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
@@ -2918,19 +2918,19 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F94">
-        <v>6.978819220421105</v>
+        <v>10.9704006065243</v>
       </c>
       <c r="G94">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="H94">
-        <v>1.055</v>
+        <v>1.047</v>
       </c>
       <c r="I94">
-        <v>2.064</v>
+        <v>3.109</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -2938,7 +2938,7 @@
         <v>11</v>
       </c>
       <c r="B95">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
@@ -2947,16 +2947,16 @@
         <v>12</v>
       </c>
       <c r="E95">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G95">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H95">
-        <v>1.067</v>
+        <v>1.1</v>
       </c>
       <c r="I95">
-        <v>2.327</v>
+        <v>6.033</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -2964,7 +2964,7 @@
         <v>11</v>
       </c>
       <c r="B96">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
@@ -2976,13 +2976,13 @@
         <v>2</v>
       </c>
       <c r="G96">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H96">
-        <v>1.077</v>
+        <v>1.112</v>
       </c>
       <c r="I96">
-        <v>3.847</v>
+        <v>7.274</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -2990,7 +2990,7 @@
         <v>11</v>
       </c>
       <c r="B97">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
@@ -2999,19 +2999,19 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F97">
-        <v>6.978819220421105</v>
+        <v>10.9704006065243</v>
       </c>
       <c r="G97">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="H97">
-        <v>1.055</v>
+        <v>1.047</v>
       </c>
       <c r="I97">
-        <v>2.064</v>
+        <v>3.109</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3019,7 +3019,7 @@
         <v>11</v>
       </c>
       <c r="B98">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -3028,16 +3028,16 @@
         <v>12</v>
       </c>
       <c r="E98">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G98">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="H98">
-        <v>1.067</v>
+        <v>1.1</v>
       </c>
       <c r="I98">
-        <v>2.327</v>
+        <v>6.033</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3045,7 +3045,7 @@
         <v>11</v>
       </c>
       <c r="B99">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
@@ -3057,13 +3057,13 @@
         <v>2</v>
       </c>
       <c r="G99">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H99">
-        <v>1.077</v>
+        <v>1.112</v>
       </c>
       <c r="I99">
-        <v>3.847</v>
+        <v>7.274</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3071,7 +3071,7 @@
         <v>11</v>
       </c>
       <c r="B100">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
@@ -3080,19 +3080,19 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F100">
-        <v>6.978819220421105</v>
+        <v>10.9704006065243</v>
       </c>
       <c r="G100">
-        <v>0.005</v>
+        <v>-0.001</v>
       </c>
       <c r="H100">
-        <v>1.055</v>
+        <v>1.047</v>
       </c>
       <c r="I100">
-        <v>2.064</v>
+        <v>3.109</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3100,7 +3100,7 @@
         <v>12</v>
       </c>
       <c r="B101">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
@@ -3112,13 +3112,13 @@
         <v>2</v>
       </c>
       <c r="G101">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H101">
-        <v>1.057</v>
+        <v>1.107</v>
       </c>
       <c r="I101">
-        <v>4.562</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3126,7 +3126,7 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C102" t="s">
         <v>9</v>
@@ -3138,13 +3138,13 @@
         <v>2</v>
       </c>
       <c r="G102">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H102">
-        <v>1.083</v>
+        <v>1.163</v>
       </c>
       <c r="I102">
-        <v>4.437</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3152,7 +3152,7 @@
         <v>12</v>
       </c>
       <c r="B103">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C103" t="s">
         <v>9</v>
@@ -3161,19 +3161,19 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F103">
-        <v>7.00387084227275</v>
+        <v>15.08086629128625</v>
       </c>
       <c r="G103">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H103">
-        <v>1.048</v>
+        <v>1.07</v>
       </c>
       <c r="I103">
-        <v>3.635</v>
+        <v>3.824</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3181,7 +3181,7 @@
         <v>12</v>
       </c>
       <c r="B104">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
@@ -3193,13 +3193,13 @@
         <v>2</v>
       </c>
       <c r="G104">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H104">
-        <v>1.057</v>
+        <v>1.107</v>
       </c>
       <c r="I104">
-        <v>4.562</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3207,7 +3207,7 @@
         <v>12</v>
       </c>
       <c r="B105">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C105" t="s">
         <v>10</v>
@@ -3219,13 +3219,13 @@
         <v>2</v>
       </c>
       <c r="G105">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H105">
-        <v>1.083</v>
+        <v>1.163</v>
       </c>
       <c r="I105">
-        <v>4.437</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3233,7 +3233,7 @@
         <v>12</v>
       </c>
       <c r="B106">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
@@ -3242,19 +3242,19 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F106">
-        <v>7.00387084227275</v>
+        <v>15.08086629128625</v>
       </c>
       <c r="G106">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H106">
-        <v>1.048</v>
+        <v>1.07</v>
       </c>
       <c r="I106">
-        <v>3.635</v>
+        <v>3.824</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3262,7 +3262,7 @@
         <v>12</v>
       </c>
       <c r="B107">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C107" t="s">
         <v>11</v>
@@ -3274,13 +3274,13 @@
         <v>2</v>
       </c>
       <c r="G107">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H107">
-        <v>1.057</v>
+        <v>1.107</v>
       </c>
       <c r="I107">
-        <v>4.562</v>
+        <v>10.189</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3288,7 +3288,7 @@
         <v>12</v>
       </c>
       <c r="B108">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C108" t="s">
         <v>11</v>
@@ -3300,13 +3300,13 @@
         <v>2</v>
       </c>
       <c r="G108">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H108">
-        <v>1.083</v>
+        <v>1.163</v>
       </c>
       <c r="I108">
-        <v>4.437</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3314,7 +3314,7 @@
         <v>12</v>
       </c>
       <c r="B109">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
         <v>11</v>
@@ -3323,19 +3323,19 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F109">
-        <v>7.00387084227275</v>
+        <v>15.08086629128625</v>
       </c>
       <c r="G109">
-        <v>0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="H109">
-        <v>1.048</v>
+        <v>1.07</v>
       </c>
       <c r="I109">
-        <v>3.635</v>
+        <v>3.824</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3343,7 +3343,7 @@
         <v>13</v>
       </c>
       <c r="B110">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C110" t="s">
         <v>9</v>
@@ -3355,13 +3355,13 @@
         <v>3</v>
       </c>
       <c r="G110">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>1.061</v>
+        <v>1.072</v>
       </c>
       <c r="I110">
-        <v>3.705</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3369,7 +3369,7 @@
         <v>13</v>
       </c>
       <c r="B111">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C111" t="s">
         <v>9</v>
@@ -3381,13 +3381,13 @@
         <v>2</v>
       </c>
       <c r="G111">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H111">
-        <v>1.096</v>
+        <v>1.134</v>
       </c>
       <c r="I111">
-        <v>4.323</v>
+        <v>9.263999999999999</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3395,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="B112">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C112" t="s">
         <v>9</v>
@@ -3404,19 +3404,19 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F112">
-        <v>6.982544670052743</v>
+        <v>13.96706662962144</v>
       </c>
       <c r="G112">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>1.042</v>
+        <v>1.065</v>
       </c>
       <c r="I112">
-        <v>2.615</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -3424,7 +3424,7 @@
         <v>13</v>
       </c>
       <c r="B113">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C113" t="s">
         <v>10</v>
@@ -3436,13 +3436,13 @@
         <v>3</v>
       </c>
       <c r="G113">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>1.061</v>
+        <v>1.072</v>
       </c>
       <c r="I113">
-        <v>3.705</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -3450,7 +3450,7 @@
         <v>13</v>
       </c>
       <c r="B114">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C114" t="s">
         <v>10</v>
@@ -3462,13 +3462,13 @@
         <v>2</v>
       </c>
       <c r="G114">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H114">
-        <v>1.096</v>
+        <v>1.134</v>
       </c>
       <c r="I114">
-        <v>4.323</v>
+        <v>9.263999999999999</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3476,7 +3476,7 @@
         <v>13</v>
       </c>
       <c r="B115">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C115" t="s">
         <v>10</v>
@@ -3485,19 +3485,19 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F115">
-        <v>6.982544670052743</v>
+        <v>13.96706662962144</v>
       </c>
       <c r="G115">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>1.042</v>
+        <v>1.065</v>
       </c>
       <c r="I115">
-        <v>2.615</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3505,7 +3505,7 @@
         <v>13</v>
       </c>
       <c r="B116">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C116" t="s">
         <v>11</v>
@@ -3517,13 +3517,13 @@
         <v>3</v>
       </c>
       <c r="G116">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>1.061</v>
+        <v>1.072</v>
       </c>
       <c r="I116">
-        <v>3.705</v>
+        <v>7.836</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3531,7 +3531,7 @@
         <v>13</v>
       </c>
       <c r="B117">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C117" t="s">
         <v>11</v>
@@ -3543,13 +3543,13 @@
         <v>2</v>
       </c>
       <c r="G117">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H117">
-        <v>1.096</v>
+        <v>1.134</v>
       </c>
       <c r="I117">
-        <v>4.323</v>
+        <v>9.263999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -3557,7 +3557,7 @@
         <v>13</v>
       </c>
       <c r="B118">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
@@ -3566,19 +3566,19 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F118">
-        <v>6.982544670052743</v>
+        <v>13.96706662962144</v>
       </c>
       <c r="G118">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>1.042</v>
+        <v>1.065</v>
       </c>
       <c r="I118">
-        <v>2.615</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -3586,7 +3586,7 @@
         <v>14</v>
       </c>
       <c r="B119">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C119" t="s">
         <v>9</v>
@@ -3595,16 +3595,16 @@
         <v>12</v>
       </c>
       <c r="E119">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G119">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>1.064</v>
+        <v>1.082</v>
       </c>
       <c r="I119">
-        <v>3.215</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3612,7 +3612,7 @@
         <v>14</v>
       </c>
       <c r="B120">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C120" t="s">
         <v>9</v>
@@ -3624,13 +3624,13 @@
         <v>2</v>
       </c>
       <c r="G120">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H120">
-        <v>1.071</v>
+        <v>1.152</v>
       </c>
       <c r="I120">
-        <v>4.246</v>
+        <v>8.587</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3638,7 +3638,7 @@
         <v>14</v>
       </c>
       <c r="B121">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C121" t="s">
         <v>9</v>
@@ -3647,19 +3647,19 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F121">
-        <v>6.999439084704824</v>
+        <v>15.02063201977164</v>
       </c>
       <c r="G121">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>1.057</v>
+        <v>1.066</v>
       </c>
       <c r="I121">
-        <v>2.578</v>
+        <v>3.088</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -3667,7 +3667,7 @@
         <v>14</v>
       </c>
       <c r="B122">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C122" t="s">
         <v>10</v>
@@ -3676,16 +3676,16 @@
         <v>12</v>
       </c>
       <c r="E122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G122">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>1.064</v>
+        <v>1.082</v>
       </c>
       <c r="I122">
-        <v>3.215</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -3693,7 +3693,7 @@
         <v>14</v>
       </c>
       <c r="B123">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C123" t="s">
         <v>10</v>
@@ -3705,13 +3705,13 @@
         <v>2</v>
       </c>
       <c r="G123">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H123">
-        <v>1.071</v>
+        <v>1.152</v>
       </c>
       <c r="I123">
-        <v>4.246</v>
+        <v>8.587</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -3719,7 +3719,7 @@
         <v>14</v>
       </c>
       <c r="B124">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C124" t="s">
         <v>10</v>
@@ -3728,19 +3728,19 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F124">
-        <v>6.999439084704824</v>
+        <v>15.02063201977164</v>
       </c>
       <c r="G124">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>1.057</v>
+        <v>1.066</v>
       </c>
       <c r="I124">
-        <v>2.578</v>
+        <v>3.088</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -3748,7 +3748,7 @@
         <v>14</v>
       </c>
       <c r="B125">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
@@ -3757,16 +3757,16 @@
         <v>12</v>
       </c>
       <c r="E125">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G125">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>1.064</v>
+        <v>1.082</v>
       </c>
       <c r="I125">
-        <v>3.215</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -3774,7 +3774,7 @@
         <v>14</v>
       </c>
       <c r="B126">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C126" t="s">
         <v>11</v>
@@ -3786,13 +3786,13 @@
         <v>2</v>
       </c>
       <c r="G126">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H126">
-        <v>1.071</v>
+        <v>1.152</v>
       </c>
       <c r="I126">
-        <v>4.246</v>
+        <v>8.587</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -3800,7 +3800,7 @@
         <v>14</v>
       </c>
       <c r="B127">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C127" t="s">
         <v>11</v>
@@ -3809,19 +3809,19 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F127">
-        <v>6.999439084704824</v>
+        <v>15.02063201977164</v>
       </c>
       <c r="G127">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>1.057</v>
+        <v>1.066</v>
       </c>
       <c r="I127">
-        <v>2.578</v>
+        <v>3.088</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -3829,7 +3829,7 @@
         <v>15</v>
       </c>
       <c r="B128">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C128" t="s">
         <v>9</v>
@@ -3838,16 +3838,16 @@
         <v>12</v>
       </c>
       <c r="E128">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G128">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H128">
-        <v>1.062</v>
+        <v>1.061</v>
       </c>
       <c r="I128">
-        <v>4.552</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -3855,7 +3855,7 @@
         <v>15</v>
       </c>
       <c r="B129">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C129" t="s">
         <v>9</v>
@@ -3870,10 +3870,10 @@
         <v>0.003</v>
       </c>
       <c r="H129">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="I129">
-        <v>4.235</v>
+        <v>5.032</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -3881,7 +3881,7 @@
         <v>15</v>
       </c>
       <c r="B130">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C130" t="s">
         <v>9</v>
@@ -3890,19 +3890,19 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130">
-        <v>7.012755957098546</v>
+        <v>7.912438240710293</v>
       </c>
       <c r="G130">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>1.037</v>
+        <v>1.039</v>
       </c>
       <c r="I130">
-        <v>3.579</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -3910,7 +3910,7 @@
         <v>15</v>
       </c>
       <c r="B131">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C131" t="s">
         <v>10</v>
@@ -3919,16 +3919,16 @@
         <v>12</v>
       </c>
       <c r="E131">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G131">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H131">
-        <v>1.062</v>
+        <v>1.061</v>
       </c>
       <c r="I131">
-        <v>4.552</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -3936,7 +3936,7 @@
         <v>15</v>
       </c>
       <c r="B132">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C132" t="s">
         <v>10</v>
@@ -3951,10 +3951,10 @@
         <v>0.003</v>
       </c>
       <c r="H132">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="I132">
-        <v>4.235</v>
+        <v>5.032</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -3962,7 +3962,7 @@
         <v>15</v>
       </c>
       <c r="B133">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C133" t="s">
         <v>10</v>
@@ -3971,19 +3971,19 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133">
-        <v>7.012755957098546</v>
+        <v>7.912438240710293</v>
       </c>
       <c r="G133">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H133">
-        <v>1.037</v>
+        <v>1.039</v>
       </c>
       <c r="I133">
-        <v>3.579</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -3991,7 +3991,7 @@
         <v>15</v>
       </c>
       <c r="B134">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C134" t="s">
         <v>11</v>
@@ -4000,16 +4000,16 @@
         <v>12</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G134">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H134">
-        <v>1.062</v>
+        <v>1.061</v>
       </c>
       <c r="I134">
-        <v>4.552</v>
+        <v>2.757</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4017,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="B135">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C135" t="s">
         <v>11</v>
@@ -4032,10 +4032,10 @@
         <v>0.003</v>
       </c>
       <c r="H135">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="I135">
-        <v>4.235</v>
+        <v>5.032</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4043,7 +4043,7 @@
         <v>15</v>
       </c>
       <c r="B136">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C136" t="s">
         <v>11</v>
@@ -4052,19 +4052,19 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136">
-        <v>7.012755957098546</v>
+        <v>7.912438240710293</v>
       </c>
       <c r="G136">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H136">
-        <v>1.037</v>
+        <v>1.039</v>
       </c>
       <c r="I136">
-        <v>3.579</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4072,7 +4072,7 @@
         <v>16</v>
       </c>
       <c r="B137">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C137" t="s">
         <v>9</v>
@@ -4081,16 +4081,16 @@
         <v>12</v>
       </c>
       <c r="E137">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G137">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H137">
-        <v>1.062</v>
+        <v>1.071</v>
       </c>
       <c r="I137">
-        <v>2.252</v>
+        <v>3.935</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4098,7 +4098,7 @@
         <v>16</v>
       </c>
       <c r="B138">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C138" t="s">
         <v>9</v>
@@ -4110,13 +4110,13 @@
         <v>2</v>
       </c>
       <c r="G138">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H138">
-        <v>1.088</v>
+        <v>1.127</v>
       </c>
       <c r="I138">
-        <v>4.339</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4124,7 +4124,7 @@
         <v>16</v>
       </c>
       <c r="B139">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C139" t="s">
         <v>9</v>
@@ -4133,19 +4133,19 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F139">
-        <v>6.994334980434537</v>
+        <v>9.14164619158197</v>
       </c>
       <c r="G139">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>1.054</v>
+        <v>1.047</v>
       </c>
       <c r="I139">
-        <v>2.606</v>
+        <v>3.296</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4153,7 +4153,7 @@
         <v>16</v>
       </c>
       <c r="B140">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C140" t="s">
         <v>10</v>
@@ -4162,16 +4162,16 @@
         <v>12</v>
       </c>
       <c r="E140">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G140">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H140">
-        <v>1.062</v>
+        <v>1.071</v>
       </c>
       <c r="I140">
-        <v>2.252</v>
+        <v>3.935</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4179,7 +4179,7 @@
         <v>16</v>
       </c>
       <c r="B141">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C141" t="s">
         <v>10</v>
@@ -4191,13 +4191,13 @@
         <v>2</v>
       </c>
       <c r="G141">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H141">
-        <v>1.088</v>
+        <v>1.127</v>
       </c>
       <c r="I141">
-        <v>4.339</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -4205,7 +4205,7 @@
         <v>16</v>
       </c>
       <c r="B142">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C142" t="s">
         <v>10</v>
@@ -4214,19 +4214,19 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F142">
-        <v>6.994334980434537</v>
+        <v>9.14164619158197</v>
       </c>
       <c r="G142">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>1.054</v>
+        <v>1.047</v>
       </c>
       <c r="I142">
-        <v>2.606</v>
+        <v>3.296</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4234,7 +4234,7 @@
         <v>16</v>
       </c>
       <c r="B143">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C143" t="s">
         <v>11</v>
@@ -4243,16 +4243,16 @@
         <v>12</v>
       </c>
       <c r="E143">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G143">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H143">
-        <v>1.062</v>
+        <v>1.071</v>
       </c>
       <c r="I143">
-        <v>2.252</v>
+        <v>3.935</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -4260,7 +4260,7 @@
         <v>16</v>
       </c>
       <c r="B144">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C144" t="s">
         <v>11</v>
@@ -4272,13 +4272,13 @@
         <v>2</v>
       </c>
       <c r="G144">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H144">
-        <v>1.088</v>
+        <v>1.127</v>
       </c>
       <c r="I144">
-        <v>4.339</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -4286,7 +4286,7 @@
         <v>16</v>
       </c>
       <c r="B145">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C145" t="s">
         <v>11</v>
@@ -4295,19 +4295,19 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F145">
-        <v>6.994334980434537</v>
+        <v>9.14164619158197</v>
       </c>
       <c r="G145">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>1.054</v>
+        <v>1.047</v>
       </c>
       <c r="I145">
-        <v>2.606</v>
+        <v>3.296</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -4315,7 +4315,7 @@
         <v>17</v>
       </c>
       <c r="B146">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C146" t="s">
         <v>9</v>
@@ -4324,16 +4324,16 @@
         <v>12</v>
       </c>
       <c r="E146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G146">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H146">
-        <v>1.061</v>
+        <v>1.118</v>
       </c>
       <c r="I146">
-        <v>3.645</v>
+        <v>9.406000000000001</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -4341,7 +4341,7 @@
         <v>17</v>
       </c>
       <c r="B147">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C147" t="s">
         <v>9</v>
@@ -4353,13 +4353,13 @@
         <v>2</v>
       </c>
       <c r="G147">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H147">
-        <v>1.078</v>
+        <v>1.147</v>
       </c>
       <c r="I147">
-        <v>3.57</v>
+        <v>8.196999999999999</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -4367,7 +4367,7 @@
         <v>17</v>
       </c>
       <c r="B148">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C148" t="s">
         <v>9</v>
@@ -4376,19 +4376,19 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F148">
-        <v>6.9991731960855</v>
+        <v>14.03894759773972</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="H148">
-        <v>1.026</v>
+        <v>1.046</v>
       </c>
       <c r="I148">
-        <v>3.323</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -4396,7 +4396,7 @@
         <v>17</v>
       </c>
       <c r="B149">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C149" t="s">
         <v>10</v>
@@ -4405,16 +4405,16 @@
         <v>12</v>
       </c>
       <c r="E149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G149">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H149">
-        <v>1.061</v>
+        <v>1.118</v>
       </c>
       <c r="I149">
-        <v>3.645</v>
+        <v>9.406000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -4422,7 +4422,7 @@
         <v>17</v>
       </c>
       <c r="B150">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C150" t="s">
         <v>10</v>
@@ -4434,13 +4434,13 @@
         <v>2</v>
       </c>
       <c r="G150">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H150">
-        <v>1.078</v>
+        <v>1.147</v>
       </c>
       <c r="I150">
-        <v>3.57</v>
+        <v>8.196999999999999</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -4448,7 +4448,7 @@
         <v>17</v>
       </c>
       <c r="B151">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C151" t="s">
         <v>10</v>
@@ -4457,19 +4457,19 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F151">
-        <v>6.9991731960855</v>
+        <v>14.03894759773972</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="H151">
-        <v>1.026</v>
+        <v>1.046</v>
       </c>
       <c r="I151">
-        <v>3.323</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -4477,7 +4477,7 @@
         <v>17</v>
       </c>
       <c r="B152">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C152" t="s">
         <v>11</v>
@@ -4486,16 +4486,16 @@
         <v>12</v>
       </c>
       <c r="E152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G152">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H152">
-        <v>1.061</v>
+        <v>1.118</v>
       </c>
       <c r="I152">
-        <v>3.645</v>
+        <v>9.406000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -4503,7 +4503,7 @@
         <v>17</v>
       </c>
       <c r="B153">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C153" t="s">
         <v>11</v>
@@ -4515,13 +4515,13 @@
         <v>2</v>
       </c>
       <c r="G153">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H153">
-        <v>1.078</v>
+        <v>1.147</v>
       </c>
       <c r="I153">
-        <v>3.57</v>
+        <v>8.196999999999999</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -4529,7 +4529,7 @@
         <v>17</v>
       </c>
       <c r="B154">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C154" t="s">
         <v>11</v>
@@ -4538,19 +4538,19 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F154">
-        <v>6.9991731960855</v>
+        <v>14.03894759773972</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="H154">
-        <v>1.026</v>
+        <v>1.046</v>
       </c>
       <c r="I154">
-        <v>3.323</v>
+        <v>3.771</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -4558,7 +4558,7 @@
         <v>18</v>
       </c>
       <c r="B155">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C155" t="s">
         <v>9</v>
@@ -4567,16 +4567,16 @@
         <v>12</v>
       </c>
       <c r="E155">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G155">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H155">
-        <v>1.063</v>
+        <v>1.07</v>
       </c>
       <c r="I155">
-        <v>2.606</v>
+        <v>4.778</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -4584,7 +4584,7 @@
         <v>18</v>
       </c>
       <c r="B156">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C156" t="s">
         <v>9</v>
@@ -4593,16 +4593,16 @@
         <v>13</v>
       </c>
       <c r="E156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G156">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H156">
-        <v>1.077</v>
+        <v>1.106</v>
       </c>
       <c r="I156">
-        <v>3.674</v>
+        <v>5.003</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -4610,7 +4610,7 @@
         <v>18</v>
       </c>
       <c r="B157">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C157" t="s">
         <v>9</v>
@@ -4622,16 +4622,16 @@
         <v>4</v>
       </c>
       <c r="F157">
-        <v>6.990043306756656</v>
+        <v>8.826018331994739</v>
       </c>
       <c r="G157">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>1.055</v>
+        <v>1.043</v>
       </c>
       <c r="I157">
-        <v>2.872</v>
+        <v>3.709</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -4639,7 +4639,7 @@
         <v>18</v>
       </c>
       <c r="B158">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C158" t="s">
         <v>10</v>
@@ -4648,16 +4648,16 @@
         <v>12</v>
       </c>
       <c r="E158">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G158">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H158">
-        <v>1.063</v>
+        <v>1.07</v>
       </c>
       <c r="I158">
-        <v>2.606</v>
+        <v>4.778</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -4665,7 +4665,7 @@
         <v>18</v>
       </c>
       <c r="B159">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C159" t="s">
         <v>10</v>
@@ -4674,16 +4674,16 @@
         <v>13</v>
       </c>
       <c r="E159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G159">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H159">
-        <v>1.077</v>
+        <v>1.106</v>
       </c>
       <c r="I159">
-        <v>3.674</v>
+        <v>5.003</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -4691,7 +4691,7 @@
         <v>18</v>
       </c>
       <c r="B160">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C160" t="s">
         <v>10</v>
@@ -4703,16 +4703,16 @@
         <v>4</v>
       </c>
       <c r="F160">
-        <v>6.990043306756656</v>
+        <v>8.826018331994739</v>
       </c>
       <c r="G160">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H160">
-        <v>1.055</v>
+        <v>1.043</v>
       </c>
       <c r="I160">
-        <v>2.872</v>
+        <v>3.709</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -4720,7 +4720,7 @@
         <v>18</v>
       </c>
       <c r="B161">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C161" t="s">
         <v>11</v>
@@ -4729,16 +4729,16 @@
         <v>12</v>
       </c>
       <c r="E161">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G161">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H161">
-        <v>1.063</v>
+        <v>1.07</v>
       </c>
       <c r="I161">
-        <v>2.606</v>
+        <v>4.778</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -4746,7 +4746,7 @@
         <v>18</v>
       </c>
       <c r="B162">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C162" t="s">
         <v>11</v>
@@ -4755,16 +4755,16 @@
         <v>13</v>
       </c>
       <c r="E162">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G162">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H162">
-        <v>1.077</v>
+        <v>1.106</v>
       </c>
       <c r="I162">
-        <v>3.674</v>
+        <v>5.003</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -4772,7 +4772,7 @@
         <v>18</v>
       </c>
       <c r="B163">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C163" t="s">
         <v>11</v>
@@ -4784,16 +4784,16 @@
         <v>4</v>
       </c>
       <c r="F163">
-        <v>6.990043306756656</v>
+        <v>8.826018331994739</v>
       </c>
       <c r="G163">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>1.055</v>
+        <v>1.043</v>
       </c>
       <c r="I163">
-        <v>2.872</v>
+        <v>3.709</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -4801,7 +4801,7 @@
         <v>19</v>
       </c>
       <c r="B164">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C164" t="s">
         <v>9</v>
@@ -4810,16 +4810,16 @@
         <v>12</v>
       </c>
       <c r="E164">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G164">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H164">
-        <v>1.06</v>
+        <v>1.081</v>
       </c>
       <c r="I164">
-        <v>2.235</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -4827,7 +4827,7 @@
         <v>19</v>
       </c>
       <c r="B165">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C165" t="s">
         <v>9</v>
@@ -4839,13 +4839,13 @@
         <v>2</v>
       </c>
       <c r="G165">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H165">
-        <v>1.08</v>
+        <v>1.139</v>
       </c>
       <c r="I165">
-        <v>4.228</v>
+        <v>7.581</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -4853,7 +4853,7 @@
         <v>19</v>
       </c>
       <c r="B166">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C166" t="s">
         <v>9</v>
@@ -4862,19 +4862,19 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F166">
-        <v>6.999031382938663</v>
+        <v>11.56470485610042</v>
       </c>
       <c r="G166">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H166">
-        <v>1.044</v>
+        <v>1.047</v>
       </c>
       <c r="I166">
-        <v>2.777</v>
+        <v>3.307</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -4882,7 +4882,7 @@
         <v>19</v>
       </c>
       <c r="B167">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C167" t="s">
         <v>10</v>
@@ -4891,16 +4891,16 @@
         <v>12</v>
       </c>
       <c r="E167">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G167">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H167">
-        <v>1.06</v>
+        <v>1.081</v>
       </c>
       <c r="I167">
-        <v>2.235</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -4908,7 +4908,7 @@
         <v>19</v>
       </c>
       <c r="B168">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C168" t="s">
         <v>10</v>
@@ -4920,13 +4920,13 @@
         <v>2</v>
       </c>
       <c r="G168">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H168">
-        <v>1.08</v>
+        <v>1.139</v>
       </c>
       <c r="I168">
-        <v>4.228</v>
+        <v>7.581</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -4934,7 +4934,7 @@
         <v>19</v>
       </c>
       <c r="B169">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C169" t="s">
         <v>10</v>
@@ -4943,19 +4943,19 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F169">
-        <v>6.999031382938663</v>
+        <v>11.56470485610042</v>
       </c>
       <c r="G169">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H169">
-        <v>1.044</v>
+        <v>1.047</v>
       </c>
       <c r="I169">
-        <v>2.777</v>
+        <v>3.307</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -4963,7 +4963,7 @@
         <v>19</v>
       </c>
       <c r="B170">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C170" t="s">
         <v>11</v>
@@ -4972,16 +4972,16 @@
         <v>12</v>
       </c>
       <c r="E170">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G170">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H170">
-        <v>1.06</v>
+        <v>1.081</v>
       </c>
       <c r="I170">
-        <v>2.235</v>
+        <v>5.63</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -4989,7 +4989,7 @@
         <v>19</v>
       </c>
       <c r="B171">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C171" t="s">
         <v>11</v>
@@ -5001,13 +5001,13 @@
         <v>2</v>
       </c>
       <c r="G171">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H171">
-        <v>1.08</v>
+        <v>1.139</v>
       </c>
       <c r="I171">
-        <v>4.228</v>
+        <v>7.581</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -5015,7 +5015,7 @@
         <v>19</v>
       </c>
       <c r="B172">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
@@ -5024,19 +5024,19 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F172">
-        <v>6.999031382938663</v>
+        <v>11.56470485610042</v>
       </c>
       <c r="G172">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H172">
-        <v>1.044</v>
+        <v>1.047</v>
       </c>
       <c r="I172">
-        <v>2.777</v>
+        <v>3.307</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -5044,7 +5044,7 @@
         <v>20</v>
       </c>
       <c r="B173">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C173" t="s">
         <v>9</v>
@@ -5053,16 +5053,16 @@
         <v>12</v>
       </c>
       <c r="E173">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G173">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H173">
-        <v>1.077</v>
+        <v>1.061</v>
       </c>
       <c r="I173">
-        <v>4.502</v>
+        <v>3.311</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -5070,7 +5070,7 @@
         <v>20</v>
       </c>
       <c r="B174">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C174" t="s">
         <v>9</v>
@@ -5085,10 +5085,10 @@
         <v>0.003</v>
       </c>
       <c r="H174">
-        <v>1.075</v>
+        <v>1.1</v>
       </c>
       <c r="I174">
-        <v>3.578</v>
+        <v>5.091</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -5096,7 +5096,7 @@
         <v>20</v>
       </c>
       <c r="B175">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C175" t="s">
         <v>9</v>
@@ -5105,19 +5105,19 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F175">
-        <v>6.996730349272068</v>
+        <v>8.50062431642713</v>
       </c>
       <c r="G175">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>1.041</v>
+        <v>1.009</v>
       </c>
       <c r="I175">
-        <v>3.172</v>
+        <v>4.978</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -5125,7 +5125,7 @@
         <v>20</v>
       </c>
       <c r="B176">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C176" t="s">
         <v>10</v>
@@ -5134,16 +5134,16 @@
         <v>12</v>
       </c>
       <c r="E176">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G176">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H176">
-        <v>1.077</v>
+        <v>1.061</v>
       </c>
       <c r="I176">
-        <v>4.502</v>
+        <v>3.311</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -5151,7 +5151,7 @@
         <v>20</v>
       </c>
       <c r="B177">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C177" t="s">
         <v>10</v>
@@ -5166,10 +5166,10 @@
         <v>0.003</v>
       </c>
       <c r="H177">
-        <v>1.075</v>
+        <v>1.1</v>
       </c>
       <c r="I177">
-        <v>3.578</v>
+        <v>5.091</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -5177,7 +5177,7 @@
         <v>20</v>
       </c>
       <c r="B178">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C178" t="s">
         <v>10</v>
@@ -5186,19 +5186,19 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F178">
-        <v>6.996730349272068</v>
+        <v>8.50062431642713</v>
       </c>
       <c r="G178">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>1.041</v>
+        <v>1.009</v>
       </c>
       <c r="I178">
-        <v>3.172</v>
+        <v>4.978</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -5206,7 +5206,7 @@
         <v>20</v>
       </c>
       <c r="B179">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C179" t="s">
         <v>11</v>
@@ -5215,16 +5215,16 @@
         <v>12</v>
       </c>
       <c r="E179">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G179">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H179">
-        <v>1.077</v>
+        <v>1.061</v>
       </c>
       <c r="I179">
-        <v>4.502</v>
+        <v>3.311</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -5232,7 +5232,7 @@
         <v>20</v>
       </c>
       <c r="B180">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C180" t="s">
         <v>11</v>
@@ -5247,10 +5247,10 @@
         <v>0.003</v>
       </c>
       <c r="H180">
-        <v>1.075</v>
+        <v>1.1</v>
       </c>
       <c r="I180">
-        <v>3.578</v>
+        <v>5.091</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -5258,7 +5258,7 @@
         <v>20</v>
       </c>
       <c r="B181">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C181" t="s">
         <v>11</v>
@@ -5267,19 +5267,19 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F181">
-        <v>6.996730349272068</v>
+        <v>8.50062431642713</v>
       </c>
       <c r="G181">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H181">
-        <v>1.041</v>
+        <v>1.009</v>
       </c>
       <c r="I181">
-        <v>3.172</v>
+        <v>4.978</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -5287,7 +5287,7 @@
         <v>21</v>
       </c>
       <c r="B182">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C182" t="s">
         <v>9</v>
@@ -5296,16 +5296,16 @@
         <v>12</v>
       </c>
       <c r="E182">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G182">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H182">
-        <v>1.078</v>
+        <v>1.074</v>
       </c>
       <c r="I182">
-        <v>4.448</v>
+        <v>5.755</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -5313,7 +5313,7 @@
         <v>21</v>
       </c>
       <c r="B183">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C183" t="s">
         <v>9</v>
@@ -5325,13 +5325,13 @@
         <v>2</v>
       </c>
       <c r="G183">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H183">
-        <v>1.087</v>
+        <v>1.142</v>
       </c>
       <c r="I183">
-        <v>4.499</v>
+        <v>6.853</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -5339,7 +5339,7 @@
         <v>21</v>
       </c>
       <c r="B184">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C184" t="s">
         <v>9</v>
@@ -5348,19 +5348,19 @@
         <v>14</v>
       </c>
       <c r="E184">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F184">
-        <v>7.003316292484643</v>
+        <v>11.79094280391565</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H184">
-        <v>1.029</v>
+        <v>1.069</v>
       </c>
       <c r="I184">
-        <v>3.315</v>
+        <v>2.949</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -5368,7 +5368,7 @@
         <v>21</v>
       </c>
       <c r="B185">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C185" t="s">
         <v>10</v>
@@ -5377,16 +5377,16 @@
         <v>12</v>
       </c>
       <c r="E185">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G185">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H185">
-        <v>1.078</v>
+        <v>1.074</v>
       </c>
       <c r="I185">
-        <v>4.448</v>
+        <v>5.755</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -5394,7 +5394,7 @@
         <v>21</v>
       </c>
       <c r="B186">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C186" t="s">
         <v>10</v>
@@ -5406,13 +5406,13 @@
         <v>2</v>
       </c>
       <c r="G186">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H186">
-        <v>1.087</v>
+        <v>1.142</v>
       </c>
       <c r="I186">
-        <v>4.499</v>
+        <v>6.853</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -5420,7 +5420,7 @@
         <v>21</v>
       </c>
       <c r="B187">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C187" t="s">
         <v>10</v>
@@ -5429,19 +5429,19 @@
         <v>14</v>
       </c>
       <c r="E187">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F187">
-        <v>7.003316292484643</v>
+        <v>11.79094280391565</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H187">
-        <v>1.029</v>
+        <v>1.069</v>
       </c>
       <c r="I187">
-        <v>3.315</v>
+        <v>2.949</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -5449,7 +5449,7 @@
         <v>21</v>
       </c>
       <c r="B188">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C188" t="s">
         <v>11</v>
@@ -5458,16 +5458,16 @@
         <v>12</v>
       </c>
       <c r="E188">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G188">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H188">
-        <v>1.078</v>
+        <v>1.074</v>
       </c>
       <c r="I188">
-        <v>4.448</v>
+        <v>5.755</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -5475,7 +5475,7 @@
         <v>21</v>
       </c>
       <c r="B189">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
@@ -5487,13 +5487,13 @@
         <v>2</v>
       </c>
       <c r="G189">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H189">
-        <v>1.087</v>
+        <v>1.142</v>
       </c>
       <c r="I189">
-        <v>4.499</v>
+        <v>6.853</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -5501,7 +5501,7 @@
         <v>21</v>
       </c>
       <c r="B190">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="C190" t="s">
         <v>11</v>
@@ -5510,19 +5510,19 @@
         <v>14</v>
       </c>
       <c r="E190">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F190">
-        <v>7.003316292484643</v>
+        <v>11.79094280391565</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="H190">
-        <v>1.029</v>
+        <v>1.069</v>
       </c>
       <c r="I190">
-        <v>3.315</v>
+        <v>2.949</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -5530,7 +5530,7 @@
         <v>22</v>
       </c>
       <c r="B191">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C191" t="s">
         <v>9</v>
@@ -5542,13 +5542,13 @@
         <v>2</v>
       </c>
       <c r="G191">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H191">
-        <v>1.073</v>
+        <v>1.081</v>
       </c>
       <c r="I191">
-        <v>4.528</v>
+        <v>6.225</v>
       </c>
     </row>
     <row r="192" spans="1:9">
@@ -5556,7 +5556,7 @@
         <v>22</v>
       </c>
       <c r="B192">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C192" t="s">
         <v>9</v>
@@ -5568,13 +5568,13 @@
         <v>2</v>
       </c>
       <c r="G192">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H192">
-        <v>1.087</v>
+        <v>1.122</v>
       </c>
       <c r="I192">
-        <v>4.046</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -5582,7 +5582,7 @@
         <v>22</v>
       </c>
       <c r="B193">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C193" t="s">
         <v>9</v>
@@ -5591,19 +5591,19 @@
         <v>14</v>
       </c>
       <c r="E193">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F193">
-        <v>6.999980549062756</v>
+        <v>9.448579323164944</v>
       </c>
       <c r="G193">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H193">
-        <v>1.047</v>
+        <v>1.067</v>
       </c>
       <c r="I193">
-        <v>2.727</v>
+        <v>2.469</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -5611,7 +5611,7 @@
         <v>22</v>
       </c>
       <c r="B194">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C194" t="s">
         <v>10</v>
@@ -5623,13 +5623,13 @@
         <v>2</v>
       </c>
       <c r="G194">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H194">
-        <v>1.073</v>
+        <v>1.081</v>
       </c>
       <c r="I194">
-        <v>4.528</v>
+        <v>6.225</v>
       </c>
     </row>
     <row r="195" spans="1:9">
@@ -5637,7 +5637,7 @@
         <v>22</v>
       </c>
       <c r="B195">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C195" t="s">
         <v>10</v>
@@ -5649,13 +5649,13 @@
         <v>2</v>
       </c>
       <c r="G195">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H195">
-        <v>1.087</v>
+        <v>1.122</v>
       </c>
       <c r="I195">
-        <v>4.046</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -5663,7 +5663,7 @@
         <v>22</v>
       </c>
       <c r="B196">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C196" t="s">
         <v>10</v>
@@ -5672,19 +5672,19 @@
         <v>14</v>
       </c>
       <c r="E196">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F196">
-        <v>6.999980549062756</v>
+        <v>9.448579323164944</v>
       </c>
       <c r="G196">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H196">
-        <v>1.047</v>
+        <v>1.067</v>
       </c>
       <c r="I196">
-        <v>2.727</v>
+        <v>2.469</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -5692,7 +5692,7 @@
         <v>22</v>
       </c>
       <c r="B197">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C197" t="s">
         <v>11</v>
@@ -5704,13 +5704,13 @@
         <v>2</v>
       </c>
       <c r="G197">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H197">
-        <v>1.073</v>
+        <v>1.081</v>
       </c>
       <c r="I197">
-        <v>4.528</v>
+        <v>6.225</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -5718,7 +5718,7 @@
         <v>22</v>
       </c>
       <c r="B198">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C198" t="s">
         <v>11</v>
@@ -5730,13 +5730,13 @@
         <v>2</v>
       </c>
       <c r="G198">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H198">
-        <v>1.087</v>
+        <v>1.122</v>
       </c>
       <c r="I198">
-        <v>4.046</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -5744,7 +5744,7 @@
         <v>22</v>
       </c>
       <c r="B199">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C199" t="s">
         <v>11</v>
@@ -5753,19 +5753,19 @@
         <v>14</v>
       </c>
       <c r="E199">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F199">
-        <v>6.999980549062756</v>
+        <v>9.448579323164944</v>
       </c>
       <c r="G199">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="H199">
-        <v>1.047</v>
+        <v>1.067</v>
       </c>
       <c r="I199">
-        <v>2.727</v>
+        <v>2.469</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -5773,7 +5773,7 @@
         <v>23</v>
       </c>
       <c r="B200">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C200" t="s">
         <v>9</v>
@@ -5788,10 +5788,10 @@
         <v>0.002</v>
       </c>
       <c r="H200">
-        <v>1.055</v>
+        <v>1.084</v>
       </c>
       <c r="I200">
-        <v>4.408</v>
+        <v>5.423</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -5799,7 +5799,7 @@
         <v>23</v>
       </c>
       <c r="B201">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C201" t="s">
         <v>9</v>
@@ -5814,10 +5814,10 @@
         <v>0.003</v>
       </c>
       <c r="H201">
-        <v>1.077</v>
+        <v>1.115</v>
       </c>
       <c r="I201">
-        <v>4.235</v>
+        <v>5.316</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -5825,7 +5825,7 @@
         <v>23</v>
       </c>
       <c r="B202">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C202" t="s">
         <v>9</v>
@@ -5834,19 +5834,19 @@
         <v>14</v>
       </c>
       <c r="E202">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F202">
-        <v>7.001118545395987</v>
+        <v>8.26762639165878</v>
       </c>
       <c r="G202">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H202">
-        <v>1.027</v>
+        <v>1.031</v>
       </c>
       <c r="I202">
-        <v>2.85</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -5854,7 +5854,7 @@
         <v>23</v>
       </c>
       <c r="B203">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C203" t="s">
         <v>10</v>
@@ -5869,10 +5869,10 @@
         <v>0.002</v>
       </c>
       <c r="H203">
-        <v>1.055</v>
+        <v>1.084</v>
       </c>
       <c r="I203">
-        <v>4.408</v>
+        <v>5.423</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -5880,7 +5880,7 @@
         <v>23</v>
       </c>
       <c r="B204">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C204" t="s">
         <v>10</v>
@@ -5895,10 +5895,10 @@
         <v>0.003</v>
       </c>
       <c r="H204">
-        <v>1.077</v>
+        <v>1.115</v>
       </c>
       <c r="I204">
-        <v>4.235</v>
+        <v>5.316</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -5906,7 +5906,7 @@
         <v>23</v>
       </c>
       <c r="B205">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C205" t="s">
         <v>10</v>
@@ -5915,19 +5915,19 @@
         <v>14</v>
       </c>
       <c r="E205">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F205">
-        <v>7.001118545395987</v>
+        <v>8.26762639165878</v>
       </c>
       <c r="G205">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H205">
-        <v>1.027</v>
+        <v>1.031</v>
       </c>
       <c r="I205">
-        <v>2.85</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -5935,7 +5935,7 @@
         <v>23</v>
       </c>
       <c r="B206">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C206" t="s">
         <v>11</v>
@@ -5950,10 +5950,10 @@
         <v>0.002</v>
       </c>
       <c r="H206">
-        <v>1.055</v>
+        <v>1.084</v>
       </c>
       <c r="I206">
-        <v>4.408</v>
+        <v>5.423</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -5961,7 +5961,7 @@
         <v>23</v>
       </c>
       <c r="B207">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C207" t="s">
         <v>11</v>
@@ -5976,10 +5976,10 @@
         <v>0.003</v>
       </c>
       <c r="H207">
-        <v>1.077</v>
+        <v>1.115</v>
       </c>
       <c r="I207">
-        <v>4.235</v>
+        <v>5.316</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -5987,7 +5987,7 @@
         <v>23</v>
       </c>
       <c r="B208">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C208" t="s">
         <v>11</v>
@@ -5996,19 +5996,19 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F208">
-        <v>7.001118545395987</v>
+        <v>8.26762639165878</v>
       </c>
       <c r="G208">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H208">
-        <v>1.027</v>
+        <v>1.031</v>
       </c>
       <c r="I208">
-        <v>2.85</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -6016,7 +6016,7 @@
         <v>24</v>
       </c>
       <c r="B209">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C209" t="s">
         <v>9</v>
@@ -6025,16 +6025,16 @@
         <v>12</v>
       </c>
       <c r="E209">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G209">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H209">
-        <v>1.059</v>
+        <v>1.074</v>
       </c>
       <c r="I209">
-        <v>3.723</v>
+        <v>4.709</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -6042,7 +6042,7 @@
         <v>24</v>
       </c>
       <c r="B210">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C210" t="s">
         <v>9</v>
@@ -6054,13 +6054,13 @@
         <v>2</v>
       </c>
       <c r="G210">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H210">
-        <v>1.089</v>
+        <v>1.136</v>
       </c>
       <c r="I210">
-        <v>4.425</v>
+        <v>7.608</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -6068,7 +6068,7 @@
         <v>24</v>
       </c>
       <c r="B211">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C211" t="s">
         <v>9</v>
@@ -6077,19 +6077,19 @@
         <v>14</v>
       </c>
       <c r="E211">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F211">
-        <v>6.992521829916196</v>
+        <v>11.56216139309612</v>
       </c>
       <c r="G211">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="H211">
-        <v>1.044</v>
+        <v>1.053</v>
       </c>
       <c r="I211">
-        <v>3.168</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -6097,7 +6097,7 @@
         <v>24</v>
       </c>
       <c r="B212">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C212" t="s">
         <v>10</v>
@@ -6106,16 +6106,16 @@
         <v>12</v>
       </c>
       <c r="E212">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G212">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H212">
-        <v>1.059</v>
+        <v>1.074</v>
       </c>
       <c r="I212">
-        <v>3.723</v>
+        <v>4.709</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -6123,7 +6123,7 @@
         <v>24</v>
       </c>
       <c r="B213">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C213" t="s">
         <v>10</v>
@@ -6135,13 +6135,13 @@
         <v>2</v>
       </c>
       <c r="G213">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H213">
-        <v>1.089</v>
+        <v>1.136</v>
       </c>
       <c r="I213">
-        <v>4.425</v>
+        <v>7.608</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -6149,7 +6149,7 @@
         <v>24</v>
       </c>
       <c r="B214">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C214" t="s">
         <v>10</v>
@@ -6158,19 +6158,19 @@
         <v>14</v>
       </c>
       <c r="E214">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F214">
-        <v>6.992521829916196</v>
+        <v>11.56216139309612</v>
       </c>
       <c r="G214">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="H214">
-        <v>1.044</v>
+        <v>1.053</v>
       </c>
       <c r="I214">
-        <v>3.168</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -6178,7 +6178,7 @@
         <v>24</v>
       </c>
       <c r="B215">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C215" t="s">
         <v>11</v>
@@ -6187,16 +6187,16 @@
         <v>12</v>
       </c>
       <c r="E215">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G215">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H215">
-        <v>1.059</v>
+        <v>1.074</v>
       </c>
       <c r="I215">
-        <v>3.723</v>
+        <v>4.709</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -6204,7 +6204,7 @@
         <v>24</v>
       </c>
       <c r="B216">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C216" t="s">
         <v>11</v>
@@ -6216,13 +6216,13 @@
         <v>2</v>
       </c>
       <c r="G216">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H216">
-        <v>1.089</v>
+        <v>1.136</v>
       </c>
       <c r="I216">
-        <v>4.425</v>
+        <v>7.608</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -6230,7 +6230,7 @@
         <v>24</v>
       </c>
       <c r="B217">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C217" t="s">
         <v>11</v>
@@ -6239,19 +6239,19 @@
         <v>14</v>
       </c>
       <c r="E217">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F217">
-        <v>6.992521829916196</v>
+        <v>11.56216139309612</v>
       </c>
       <c r="G217">
-        <v>0.002</v>
+        <v>-0.002</v>
       </c>
       <c r="H217">
-        <v>1.044</v>
+        <v>1.053</v>
       </c>
       <c r="I217">
-        <v>3.168</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -6259,7 +6259,7 @@
         <v>25</v>
       </c>
       <c r="B218">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C218" t="s">
         <v>9</v>
@@ -6268,16 +6268,16 @@
         <v>12</v>
       </c>
       <c r="E218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G218">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H218">
-        <v>1.057</v>
+        <v>1.065</v>
       </c>
       <c r="I218">
-        <v>3.2</v>
+        <v>6.906</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -6285,7 +6285,7 @@
         <v>25</v>
       </c>
       <c r="B219">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C219" t="s">
         <v>9</v>
@@ -6297,13 +6297,13 @@
         <v>2</v>
       </c>
       <c r="G219">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H219">
-        <v>1.083</v>
+        <v>1.118</v>
       </c>
       <c r="I219">
-        <v>4.438</v>
+        <v>7.982</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -6311,7 +6311,7 @@
         <v>25</v>
       </c>
       <c r="B220">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C220" t="s">
         <v>9</v>
@@ -6320,19 +6320,19 @@
         <v>14</v>
       </c>
       <c r="E220">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F220">
-        <v>7.005046812630177</v>
+        <v>12.28814752963171</v>
       </c>
       <c r="G220">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H220">
-        <v>1.039</v>
+        <v>1.05</v>
       </c>
       <c r="I220">
-        <v>3.271</v>
+        <v>3.534</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -6340,7 +6340,7 @@
         <v>25</v>
       </c>
       <c r="B221">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C221" t="s">
         <v>10</v>
@@ -6349,16 +6349,16 @@
         <v>12</v>
       </c>
       <c r="E221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G221">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>1.057</v>
+        <v>1.065</v>
       </c>
       <c r="I221">
-        <v>3.2</v>
+        <v>6.906</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -6366,7 +6366,7 @@
         <v>25</v>
       </c>
       <c r="B222">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C222" t="s">
         <v>10</v>
@@ -6378,13 +6378,13 @@
         <v>2</v>
       </c>
       <c r="G222">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H222">
-        <v>1.083</v>
+        <v>1.118</v>
       </c>
       <c r="I222">
-        <v>4.438</v>
+        <v>7.982</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -6392,7 +6392,7 @@
         <v>25</v>
       </c>
       <c r="B223">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C223" t="s">
         <v>10</v>
@@ -6401,19 +6401,19 @@
         <v>14</v>
       </c>
       <c r="E223">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F223">
-        <v>7.005046812630177</v>
+        <v>12.28814752963171</v>
       </c>
       <c r="G223">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H223">
-        <v>1.039</v>
+        <v>1.05</v>
       </c>
       <c r="I223">
-        <v>3.271</v>
+        <v>3.534</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -6421,7 +6421,7 @@
         <v>25</v>
       </c>
       <c r="B224">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C224" t="s">
         <v>11</v>
@@ -6430,16 +6430,16 @@
         <v>12</v>
       </c>
       <c r="E224">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G224">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H224">
-        <v>1.057</v>
+        <v>1.065</v>
       </c>
       <c r="I224">
-        <v>3.2</v>
+        <v>6.906</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -6447,7 +6447,7 @@
         <v>25</v>
       </c>
       <c r="B225">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C225" t="s">
         <v>11</v>
@@ -6459,13 +6459,13 @@
         <v>2</v>
       </c>
       <c r="G225">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H225">
-        <v>1.083</v>
+        <v>1.118</v>
       </c>
       <c r="I225">
-        <v>4.438</v>
+        <v>7.982</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -6473,7 +6473,7 @@
         <v>25</v>
       </c>
       <c r="B226">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C226" t="s">
         <v>11</v>
@@ -6482,19 +6482,19 @@
         <v>14</v>
       </c>
       <c r="E226">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F226">
-        <v>7.005046812630177</v>
+        <v>12.28814752963171</v>
       </c>
       <c r="G226">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="H226">
-        <v>1.039</v>
+        <v>1.05</v>
       </c>
       <c r="I226">
-        <v>3.271</v>
+        <v>3.534</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -6502,7 +6502,7 @@
         <v>26</v>
       </c>
       <c r="B227">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C227" t="s">
         <v>9</v>
@@ -6514,13 +6514,13 @@
         <v>2</v>
       </c>
       <c r="G227">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H227">
-        <v>1.079</v>
+        <v>1.09</v>
       </c>
       <c r="I227">
-        <v>4.499</v>
+        <v>9.531000000000001</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -6528,7 +6528,7 @@
         <v>26</v>
       </c>
       <c r="B228">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C228" t="s">
         <v>9</v>
@@ -6540,13 +6540,13 @@
         <v>2</v>
       </c>
       <c r="G228">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H228">
-        <v>1.105</v>
+        <v>1.141</v>
       </c>
       <c r="I228">
-        <v>4.305</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -6554,7 +6554,7 @@
         <v>26</v>
       </c>
       <c r="B229">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C229" t="s">
         <v>9</v>
@@ -6563,19 +6563,19 @@
         <v>14</v>
       </c>
       <c r="E229">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F229">
-        <v>6.992210810380367</v>
+        <v>14.03932446499019</v>
       </c>
       <c r="G229">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="H229">
-        <v>1.049</v>
+        <v>1.046</v>
       </c>
       <c r="I229">
-        <v>2.603</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -6583,7 +6583,7 @@
         <v>26</v>
       </c>
       <c r="B230">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C230" t="s">
         <v>10</v>
@@ -6595,13 +6595,13 @@
         <v>2</v>
       </c>
       <c r="G230">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H230">
-        <v>1.079</v>
+        <v>1.09</v>
       </c>
       <c r="I230">
-        <v>4.499</v>
+        <v>9.531000000000001</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -6609,7 +6609,7 @@
         <v>26</v>
       </c>
       <c r="B231">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C231" t="s">
         <v>10</v>
@@ -6621,13 +6621,13 @@
         <v>2</v>
       </c>
       <c r="G231">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H231">
-        <v>1.105</v>
+        <v>1.141</v>
       </c>
       <c r="I231">
-        <v>4.305</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -6635,7 +6635,7 @@
         <v>26</v>
       </c>
       <c r="B232">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C232" t="s">
         <v>10</v>
@@ -6644,19 +6644,19 @@
         <v>14</v>
       </c>
       <c r="E232">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F232">
-        <v>6.992210810380367</v>
+        <v>14.03932446499019</v>
       </c>
       <c r="G232">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="H232">
-        <v>1.049</v>
+        <v>1.046</v>
       </c>
       <c r="I232">
-        <v>2.603</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -6664,7 +6664,7 @@
         <v>26</v>
       </c>
       <c r="B233">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C233" t="s">
         <v>11</v>
@@ -6676,13 +6676,13 @@
         <v>2</v>
       </c>
       <c r="G233">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H233">
-        <v>1.079</v>
+        <v>1.09</v>
       </c>
       <c r="I233">
-        <v>4.499</v>
+        <v>9.531000000000001</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -6690,7 +6690,7 @@
         <v>26</v>
       </c>
       <c r="B234">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C234" t="s">
         <v>11</v>
@@ -6702,13 +6702,13 @@
         <v>2</v>
       </c>
       <c r="G234">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H234">
-        <v>1.105</v>
+        <v>1.141</v>
       </c>
       <c r="I234">
-        <v>4.305</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -6716,7 +6716,7 @@
         <v>26</v>
       </c>
       <c r="B235">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="C235" t="s">
         <v>11</v>
@@ -6725,19 +6725,19 @@
         <v>14</v>
       </c>
       <c r="E235">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F235">
-        <v>6.992210810380367</v>
+        <v>14.03932446499019</v>
       </c>
       <c r="G235">
-        <v>0.003</v>
+        <v>-0.003</v>
       </c>
       <c r="H235">
-        <v>1.049</v>
+        <v>1.046</v>
       </c>
       <c r="I235">
-        <v>2.603</v>
+        <v>3.754</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -6745,7 +6745,7 @@
         <v>27</v>
       </c>
       <c r="B236">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C236" t="s">
         <v>9</v>
@@ -6757,13 +6757,13 @@
         <v>2</v>
       </c>
       <c r="G236">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H236">
-        <v>1.067</v>
+        <v>1.079</v>
       </c>
       <c r="I236">
-        <v>4.524</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -6771,7 +6771,7 @@
         <v>27</v>
       </c>
       <c r="B237">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C237" t="s">
         <v>9</v>
@@ -6780,16 +6780,16 @@
         <v>13</v>
       </c>
       <c r="E237">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G237">
         <v>0.003</v>
       </c>
       <c r="H237">
-        <v>1.078</v>
+        <v>1.104</v>
       </c>
       <c r="I237">
-        <v>4.233</v>
+        <v>5.233</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -6797,7 +6797,7 @@
         <v>27</v>
       </c>
       <c r="B238">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C238" t="s">
         <v>9</v>
@@ -6806,19 +6806,19 @@
         <v>14</v>
       </c>
       <c r="E238">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F238">
-        <v>6.996226848417051</v>
+        <v>9.557547689441687</v>
       </c>
       <c r="G238">
-        <v>0.006</v>
+        <v>-0</v>
       </c>
       <c r="H238">
-        <v>1.055</v>
+        <v>1.048</v>
       </c>
       <c r="I238">
-        <v>2.199</v>
+        <v>3.328</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -6826,7 +6826,7 @@
         <v>27</v>
       </c>
       <c r="B239">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C239" t="s">
         <v>10</v>
@@ -6838,13 +6838,13 @@
         <v>2</v>
       </c>
       <c r="G239">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H239">
-        <v>1.067</v>
+        <v>1.079</v>
       </c>
       <c r="I239">
-        <v>4.524</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -6852,7 +6852,7 @@
         <v>27</v>
       </c>
       <c r="B240">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C240" t="s">
         <v>10</v>
@@ -6861,16 +6861,16 @@
         <v>13</v>
       </c>
       <c r="E240">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G240">
         <v>0.003</v>
       </c>
       <c r="H240">
-        <v>1.078</v>
+        <v>1.104</v>
       </c>
       <c r="I240">
-        <v>4.233</v>
+        <v>5.233</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -6878,7 +6878,7 @@
         <v>27</v>
       </c>
       <c r="B241">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C241" t="s">
         <v>10</v>
@@ -6887,19 +6887,19 @@
         <v>14</v>
       </c>
       <c r="E241">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F241">
-        <v>6.996226848417051</v>
+        <v>9.557547689441687</v>
       </c>
       <c r="G241">
-        <v>0.006</v>
+        <v>-0</v>
       </c>
       <c r="H241">
-        <v>1.055</v>
+        <v>1.048</v>
       </c>
       <c r="I241">
-        <v>2.199</v>
+        <v>3.328</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -6907,7 +6907,7 @@
         <v>27</v>
       </c>
       <c r="B242">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C242" t="s">
         <v>11</v>
@@ -6919,13 +6919,13 @@
         <v>2</v>
       </c>
       <c r="G242">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H242">
-        <v>1.067</v>
+        <v>1.079</v>
       </c>
       <c r="I242">
-        <v>4.524</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -6933,7 +6933,7 @@
         <v>27</v>
       </c>
       <c r="B243">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C243" t="s">
         <v>11</v>
@@ -6942,16 +6942,16 @@
         <v>13</v>
       </c>
       <c r="E243">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G243">
         <v>0.003</v>
       </c>
       <c r="H243">
-        <v>1.078</v>
+        <v>1.104</v>
       </c>
       <c r="I243">
-        <v>4.233</v>
+        <v>5.233</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -6959,7 +6959,7 @@
         <v>27</v>
       </c>
       <c r="B244">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C244" t="s">
         <v>11</v>
@@ -6968,19 +6968,19 @@
         <v>14</v>
       </c>
       <c r="E244">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F244">
-        <v>6.996226848417051</v>
+        <v>9.557547689441687</v>
       </c>
       <c r="G244">
-        <v>0.006</v>
+        <v>-0</v>
       </c>
       <c r="H244">
-        <v>1.055</v>
+        <v>1.048</v>
       </c>
       <c r="I244">
-        <v>2.199</v>
+        <v>3.328</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -6988,7 +6988,7 @@
         <v>28</v>
       </c>
       <c r="B245">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C245" t="s">
         <v>9</v>
@@ -6997,16 +6997,16 @@
         <v>12</v>
       </c>
       <c r="E245">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G245">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H245">
-        <v>1.062</v>
+        <v>1.058</v>
       </c>
       <c r="I245">
-        <v>4.534</v>
+        <v>2.487</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -7014,7 +7014,7 @@
         <v>28</v>
       </c>
       <c r="B246">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C246" t="s">
         <v>9</v>
@@ -7026,13 +7026,13 @@
         <v>2</v>
       </c>
       <c r="G246">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H246">
-        <v>1.089</v>
+        <v>1.083</v>
       </c>
       <c r="I246">
-        <v>4.478</v>
+        <v>3.619</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -7040,7 +7040,7 @@
         <v>28</v>
       </c>
       <c r="B247">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C247" t="s">
         <v>9</v>
@@ -7049,19 +7049,19 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F247">
-        <v>6.997423232487722</v>
+        <v>7.4040992227928</v>
       </c>
       <c r="G247">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H247">
-        <v>1.049</v>
+        <v>1.042</v>
       </c>
       <c r="I247">
-        <v>2.398</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -7069,7 +7069,7 @@
         <v>28</v>
       </c>
       <c r="B248">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C248" t="s">
         <v>10</v>
@@ -7078,16 +7078,16 @@
         <v>12</v>
       </c>
       <c r="E248">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G248">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H248">
-        <v>1.062</v>
+        <v>1.058</v>
       </c>
       <c r="I248">
-        <v>4.534</v>
+        <v>2.487</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -7095,7 +7095,7 @@
         <v>28</v>
       </c>
       <c r="B249">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C249" t="s">
         <v>10</v>
@@ -7107,13 +7107,13 @@
         <v>2</v>
       </c>
       <c r="G249">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H249">
-        <v>1.089</v>
+        <v>1.083</v>
       </c>
       <c r="I249">
-        <v>4.478</v>
+        <v>3.619</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -7121,7 +7121,7 @@
         <v>28</v>
       </c>
       <c r="B250">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C250" t="s">
         <v>10</v>
@@ -7130,19 +7130,19 @@
         <v>14</v>
       </c>
       <c r="E250">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F250">
-        <v>6.997423232487722</v>
+        <v>7.4040992227928</v>
       </c>
       <c r="G250">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H250">
-        <v>1.049</v>
+        <v>1.042</v>
       </c>
       <c r="I250">
-        <v>2.398</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -7150,7 +7150,7 @@
         <v>28</v>
       </c>
       <c r="B251">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C251" t="s">
         <v>11</v>
@@ -7159,16 +7159,16 @@
         <v>12</v>
       </c>
       <c r="E251">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G251">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H251">
-        <v>1.062</v>
+        <v>1.058</v>
       </c>
       <c r="I251">
-        <v>4.534</v>
+        <v>2.487</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -7176,7 +7176,7 @@
         <v>28</v>
       </c>
       <c r="B252">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C252" t="s">
         <v>11</v>
@@ -7188,13 +7188,13 @@
         <v>2</v>
       </c>
       <c r="G252">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H252">
-        <v>1.089</v>
+        <v>1.083</v>
       </c>
       <c r="I252">
-        <v>4.478</v>
+        <v>3.619</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -7202,7 +7202,7 @@
         <v>28</v>
       </c>
       <c r="B253">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C253" t="s">
         <v>11</v>
@@ -7211,19 +7211,19 @@
         <v>14</v>
       </c>
       <c r="E253">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F253">
-        <v>6.997423232487722</v>
+        <v>7.4040992227928</v>
       </c>
       <c r="G253">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H253">
-        <v>1.049</v>
+        <v>1.042</v>
       </c>
       <c r="I253">
-        <v>2.398</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -7231,7 +7231,7 @@
         <v>29</v>
       </c>
       <c r="B254">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C254" t="s">
         <v>9</v>
@@ -7240,16 +7240,16 @@
         <v>12</v>
       </c>
       <c r="E254">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G254">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H254">
-        <v>1.083</v>
+        <v>1.081</v>
       </c>
       <c r="I254">
-        <v>4.349</v>
+        <v>7.585</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -7257,7 +7257,7 @@
         <v>29</v>
       </c>
       <c r="B255">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C255" t="s">
         <v>9</v>
@@ -7269,13 +7269,13 @@
         <v>2</v>
       </c>
       <c r="G255">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H255">
-        <v>1.093</v>
+        <v>1.16</v>
       </c>
       <c r="I255">
-        <v>4.034</v>
+        <v>8.666</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -7283,7 +7283,7 @@
         <v>29</v>
       </c>
       <c r="B256">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C256" t="s">
         <v>9</v>
@@ -7292,19 +7292,19 @@
         <v>14</v>
       </c>
       <c r="E256">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F256">
-        <v>6.9859771636255</v>
+        <v>13.46653697458217</v>
       </c>
       <c r="G256">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H256">
-        <v>1.047</v>
+        <v>1.067</v>
       </c>
       <c r="I256">
-        <v>3.054</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -7312,7 +7312,7 @@
         <v>29</v>
       </c>
       <c r="B257">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C257" t="s">
         <v>10</v>
@@ -7321,16 +7321,16 @@
         <v>12</v>
       </c>
       <c r="E257">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G257">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H257">
-        <v>1.083</v>
+        <v>1.081</v>
       </c>
       <c r="I257">
-        <v>4.349</v>
+        <v>7.585</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -7338,7 +7338,7 @@
         <v>29</v>
       </c>
       <c r="B258">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C258" t="s">
         <v>10</v>
@@ -7350,13 +7350,13 @@
         <v>2</v>
       </c>
       <c r="G258">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H258">
-        <v>1.093</v>
+        <v>1.16</v>
       </c>
       <c r="I258">
-        <v>4.034</v>
+        <v>8.666</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -7364,7 +7364,7 @@
         <v>29</v>
       </c>
       <c r="B259">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C259" t="s">
         <v>10</v>
@@ -7373,19 +7373,19 @@
         <v>14</v>
       </c>
       <c r="E259">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F259">
-        <v>6.9859771636255</v>
+        <v>13.46653697458217</v>
       </c>
       <c r="G259">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H259">
-        <v>1.047</v>
+        <v>1.067</v>
       </c>
       <c r="I259">
-        <v>3.054</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -7393,7 +7393,7 @@
         <v>29</v>
       </c>
       <c r="B260">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C260" t="s">
         <v>11</v>
@@ -7402,16 +7402,16 @@
         <v>12</v>
       </c>
       <c r="E260">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G260">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H260">
-        <v>1.083</v>
+        <v>1.081</v>
       </c>
       <c r="I260">
-        <v>4.349</v>
+        <v>7.585</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -7419,7 +7419,7 @@
         <v>29</v>
       </c>
       <c r="B261">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C261" t="s">
         <v>11</v>
@@ -7431,13 +7431,13 @@
         <v>2</v>
       </c>
       <c r="G261">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H261">
-        <v>1.093</v>
+        <v>1.16</v>
       </c>
       <c r="I261">
-        <v>4.034</v>
+        <v>8.666</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -7445,7 +7445,7 @@
         <v>29</v>
       </c>
       <c r="B262">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="C262" t="s">
         <v>11</v>
@@ -7454,19 +7454,19 @@
         <v>14</v>
       </c>
       <c r="E262">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F262">
-        <v>6.9859771636255</v>
+        <v>13.46653697458217</v>
       </c>
       <c r="G262">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="H262">
-        <v>1.047</v>
+        <v>1.067</v>
       </c>
       <c r="I262">
-        <v>3.054</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -7474,7 +7474,7 @@
         <v>30</v>
       </c>
       <c r="B263">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C263" t="s">
         <v>9</v>
@@ -7483,16 +7483,16 @@
         <v>12</v>
       </c>
       <c r="E263">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G263">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H263">
-        <v>1.069</v>
+        <v>1.099</v>
       </c>
       <c r="I263">
-        <v>3.163</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -7500,7 +7500,7 @@
         <v>30</v>
       </c>
       <c r="B264">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C264" t="s">
         <v>9</v>
@@ -7512,13 +7512,13 @@
         <v>2</v>
       </c>
       <c r="G264">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H264">
-        <v>1.081</v>
+        <v>1.144</v>
       </c>
       <c r="I264">
-        <v>2.778</v>
+        <v>7.061</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -7526,7 +7526,7 @@
         <v>30</v>
       </c>
       <c r="B265">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C265" t="s">
         <v>9</v>
@@ -7535,19 +7535,19 @@
         <v>14</v>
       </c>
       <c r="E265">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F265">
-        <v>6.996184992895925</v>
+        <v>11.47407353110164</v>
       </c>
       <c r="G265">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H265">
-        <v>1.06</v>
+        <v>1.071</v>
       </c>
       <c r="I265">
-        <v>2.856</v>
+        <v>3.189</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -7555,7 +7555,7 @@
         <v>30</v>
       </c>
       <c r="B266">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C266" t="s">
         <v>10</v>
@@ -7564,16 +7564,16 @@
         <v>12</v>
       </c>
       <c r="E266">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G266">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H266">
-        <v>1.069</v>
+        <v>1.099</v>
       </c>
       <c r="I266">
-        <v>3.163</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -7581,7 +7581,7 @@
         <v>30</v>
       </c>
       <c r="B267">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C267" t="s">
         <v>10</v>
@@ -7593,13 +7593,13 @@
         <v>2</v>
       </c>
       <c r="G267">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H267">
-        <v>1.081</v>
+        <v>1.144</v>
       </c>
       <c r="I267">
-        <v>2.778</v>
+        <v>7.061</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -7607,7 +7607,7 @@
         <v>30</v>
       </c>
       <c r="B268">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C268" t="s">
         <v>10</v>
@@ -7616,19 +7616,19 @@
         <v>14</v>
       </c>
       <c r="E268">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F268">
-        <v>6.996184992895925</v>
+        <v>11.47407353110164</v>
       </c>
       <c r="G268">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H268">
-        <v>1.06</v>
+        <v>1.071</v>
       </c>
       <c r="I268">
-        <v>2.856</v>
+        <v>3.189</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -7636,7 +7636,7 @@
         <v>30</v>
       </c>
       <c r="B269">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C269" t="s">
         <v>11</v>
@@ -7645,16 +7645,16 @@
         <v>12</v>
       </c>
       <c r="E269">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G269">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H269">
-        <v>1.069</v>
+        <v>1.099</v>
       </c>
       <c r="I269">
-        <v>3.163</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -7662,7 +7662,7 @@
         <v>30</v>
       </c>
       <c r="B270">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C270" t="s">
         <v>11</v>
@@ -7674,13 +7674,13 @@
         <v>2</v>
       </c>
       <c r="G270">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H270">
-        <v>1.081</v>
+        <v>1.144</v>
       </c>
       <c r="I270">
-        <v>2.778</v>
+        <v>7.061</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -7688,7 +7688,7 @@
         <v>30</v>
       </c>
       <c r="B271">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C271" t="s">
         <v>11</v>
@@ -7697,19 +7697,19 @@
         <v>14</v>
       </c>
       <c r="E271">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F271">
-        <v>6.996184992895925</v>
+        <v>11.47407353110164</v>
       </c>
       <c r="G271">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H271">
-        <v>1.06</v>
+        <v>1.071</v>
       </c>
       <c r="I271">
-        <v>2.856</v>
+        <v>3.189</v>
       </c>
     </row>
   </sheetData>

--- a/output/resultado_resumen_final.xlsx
+++ b/output/resultado_resumen_final.xlsx
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -436,16 +436,16 @@
         <v>12</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H2">
-        <v>1.08</v>
+        <v>1.065</v>
       </c>
       <c r="I2">
-        <v>3.892</v>
+        <v>4.816</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -462,16 +462,16 @@
         <v>13</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>0.004</v>
       </c>
       <c r="H3">
-        <v>1.087</v>
+        <v>1.096</v>
       </c>
       <c r="I3">
-        <v>3.782</v>
+        <v>4.157</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -479,7 +479,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -488,19 +488,19 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>7.24705987828718</v>
+        <v>1.3771</v>
       </c>
       <c r="G4">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="H4">
-        <v>1.05</v>
+        <v>1.087</v>
       </c>
       <c r="I4">
-        <v>2.239</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -508,7 +508,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -517,16 +517,16 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H5">
-        <v>1.08</v>
+        <v>1.065</v>
       </c>
       <c r="I5">
-        <v>3.892</v>
+        <v>4.816</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -534,7 +534,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -543,16 +543,16 @@
         <v>13</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>0.004</v>
       </c>
       <c r="H6">
-        <v>1.087</v>
+        <v>1.096</v>
       </c>
       <c r="I6">
-        <v>3.782</v>
+        <v>4.157</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -569,19 +569,19 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>7.24705987828718</v>
+        <v>1.3771</v>
       </c>
       <c r="G7">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="H7">
-        <v>1.05</v>
+        <v>1.087</v>
       </c>
       <c r="I7">
-        <v>2.239</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -598,16 +598,16 @@
         <v>12</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="H8">
-        <v>1.08</v>
+        <v>1.065</v>
       </c>
       <c r="I8">
-        <v>3.892</v>
+        <v>4.816</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -624,16 +624,16 @@
         <v>13</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>0.004</v>
       </c>
       <c r="H9">
-        <v>1.087</v>
+        <v>1.096</v>
       </c>
       <c r="I9">
-        <v>3.782</v>
+        <v>4.157</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -650,19 +650,19 @@
         <v>14</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>7.24705987828718</v>
+        <v>1.3771</v>
       </c>
       <c r="G10">
-        <v>0.003</v>
+        <v>0.014</v>
       </c>
       <c r="H10">
-        <v>1.05</v>
+        <v>1.087</v>
       </c>
       <c r="I10">
-        <v>2.239</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -670,7 +670,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -679,16 +679,16 @@
         <v>12</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11">
         <v>0.002</v>
       </c>
       <c r="H11">
-        <v>1.075</v>
+        <v>1.08</v>
       </c>
       <c r="I11">
-        <v>4.279</v>
+        <v>4.872</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -708,13 +708,13 @@
         <v>2</v>
       </c>
       <c r="G12">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H12">
-        <v>1.124</v>
+        <v>1.119</v>
       </c>
       <c r="I12">
-        <v>5.337</v>
+        <v>5.699</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
       <c r="B13">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -731,19 +731,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>9.851477532794901</v>
+        <v>1.3746</v>
       </c>
       <c r="G13">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H13">
-        <v>1.045</v>
+        <v>1.077</v>
       </c>
       <c r="I13">
-        <v>3.229</v>
+        <v>2.441</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B14">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -760,16 +760,16 @@
         <v>12</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>0.002</v>
       </c>
       <c r="H14">
-        <v>1.075</v>
+        <v>1.08</v>
       </c>
       <c r="I14">
-        <v>4.279</v>
+        <v>4.872</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -777,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="B15">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -789,13 +789,13 @@
         <v>2</v>
       </c>
       <c r="G15">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H15">
-        <v>1.124</v>
+        <v>1.119</v>
       </c>
       <c r="I15">
-        <v>5.337</v>
+        <v>5.699</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -803,7 +803,7 @@
         <v>2</v>
       </c>
       <c r="B16">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -812,19 +812,19 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>9.851477532794901</v>
+        <v>1.3746</v>
       </c>
       <c r="G16">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H16">
-        <v>1.045</v>
+        <v>1.077</v>
       </c>
       <c r="I16">
-        <v>3.229</v>
+        <v>2.441</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="B17">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -841,16 +841,16 @@
         <v>12</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G17">
         <v>0.002</v>
       </c>
       <c r="H17">
-        <v>1.075</v>
+        <v>1.08</v>
       </c>
       <c r="I17">
-        <v>4.279</v>
+        <v>4.872</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -858,7 +858,7 @@
         <v>2</v>
       </c>
       <c r="B18">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -870,13 +870,13 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H18">
-        <v>1.124</v>
+        <v>1.119</v>
       </c>
       <c r="I18">
-        <v>5.337</v>
+        <v>5.699</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -884,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="B19">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -893,19 +893,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>9.851477532794901</v>
+        <v>1.3746</v>
       </c>
       <c r="G19">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H19">
-        <v>1.045</v>
+        <v>1.077</v>
       </c>
       <c r="I19">
-        <v>3.229</v>
+        <v>2.441</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="B20">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
@@ -922,16 +922,16 @@
         <v>12</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G20">
         <v>0.001</v>
       </c>
       <c r="H20">
-        <v>1.115</v>
+        <v>1.064</v>
       </c>
       <c r="I20">
-        <v>9.792</v>
+        <v>3.941</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -939,7 +939,7 @@
         <v>3</v>
       </c>
       <c r="B21">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
@@ -954,10 +954,10 @@
         <v>0.002</v>
       </c>
       <c r="H21">
-        <v>1.165</v>
+        <v>1.116</v>
       </c>
       <c r="I21">
-        <v>8.244</v>
+        <v>6.798</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -965,7 +965,7 @@
         <v>3</v>
       </c>
       <c r="B22">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -974,19 +974,19 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>14.57762604402895</v>
+        <v>1.3711</v>
       </c>
       <c r="G22">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H22">
-        <v>1.057</v>
+        <v>1.11</v>
       </c>
       <c r="I22">
-        <v>3.758</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -994,7 +994,7 @@
         <v>3</v>
       </c>
       <c r="B23">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -1003,16 +1003,16 @@
         <v>12</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G23">
         <v>0.001</v>
       </c>
       <c r="H23">
-        <v>1.115</v>
+        <v>1.064</v>
       </c>
       <c r="I23">
-        <v>9.792</v>
+        <v>3.941</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1020,7 +1020,7 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -1035,10 +1035,10 @@
         <v>0.002</v>
       </c>
       <c r="H24">
-        <v>1.165</v>
+        <v>1.116</v>
       </c>
       <c r="I24">
-        <v>8.244</v>
+        <v>6.798</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1046,7 +1046,7 @@
         <v>3</v>
       </c>
       <c r="B25">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -1055,19 +1055,19 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>14.57762604402895</v>
+        <v>1.3711</v>
       </c>
       <c r="G25">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H25">
-        <v>1.057</v>
+        <v>1.11</v>
       </c>
       <c r="I25">
-        <v>3.758</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1075,7 +1075,7 @@
         <v>3</v>
       </c>
       <c r="B26">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1084,16 +1084,16 @@
         <v>12</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G26">
         <v>0.001</v>
       </c>
       <c r="H26">
-        <v>1.115</v>
+        <v>1.064</v>
       </c>
       <c r="I26">
-        <v>9.792</v>
+        <v>3.941</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1101,7 +1101,7 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1116,10 +1116,10 @@
         <v>0.002</v>
       </c>
       <c r="H27">
-        <v>1.165</v>
+        <v>1.116</v>
       </c>
       <c r="I27">
-        <v>8.244</v>
+        <v>6.798</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1127,7 +1127,7 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1136,19 +1136,19 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>14.57762604402895</v>
+        <v>1.3711</v>
       </c>
       <c r="G28">
-        <v>-0.002</v>
+        <v>0.008</v>
       </c>
       <c r="H28">
-        <v>1.057</v>
+        <v>1.11</v>
       </c>
       <c r="I28">
-        <v>3.758</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1156,7 +1156,7 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1165,16 +1165,16 @@
         <v>12</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29">
         <v>0.001</v>
       </c>
       <c r="H29">
-        <v>1.082</v>
+        <v>1.088</v>
       </c>
       <c r="I29">
-        <v>7.886</v>
+        <v>6.308</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1182,7 +1182,7 @@
         <v>4</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1197,10 +1197,10 @@
         <v>0.002</v>
       </c>
       <c r="H30">
-        <v>1.154</v>
+        <v>1.159</v>
       </c>
       <c r="I30">
-        <v>9.166</v>
+        <v>8.253</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1217,19 +1217,19 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>13.97165487492945</v>
+        <v>1.3704</v>
       </c>
       <c r="G31">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H31">
-        <v>1.045</v>
+        <v>1.077</v>
       </c>
       <c r="I31">
-        <v>3.735</v>
+        <v>2.742</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1237,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
@@ -1246,16 +1246,16 @@
         <v>12</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32">
         <v>0.001</v>
       </c>
       <c r="H32">
-        <v>1.082</v>
+        <v>1.088</v>
       </c>
       <c r="I32">
-        <v>7.886</v>
+        <v>6.308</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1263,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="B33">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
@@ -1278,10 +1278,10 @@
         <v>0.002</v>
       </c>
       <c r="H33">
-        <v>1.154</v>
+        <v>1.159</v>
       </c>
       <c r="I33">
-        <v>9.166</v>
+        <v>8.253</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1289,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="B34">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -1298,19 +1298,19 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F34">
-        <v>13.97165487492945</v>
+        <v>1.3704</v>
       </c>
       <c r="G34">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H34">
-        <v>1.045</v>
+        <v>1.077</v>
       </c>
       <c r="I34">
-        <v>3.735</v>
+        <v>2.742</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1318,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -1327,16 +1327,16 @@
         <v>12</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35">
         <v>0.001</v>
       </c>
       <c r="H35">
-        <v>1.082</v>
+        <v>1.088</v>
       </c>
       <c r="I35">
-        <v>7.886</v>
+        <v>6.308</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1344,7 +1344,7 @@
         <v>4</v>
       </c>
       <c r="B36">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
@@ -1359,10 +1359,10 @@
         <v>0.002</v>
       </c>
       <c r="H36">
-        <v>1.154</v>
+        <v>1.159</v>
       </c>
       <c r="I36">
-        <v>9.166</v>
+        <v>8.253</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1370,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -1379,19 +1379,19 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F37">
-        <v>13.97165487492945</v>
+        <v>1.3704</v>
       </c>
       <c r="G37">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H37">
-        <v>1.045</v>
+        <v>1.077</v>
       </c>
       <c r="I37">
-        <v>3.735</v>
+        <v>2.742</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1399,7 +1399,7 @@
         <v>5</v>
       </c>
       <c r="B38">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
@@ -1408,16 +1408,16 @@
         <v>12</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G38">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H38">
-        <v>1.081</v>
+        <v>1.077</v>
       </c>
       <c r="I38">
-        <v>5.524</v>
+        <v>4.774</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="B39">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
@@ -1440,10 +1440,10 @@
         <v>0.002</v>
       </c>
       <c r="H39">
-        <v>1.085</v>
+        <v>1.143</v>
       </c>
       <c r="I39">
-        <v>5.316</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1451,7 +1451,7 @@
         <v>5</v>
       </c>
       <c r="B40">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
@@ -1460,19 +1460,19 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F40">
-        <v>8.380744769816141</v>
+        <v>1.3715</v>
       </c>
       <c r="G40">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="H40">
-        <v>1.037</v>
+        <v>1.09</v>
       </c>
       <c r="I40">
-        <v>3.861</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1480,7 +1480,7 @@
         <v>5</v>
       </c>
       <c r="B41">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C41" t="s">
         <v>10</v>
@@ -1489,16 +1489,16 @@
         <v>12</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G41">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H41">
-        <v>1.081</v>
+        <v>1.077</v>
       </c>
       <c r="I41">
-        <v>5.524</v>
+        <v>4.774</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1506,7 +1506,7 @@
         <v>5</v>
       </c>
       <c r="B42">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
@@ -1521,10 +1521,10 @@
         <v>0.002</v>
       </c>
       <c r="H42">
-        <v>1.085</v>
+        <v>1.143</v>
       </c>
       <c r="I42">
-        <v>5.316</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1532,7 +1532,7 @@
         <v>5</v>
       </c>
       <c r="B43">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
@@ -1541,19 +1541,19 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>8.380744769816141</v>
+        <v>1.3715</v>
       </c>
       <c r="G43">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="H43">
-        <v>1.037</v>
+        <v>1.09</v>
       </c>
       <c r="I43">
-        <v>3.861</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1561,7 +1561,7 @@
         <v>5</v>
       </c>
       <c r="B44">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C44" t="s">
         <v>11</v>
@@ -1570,16 +1570,16 @@
         <v>12</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G44">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H44">
-        <v>1.081</v>
+        <v>1.077</v>
       </c>
       <c r="I44">
-        <v>5.524</v>
+        <v>4.774</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1587,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="B45">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C45" t="s">
         <v>11</v>
@@ -1602,10 +1602,10 @@
         <v>0.002</v>
       </c>
       <c r="H45">
-        <v>1.085</v>
+        <v>1.143</v>
       </c>
       <c r="I45">
-        <v>5.316</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -1613,7 +1613,7 @@
         <v>5</v>
       </c>
       <c r="B46">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C46" t="s">
         <v>11</v>
@@ -1622,19 +1622,19 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F46">
-        <v>8.380744769816141</v>
+        <v>1.3715</v>
       </c>
       <c r="G46">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="H46">
-        <v>1.037</v>
+        <v>1.09</v>
       </c>
       <c r="I46">
-        <v>3.861</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -1642,7 +1642,7 @@
         <v>6</v>
       </c>
       <c r="B47">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
@@ -1657,10 +1657,10 @@
         <v>0.001</v>
       </c>
       <c r="H47">
-        <v>1.111</v>
+        <v>1.077</v>
       </c>
       <c r="I47">
-        <v>9.715999999999999</v>
+        <v>7.823</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -1668,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="B48">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
@@ -1683,10 +1683,10 @@
         <v>0.002</v>
       </c>
       <c r="H48">
-        <v>1.173</v>
+        <v>1.145</v>
       </c>
       <c r="I48">
-        <v>9.194000000000001</v>
+        <v>7.563</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -1694,7 +1694,7 @@
         <v>6</v>
       </c>
       <c r="B49">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
@@ -1703,19 +1703,19 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>14.4181549479407</v>
+        <v>1.3713</v>
       </c>
       <c r="G49">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H49">
-        <v>1.06</v>
+        <v>1.085</v>
       </c>
       <c r="I49">
-        <v>3.274</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -1723,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="B50">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
         <v>10</v>
@@ -1738,10 +1738,10 @@
         <v>0.001</v>
       </c>
       <c r="H50">
-        <v>1.111</v>
+        <v>1.077</v>
       </c>
       <c r="I50">
-        <v>9.715999999999999</v>
+        <v>7.823</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -1749,7 +1749,7 @@
         <v>6</v>
       </c>
       <c r="B51">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -1764,10 +1764,10 @@
         <v>0.002</v>
       </c>
       <c r="H51">
-        <v>1.173</v>
+        <v>1.145</v>
       </c>
       <c r="I51">
-        <v>9.194000000000001</v>
+        <v>7.563</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -1775,7 +1775,7 @@
         <v>6</v>
       </c>
       <c r="B52">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C52" t="s">
         <v>10</v>
@@ -1784,19 +1784,19 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>14.4181549479407</v>
+        <v>1.3713</v>
       </c>
       <c r="G52">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H52">
-        <v>1.06</v>
+        <v>1.085</v>
       </c>
       <c r="I52">
-        <v>3.274</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -1804,7 +1804,7 @@
         <v>6</v>
       </c>
       <c r="B53">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C53" t="s">
         <v>11</v>
@@ -1819,10 +1819,10 @@
         <v>0.001</v>
       </c>
       <c r="H53">
-        <v>1.111</v>
+        <v>1.077</v>
       </c>
       <c r="I53">
-        <v>9.715999999999999</v>
+        <v>7.823</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -1830,7 +1830,7 @@
         <v>6</v>
       </c>
       <c r="B54">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C54" t="s">
         <v>11</v>
@@ -1845,10 +1845,10 @@
         <v>0.002</v>
       </c>
       <c r="H54">
-        <v>1.173</v>
+        <v>1.145</v>
       </c>
       <c r="I54">
-        <v>9.194000000000001</v>
+        <v>7.563</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -1856,7 +1856,7 @@
         <v>6</v>
       </c>
       <c r="B55">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
         <v>11</v>
@@ -1865,19 +1865,19 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>14.4181549479407</v>
+        <v>1.3713</v>
       </c>
       <c r="G55">
-        <v>-0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H55">
-        <v>1.06</v>
+        <v>1.085</v>
       </c>
       <c r="I55">
-        <v>3.274</v>
+        <v>2.535</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -1885,7 +1885,7 @@
         <v>7</v>
       </c>
       <c r="B56">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
@@ -1897,13 +1897,13 @@
         <v>2</v>
       </c>
       <c r="G56">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H56">
         <v>1.087</v>
       </c>
       <c r="I56">
-        <v>6.778</v>
+        <v>7.656</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -1911,7 +1911,7 @@
         <v>7</v>
       </c>
       <c r="B57">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
@@ -1926,10 +1926,10 @@
         <v>0.002</v>
       </c>
       <c r="H57">
-        <v>1.112</v>
+        <v>1.147</v>
       </c>
       <c r="I57">
-        <v>6.574</v>
+        <v>7.622</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -1937,7 +1937,7 @@
         <v>7</v>
       </c>
       <c r="B58">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
@@ -1946,19 +1946,19 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F58">
-        <v>10.15579714509119</v>
+        <v>1.3707</v>
       </c>
       <c r="G58">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H58">
-        <v>1.031</v>
+        <v>1.088</v>
       </c>
       <c r="I58">
-        <v>4.681</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -1966,7 +1966,7 @@
         <v>7</v>
       </c>
       <c r="B59">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C59" t="s">
         <v>10</v>
@@ -1978,13 +1978,13 @@
         <v>2</v>
       </c>
       <c r="G59">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H59">
         <v>1.087</v>
       </c>
       <c r="I59">
-        <v>6.778</v>
+        <v>7.656</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -1992,7 +1992,7 @@
         <v>7</v>
       </c>
       <c r="B60">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C60" t="s">
         <v>10</v>
@@ -2007,10 +2007,10 @@
         <v>0.002</v>
       </c>
       <c r="H60">
-        <v>1.112</v>
+        <v>1.147</v>
       </c>
       <c r="I60">
-        <v>6.574</v>
+        <v>7.622</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2018,7 +2018,7 @@
         <v>7</v>
       </c>
       <c r="B61">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
         <v>10</v>
@@ -2027,19 +2027,19 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F61">
-        <v>10.15579714509119</v>
+        <v>1.3707</v>
       </c>
       <c r="G61">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H61">
-        <v>1.031</v>
+        <v>1.088</v>
       </c>
       <c r="I61">
-        <v>4.681</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2047,7 +2047,7 @@
         <v>7</v>
       </c>
       <c r="B62">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C62" t="s">
         <v>11</v>
@@ -2059,13 +2059,13 @@
         <v>2</v>
       </c>
       <c r="G62">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H62">
         <v>1.087</v>
       </c>
       <c r="I62">
-        <v>6.778</v>
+        <v>7.656</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2073,7 +2073,7 @@
         <v>7</v>
       </c>
       <c r="B63">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
@@ -2088,10 +2088,10 @@
         <v>0.002</v>
       </c>
       <c r="H63">
-        <v>1.112</v>
+        <v>1.147</v>
       </c>
       <c r="I63">
-        <v>6.574</v>
+        <v>7.622</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2099,7 +2099,7 @@
         <v>7</v>
       </c>
       <c r="B64">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C64" t="s">
         <v>11</v>
@@ -2108,19 +2108,19 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F64">
-        <v>10.15579714509119</v>
+        <v>1.3707</v>
       </c>
       <c r="G64">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H64">
-        <v>1.031</v>
+        <v>1.088</v>
       </c>
       <c r="I64">
-        <v>4.681</v>
+        <v>2.839</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2128,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="B65">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
@@ -2137,16 +2137,16 @@
         <v>12</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H65">
-        <v>1.073</v>
+        <v>1.079</v>
       </c>
       <c r="I65">
-        <v>5.428</v>
+        <v>7.014</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2154,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="B66">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
@@ -2169,10 +2169,10 @@
         <v>0.002</v>
       </c>
       <c r="H66">
-        <v>1.091</v>
+        <v>1.148</v>
       </c>
       <c r="I66">
-        <v>4.756</v>
+        <v>7.876</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2180,7 +2180,7 @@
         <v>8</v>
       </c>
       <c r="B67">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
@@ -2189,19 +2189,19 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F67">
-        <v>8.390488438364949</v>
+        <v>1.3711</v>
       </c>
       <c r="G67">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H67">
-        <v>1.059</v>
+        <v>1.086</v>
       </c>
       <c r="I67">
-        <v>4.224</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2209,7 +2209,7 @@
         <v>8</v>
       </c>
       <c r="B68">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C68" t="s">
         <v>10</v>
@@ -2218,16 +2218,16 @@
         <v>12</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H68">
-        <v>1.073</v>
+        <v>1.079</v>
       </c>
       <c r="I68">
-        <v>5.428</v>
+        <v>7.014</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2235,7 +2235,7 @@
         <v>8</v>
       </c>
       <c r="B69">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C69" t="s">
         <v>10</v>
@@ -2250,10 +2250,10 @@
         <v>0.002</v>
       </c>
       <c r="H69">
-        <v>1.091</v>
+        <v>1.148</v>
       </c>
       <c r="I69">
-        <v>4.756</v>
+        <v>7.876</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2261,7 +2261,7 @@
         <v>8</v>
       </c>
       <c r="B70">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
@@ -2270,19 +2270,19 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F70">
-        <v>8.390488438364949</v>
+        <v>1.3711</v>
       </c>
       <c r="G70">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H70">
-        <v>1.059</v>
+        <v>1.086</v>
       </c>
       <c r="I70">
-        <v>4.224</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2290,7 +2290,7 @@
         <v>8</v>
       </c>
       <c r="B71">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C71" t="s">
         <v>11</v>
@@ -2299,16 +2299,16 @@
         <v>12</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G71">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H71">
-        <v>1.073</v>
+        <v>1.079</v>
       </c>
       <c r="I71">
-        <v>5.428</v>
+        <v>7.014</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2316,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="B72">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
@@ -2331,10 +2331,10 @@
         <v>0.002</v>
       </c>
       <c r="H72">
-        <v>1.091</v>
+        <v>1.148</v>
       </c>
       <c r="I72">
-        <v>4.756</v>
+        <v>7.876</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2342,7 +2342,7 @@
         <v>8</v>
       </c>
       <c r="B73">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
         <v>11</v>
@@ -2351,19 +2351,19 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73">
-        <v>8.390488438364949</v>
+        <v>1.3711</v>
       </c>
       <c r="G73">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H73">
-        <v>1.059</v>
+        <v>1.086</v>
       </c>
       <c r="I73">
-        <v>4.224</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2371,7 +2371,7 @@
         <v>9</v>
       </c>
       <c r="B74">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
@@ -2383,13 +2383,13 @@
         <v>2</v>
       </c>
       <c r="G74">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H74">
-        <v>1.086</v>
+        <v>1.099</v>
       </c>
       <c r="I74">
-        <v>4.793</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2397,7 +2397,7 @@
         <v>9</v>
       </c>
       <c r="B75">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
@@ -2409,13 +2409,13 @@
         <v>2</v>
       </c>
       <c r="G75">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H75">
-        <v>1.1</v>
+        <v>1.149</v>
       </c>
       <c r="I75">
-        <v>4.763</v>
+        <v>9.973000000000001</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2423,7 +2423,7 @@
         <v>9</v>
       </c>
       <c r="B76">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C76" t="s">
         <v>9</v>
@@ -2432,19 +2432,19 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F76">
-        <v>7.394710106675184</v>
+        <v>1.3688</v>
       </c>
       <c r="G76">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H76">
-        <v>1.047</v>
+        <v>1.108</v>
       </c>
       <c r="I76">
-        <v>3.45</v>
+        <v>2.974</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2452,7 +2452,7 @@
         <v>9</v>
       </c>
       <c r="B77">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C77" t="s">
         <v>10</v>
@@ -2464,13 +2464,13 @@
         <v>2</v>
       </c>
       <c r="G77">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H77">
-        <v>1.086</v>
+        <v>1.099</v>
       </c>
       <c r="I77">
-        <v>4.793</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2478,7 +2478,7 @@
         <v>9</v>
       </c>
       <c r="B78">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C78" t="s">
         <v>10</v>
@@ -2490,13 +2490,13 @@
         <v>2</v>
       </c>
       <c r="G78">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H78">
-        <v>1.1</v>
+        <v>1.149</v>
       </c>
       <c r="I78">
-        <v>4.763</v>
+        <v>9.973000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2504,7 +2504,7 @@
         <v>9</v>
       </c>
       <c r="B79">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
@@ -2513,19 +2513,19 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F79">
-        <v>7.394710106675184</v>
+        <v>1.3688</v>
       </c>
       <c r="G79">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H79">
-        <v>1.047</v>
+        <v>1.108</v>
       </c>
       <c r="I79">
-        <v>3.45</v>
+        <v>2.974</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2533,7 +2533,7 @@
         <v>9</v>
       </c>
       <c r="B80">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C80" t="s">
         <v>11</v>
@@ -2545,13 +2545,13 @@
         <v>2</v>
       </c>
       <c r="G80">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="H80">
-        <v>1.086</v>
+        <v>1.099</v>
       </c>
       <c r="I80">
-        <v>4.793</v>
+        <v>10.219</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -2559,7 +2559,7 @@
         <v>9</v>
       </c>
       <c r="B81">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C81" t="s">
         <v>11</v>
@@ -2571,13 +2571,13 @@
         <v>2</v>
       </c>
       <c r="G81">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H81">
-        <v>1.1</v>
+        <v>1.149</v>
       </c>
       <c r="I81">
-        <v>4.763</v>
+        <v>9.973000000000001</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -2585,7 +2585,7 @@
         <v>9</v>
       </c>
       <c r="B82">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
         <v>11</v>
@@ -2594,19 +2594,19 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F82">
-        <v>7.394710106675184</v>
+        <v>1.3688</v>
       </c>
       <c r="G82">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H82">
-        <v>1.047</v>
+        <v>1.108</v>
       </c>
       <c r="I82">
-        <v>3.45</v>
+        <v>2.974</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -2614,7 +2614,7 @@
         <v>10</v>
       </c>
       <c r="B83">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
@@ -2629,10 +2629,10 @@
         <v>0.001</v>
       </c>
       <c r="H83">
-        <v>1.095</v>
+        <v>1.07</v>
       </c>
       <c r="I83">
-        <v>10.196</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -2640,7 +2640,7 @@
         <v>10</v>
       </c>
       <c r="B84">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C84" t="s">
         <v>9</v>
@@ -2652,13 +2652,13 @@
         <v>2</v>
       </c>
       <c r="G84">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H84">
-        <v>1.161</v>
+        <v>1.132</v>
       </c>
       <c r="I84">
-        <v>9.224</v>
+        <v>7.211</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -2666,7 +2666,7 @@
         <v>10</v>
       </c>
       <c r="B85">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
@@ -2675,19 +2675,19 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F85">
-        <v>15.02334732593209</v>
+        <v>1.3725</v>
       </c>
       <c r="G85">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H85">
-        <v>1.061</v>
+        <v>1.093</v>
       </c>
       <c r="I85">
-        <v>3.047</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -2695,7 +2695,7 @@
         <v>10</v>
       </c>
       <c r="B86">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
@@ -2710,10 +2710,10 @@
         <v>0.001</v>
       </c>
       <c r="H86">
-        <v>1.095</v>
+        <v>1.07</v>
       </c>
       <c r="I86">
-        <v>10.196</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -2721,7 +2721,7 @@
         <v>10</v>
       </c>
       <c r="B87">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
@@ -2733,13 +2733,13 @@
         <v>2</v>
       </c>
       <c r="G87">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H87">
-        <v>1.161</v>
+        <v>1.132</v>
       </c>
       <c r="I87">
-        <v>9.224</v>
+        <v>7.211</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="B88">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C88" t="s">
         <v>10</v>
@@ -2756,19 +2756,19 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F88">
-        <v>15.02334732593209</v>
+        <v>1.3725</v>
       </c>
       <c r="G88">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H88">
-        <v>1.061</v>
+        <v>1.093</v>
       </c>
       <c r="I88">
-        <v>3.047</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -2776,7 +2776,7 @@
         <v>10</v>
       </c>
       <c r="B89">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C89" t="s">
         <v>11</v>
@@ -2791,10 +2791,10 @@
         <v>0.001</v>
       </c>
       <c r="H89">
-        <v>1.095</v>
+        <v>1.07</v>
       </c>
       <c r="I89">
-        <v>10.196</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -2802,7 +2802,7 @@
         <v>10</v>
       </c>
       <c r="B90">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C90" t="s">
         <v>11</v>
@@ -2814,13 +2814,13 @@
         <v>2</v>
       </c>
       <c r="G90">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H90">
-        <v>1.161</v>
+        <v>1.132</v>
       </c>
       <c r="I90">
-        <v>9.224</v>
+        <v>7.211</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -2828,7 +2828,7 @@
         <v>10</v>
       </c>
       <c r="B91">
-        <v>116</v>
+        <v>61</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -2837,19 +2837,19 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F91">
-        <v>15.02334732593209</v>
+        <v>1.3725</v>
       </c>
       <c r="G91">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H91">
-        <v>1.061</v>
+        <v>1.093</v>
       </c>
       <c r="I91">
-        <v>3.047</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -2857,7 +2857,7 @@
         <v>11</v>
       </c>
       <c r="B92">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
@@ -2866,16 +2866,16 @@
         <v>12</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G92">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H92">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="I92">
-        <v>6.033</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -2883,7 +2883,7 @@
         <v>11</v>
       </c>
       <c r="B93">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
@@ -2895,13 +2895,13 @@
         <v>2</v>
       </c>
       <c r="G93">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H93">
-        <v>1.112</v>
+        <v>1.107</v>
       </c>
       <c r="I93">
-        <v>7.274</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -2909,7 +2909,7 @@
         <v>11</v>
       </c>
       <c r="B94">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
@@ -2918,19 +2918,19 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F94">
-        <v>10.9704006065243</v>
+        <v>1.3735</v>
       </c>
       <c r="G94">
-        <v>-0.001</v>
+        <v>0.014</v>
       </c>
       <c r="H94">
-        <v>1.047</v>
+        <v>1.094</v>
       </c>
       <c r="I94">
-        <v>3.109</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -2938,7 +2938,7 @@
         <v>11</v>
       </c>
       <c r="B95">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C95" t="s">
         <v>10</v>
@@ -2947,16 +2947,16 @@
         <v>12</v>
       </c>
       <c r="E95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G95">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H95">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="I95">
-        <v>6.033</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -2964,7 +2964,7 @@
         <v>11</v>
       </c>
       <c r="B96">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C96" t="s">
         <v>10</v>
@@ -2976,13 +2976,13 @@
         <v>2</v>
       </c>
       <c r="G96">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H96">
-        <v>1.112</v>
+        <v>1.107</v>
       </c>
       <c r="I96">
-        <v>7.274</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -2990,7 +2990,7 @@
         <v>11</v>
       </c>
       <c r="B97">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C97" t="s">
         <v>10</v>
@@ -2999,19 +2999,19 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F97">
-        <v>10.9704006065243</v>
+        <v>1.3735</v>
       </c>
       <c r="G97">
-        <v>-0.001</v>
+        <v>0.014</v>
       </c>
       <c r="H97">
-        <v>1.047</v>
+        <v>1.094</v>
       </c>
       <c r="I97">
-        <v>3.109</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3019,7 +3019,7 @@
         <v>11</v>
       </c>
       <c r="B98">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -3028,16 +3028,16 @@
         <v>12</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G98">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H98">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="I98">
-        <v>6.033</v>
+        <v>4.617</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3045,7 +3045,7 @@
         <v>11</v>
       </c>
       <c r="B99">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C99" t="s">
         <v>11</v>
@@ -3057,13 +3057,13 @@
         <v>2</v>
       </c>
       <c r="G99">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H99">
-        <v>1.112</v>
+        <v>1.107</v>
       </c>
       <c r="I99">
-        <v>7.274</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3071,7 +3071,7 @@
         <v>11</v>
       </c>
       <c r="B100">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="C100" t="s">
         <v>11</v>
@@ -3080,19 +3080,19 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F100">
-        <v>10.9704006065243</v>
+        <v>1.3735</v>
       </c>
       <c r="G100">
-        <v>-0.001</v>
+        <v>0.014</v>
       </c>
       <c r="H100">
-        <v>1.047</v>
+        <v>1.094</v>
       </c>
       <c r="I100">
-        <v>3.109</v>
+        <v>1.918</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3100,7 +3100,7 @@
         <v>12</v>
       </c>
       <c r="B101">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
@@ -3112,13 +3112,13 @@
         <v>2</v>
       </c>
       <c r="G101">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H101">
-        <v>1.107</v>
+        <v>1.065</v>
       </c>
       <c r="I101">
-        <v>10.189</v>
+        <v>5.072</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3126,7 +3126,7 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C102" t="s">
         <v>9</v>
@@ -3138,13 +3138,13 @@
         <v>2</v>
       </c>
       <c r="G102">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H102">
-        <v>1.163</v>
+        <v>1.104</v>
       </c>
       <c r="I102">
-        <v>9.859999999999999</v>
+        <v>4.982</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3152,7 +3152,7 @@
         <v>12</v>
       </c>
       <c r="B103">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C103" t="s">
         <v>9</v>
@@ -3161,19 +3161,19 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F103">
-        <v>15.08086629128625</v>
+        <v>1.3733</v>
       </c>
       <c r="G103">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H103">
-        <v>1.07</v>
+        <v>1.076</v>
       </c>
       <c r="I103">
-        <v>3.824</v>
+        <v>2.127</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3181,7 +3181,7 @@
         <v>12</v>
       </c>
       <c r="B104">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
@@ -3193,13 +3193,13 @@
         <v>2</v>
       </c>
       <c r="G104">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H104">
-        <v>1.107</v>
+        <v>1.065</v>
       </c>
       <c r="I104">
-        <v>10.189</v>
+        <v>5.072</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3207,7 +3207,7 @@
         <v>12</v>
       </c>
       <c r="B105">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C105" t="s">
         <v>10</v>
@@ -3219,13 +3219,13 @@
         <v>2</v>
       </c>
       <c r="G105">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H105">
-        <v>1.163</v>
+        <v>1.104</v>
       </c>
       <c r="I105">
-        <v>9.859999999999999</v>
+        <v>4.982</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3233,7 +3233,7 @@
         <v>12</v>
       </c>
       <c r="B106">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C106" t="s">
         <v>10</v>
@@ -3242,19 +3242,19 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F106">
-        <v>15.08086629128625</v>
+        <v>1.3733</v>
       </c>
       <c r="G106">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H106">
-        <v>1.07</v>
+        <v>1.076</v>
       </c>
       <c r="I106">
-        <v>3.824</v>
+        <v>2.127</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3262,7 +3262,7 @@
         <v>12</v>
       </c>
       <c r="B107">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C107" t="s">
         <v>11</v>
@@ -3274,13 +3274,13 @@
         <v>2</v>
       </c>
       <c r="G107">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H107">
-        <v>1.107</v>
+        <v>1.065</v>
       </c>
       <c r="I107">
-        <v>10.189</v>
+        <v>5.072</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3288,7 +3288,7 @@
         <v>12</v>
       </c>
       <c r="B108">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C108" t="s">
         <v>11</v>
@@ -3300,13 +3300,13 @@
         <v>2</v>
       </c>
       <c r="G108">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H108">
-        <v>1.163</v>
+        <v>1.104</v>
       </c>
       <c r="I108">
-        <v>9.859999999999999</v>
+        <v>4.982</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3314,7 +3314,7 @@
         <v>12</v>
       </c>
       <c r="B109">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="C109" t="s">
         <v>11</v>
@@ -3323,19 +3323,19 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F109">
-        <v>15.08086629128625</v>
+        <v>1.3733</v>
       </c>
       <c r="G109">
-        <v>-0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H109">
-        <v>1.07</v>
+        <v>1.076</v>
       </c>
       <c r="I109">
-        <v>3.824</v>
+        <v>2.127</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3343,7 +3343,7 @@
         <v>13</v>
       </c>
       <c r="B110">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C110" t="s">
         <v>9</v>
@@ -3352,16 +3352,16 @@
         <v>12</v>
       </c>
       <c r="E110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H110">
-        <v>1.072</v>
+        <v>1.067</v>
       </c>
       <c r="I110">
-        <v>7.836</v>
+        <v>4.249</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3369,7 +3369,7 @@
         <v>13</v>
       </c>
       <c r="B111">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C111" t="s">
         <v>9</v>
@@ -3381,13 +3381,13 @@
         <v>2</v>
       </c>
       <c r="G111">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H111">
-        <v>1.134</v>
+        <v>1.081</v>
       </c>
       <c r="I111">
-        <v>9.263999999999999</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -3395,7 +3395,7 @@
         <v>13</v>
       </c>
       <c r="B112">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C112" t="s">
         <v>9</v>
@@ -3404,19 +3404,19 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F112">
-        <v>13.96706662962144</v>
+        <v>1.3778</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H112">
-        <v>1.065</v>
+        <v>1.07</v>
       </c>
       <c r="I112">
-        <v>3.15</v>
+        <v>2.262</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -3424,7 +3424,7 @@
         <v>13</v>
       </c>
       <c r="B113">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C113" t="s">
         <v>10</v>
@@ -3433,16 +3433,16 @@
         <v>12</v>
       </c>
       <c r="E113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H113">
-        <v>1.072</v>
+        <v>1.067</v>
       </c>
       <c r="I113">
-        <v>7.836</v>
+        <v>4.249</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -3450,7 +3450,7 @@
         <v>13</v>
       </c>
       <c r="B114">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C114" t="s">
         <v>10</v>
@@ -3462,13 +3462,13 @@
         <v>2</v>
       </c>
       <c r="G114">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H114">
-        <v>1.134</v>
+        <v>1.081</v>
       </c>
       <c r="I114">
-        <v>9.263999999999999</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -3476,7 +3476,7 @@
         <v>13</v>
       </c>
       <c r="B115">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C115" t="s">
         <v>10</v>
@@ -3485,19 +3485,19 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F115">
-        <v>13.96706662962144</v>
+        <v>1.3778</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H115">
-        <v>1.065</v>
+        <v>1.07</v>
       </c>
       <c r="I115">
-        <v>3.15</v>
+        <v>2.262</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -3505,7 +3505,7 @@
         <v>13</v>
       </c>
       <c r="B116">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C116" t="s">
         <v>11</v>
@@ -3514,16 +3514,16 @@
         <v>12</v>
       </c>
       <c r="E116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H116">
-        <v>1.072</v>
+        <v>1.067</v>
       </c>
       <c r="I116">
-        <v>7.836</v>
+        <v>4.249</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -3531,7 +3531,7 @@
         <v>13</v>
       </c>
       <c r="B117">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C117" t="s">
         <v>11</v>
@@ -3543,13 +3543,13 @@
         <v>2</v>
       </c>
       <c r="G117">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H117">
-        <v>1.134</v>
+        <v>1.081</v>
       </c>
       <c r="I117">
-        <v>9.263999999999999</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -3557,7 +3557,7 @@
         <v>13</v>
       </c>
       <c r="B118">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C118" t="s">
         <v>11</v>
@@ -3566,19 +3566,19 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F118">
-        <v>13.96706662962144</v>
+        <v>1.3778</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H118">
-        <v>1.065</v>
+        <v>1.07</v>
       </c>
       <c r="I118">
-        <v>3.15</v>
+        <v>2.262</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -3586,7 +3586,7 @@
         <v>14</v>
       </c>
       <c r="B119">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C119" t="s">
         <v>9</v>
@@ -3595,16 +3595,16 @@
         <v>12</v>
       </c>
       <c r="E119">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H119">
-        <v>1.082</v>
+        <v>1.07</v>
       </c>
       <c r="I119">
-        <v>6.58</v>
+        <v>4.166</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -3612,7 +3612,7 @@
         <v>14</v>
       </c>
       <c r="B120">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C120" t="s">
         <v>9</v>
@@ -3624,13 +3624,13 @@
         <v>2</v>
       </c>
       <c r="G120">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H120">
-        <v>1.152</v>
+        <v>1.088</v>
       </c>
       <c r="I120">
-        <v>8.587</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -3638,7 +3638,7 @@
         <v>14</v>
       </c>
       <c r="B121">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C121" t="s">
         <v>9</v>
@@ -3647,19 +3647,19 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F121">
-        <v>15.02063201977164</v>
+        <v>0</v>
       </c>
       <c r="G121">
         <v>0</v>
       </c>
       <c r="H121">
-        <v>1.066</v>
+        <v>0</v>
       </c>
       <c r="I121">
-        <v>3.088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -3667,7 +3667,7 @@
         <v>14</v>
       </c>
       <c r="B122">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C122" t="s">
         <v>10</v>
@@ -3676,16 +3676,16 @@
         <v>12</v>
       </c>
       <c r="E122">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H122">
-        <v>1.082</v>
+        <v>1.07</v>
       </c>
       <c r="I122">
-        <v>6.58</v>
+        <v>4.166</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -3693,7 +3693,7 @@
         <v>14</v>
       </c>
       <c r="B123">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C123" t="s">
         <v>10</v>
@@ -3705,13 +3705,13 @@
         <v>2</v>
       </c>
       <c r="G123">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H123">
-        <v>1.152</v>
+        <v>1.088</v>
       </c>
       <c r="I123">
-        <v>8.587</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -3719,7 +3719,7 @@
         <v>14</v>
       </c>
       <c r="B124">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C124" t="s">
         <v>10</v>
@@ -3728,19 +3728,19 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F124">
-        <v>15.02063201977164</v>
+        <v>0</v>
       </c>
       <c r="G124">
         <v>0</v>
       </c>
       <c r="H124">
-        <v>1.066</v>
+        <v>0</v>
       </c>
       <c r="I124">
-        <v>3.088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -3748,7 +3748,7 @@
         <v>14</v>
       </c>
       <c r="B125">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C125" t="s">
         <v>11</v>
@@ -3757,16 +3757,16 @@
         <v>12</v>
       </c>
       <c r="E125">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H125">
-        <v>1.082</v>
+        <v>1.07</v>
       </c>
       <c r="I125">
-        <v>6.58</v>
+        <v>4.166</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -3774,7 +3774,7 @@
         <v>14</v>
       </c>
       <c r="B126">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C126" t="s">
         <v>11</v>
@@ -3786,13 +3786,13 @@
         <v>2</v>
       </c>
       <c r="G126">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H126">
-        <v>1.152</v>
+        <v>1.088</v>
       </c>
       <c r="I126">
-        <v>8.587</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -3800,7 +3800,7 @@
         <v>14</v>
       </c>
       <c r="B127">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="C127" t="s">
         <v>11</v>
@@ -3809,19 +3809,19 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F127">
-        <v>15.02063201977164</v>
+        <v>0</v>
       </c>
       <c r="G127">
         <v>0</v>
       </c>
       <c r="H127">
-        <v>1.066</v>
+        <v>0</v>
       </c>
       <c r="I127">
-        <v>3.088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -3829,7 +3829,7 @@
         <v>15</v>
       </c>
       <c r="B128">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C128" t="s">
         <v>9</v>
@@ -3838,16 +3838,16 @@
         <v>12</v>
       </c>
       <c r="E128">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G128">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H128">
-        <v>1.061</v>
+        <v>1.084</v>
       </c>
       <c r="I128">
-        <v>2.757</v>
+        <v>6.578</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -3855,7 +3855,7 @@
         <v>15</v>
       </c>
       <c r="B129">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C129" t="s">
         <v>9</v>
@@ -3867,13 +3867,13 @@
         <v>2</v>
       </c>
       <c r="G129">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H129">
-        <v>1.082</v>
+        <v>1.179</v>
       </c>
       <c r="I129">
-        <v>5.032</v>
+        <v>8.473000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -3881,7 +3881,7 @@
         <v>15</v>
       </c>
       <c r="B130">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C130" t="s">
         <v>9</v>
@@ -3890,19 +3890,19 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F130">
-        <v>7.912438240710293</v>
+        <v>1.3689</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H130">
-        <v>1.039</v>
+        <v>1.082</v>
       </c>
       <c r="I130">
-        <v>3.661</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -3910,7 +3910,7 @@
         <v>15</v>
       </c>
       <c r="B131">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C131" t="s">
         <v>10</v>
@@ -3919,16 +3919,16 @@
         <v>12</v>
       </c>
       <c r="E131">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G131">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>1.061</v>
+        <v>1.084</v>
       </c>
       <c r="I131">
-        <v>2.757</v>
+        <v>6.578</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -3936,7 +3936,7 @@
         <v>15</v>
       </c>
       <c r="B132">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C132" t="s">
         <v>10</v>
@@ -3948,13 +3948,13 @@
         <v>2</v>
       </c>
       <c r="G132">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H132">
-        <v>1.082</v>
+        <v>1.179</v>
       </c>
       <c r="I132">
-        <v>5.032</v>
+        <v>8.473000000000001</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -3962,7 +3962,7 @@
         <v>15</v>
       </c>
       <c r="B133">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C133" t="s">
         <v>10</v>
@@ -3971,19 +3971,19 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F133">
-        <v>7.912438240710293</v>
+        <v>1.3689</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H133">
-        <v>1.039</v>
+        <v>1.082</v>
       </c>
       <c r="I133">
-        <v>3.661</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -3991,7 +3991,7 @@
         <v>15</v>
       </c>
       <c r="B134">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C134" t="s">
         <v>11</v>
@@ -4000,16 +4000,16 @@
         <v>12</v>
       </c>
       <c r="E134">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G134">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>1.061</v>
+        <v>1.084</v>
       </c>
       <c r="I134">
-        <v>2.757</v>
+        <v>6.578</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4017,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="B135">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C135" t="s">
         <v>11</v>
@@ -4029,13 +4029,13 @@
         <v>2</v>
       </c>
       <c r="G135">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H135">
-        <v>1.082</v>
+        <v>1.179</v>
       </c>
       <c r="I135">
-        <v>5.032</v>
+        <v>8.473000000000001</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4043,7 +4043,7 @@
         <v>15</v>
       </c>
       <c r="B136">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C136" t="s">
         <v>11</v>
@@ -4052,19 +4052,19 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F136">
-        <v>7.912438240710293</v>
+        <v>1.3689</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H136">
-        <v>1.039</v>
+        <v>1.082</v>
       </c>
       <c r="I136">
-        <v>3.661</v>
+        <v>2.737</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4072,7 +4072,7 @@
         <v>16</v>
       </c>
       <c r="B137">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C137" t="s">
         <v>9</v>
@@ -4081,16 +4081,16 @@
         <v>12</v>
       </c>
       <c r="E137">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G137">
         <v>0.002</v>
       </c>
       <c r="H137">
-        <v>1.071</v>
+        <v>1.103</v>
       </c>
       <c r="I137">
-        <v>3.935</v>
+        <v>7.232</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4098,7 +4098,7 @@
         <v>16</v>
       </c>
       <c r="B138">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C138" t="s">
         <v>9</v>
@@ -4110,13 +4110,13 @@
         <v>2</v>
       </c>
       <c r="G138">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H138">
-        <v>1.127</v>
+        <v>1.135</v>
       </c>
       <c r="I138">
-        <v>4.82</v>
+        <v>7.183</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4124,7 +4124,7 @@
         <v>16</v>
       </c>
       <c r="B139">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C139" t="s">
         <v>9</v>
@@ -4133,19 +4133,19 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F139">
-        <v>9.14164619158197</v>
+        <v>1.3709</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H139">
-        <v>1.047</v>
+        <v>1.089</v>
       </c>
       <c r="I139">
-        <v>3.296</v>
+        <v>2.424</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4153,7 +4153,7 @@
         <v>16</v>
       </c>
       <c r="B140">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C140" t="s">
         <v>10</v>
@@ -4162,16 +4162,16 @@
         <v>12</v>
       </c>
       <c r="E140">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G140">
         <v>0.002</v>
       </c>
       <c r="H140">
-        <v>1.071</v>
+        <v>1.103</v>
       </c>
       <c r="I140">
-        <v>3.935</v>
+        <v>7.232</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4179,7 +4179,7 @@
         <v>16</v>
       </c>
       <c r="B141">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C141" t="s">
         <v>10</v>
@@ -4191,13 +4191,13 @@
         <v>2</v>
       </c>
       <c r="G141">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H141">
-        <v>1.127</v>
+        <v>1.135</v>
       </c>
       <c r="I141">
-        <v>4.82</v>
+        <v>7.183</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -4205,7 +4205,7 @@
         <v>16</v>
       </c>
       <c r="B142">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C142" t="s">
         <v>10</v>
@@ -4214,19 +4214,19 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F142">
-        <v>9.14164619158197</v>
+        <v>1.3709</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H142">
-        <v>1.047</v>
+        <v>1.089</v>
       </c>
       <c r="I142">
-        <v>3.296</v>
+        <v>2.424</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4234,7 +4234,7 @@
         <v>16</v>
       </c>
       <c r="B143">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C143" t="s">
         <v>11</v>
@@ -4243,16 +4243,16 @@
         <v>12</v>
       </c>
       <c r="E143">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G143">
         <v>0.002</v>
       </c>
       <c r="H143">
-        <v>1.071</v>
+        <v>1.103</v>
       </c>
       <c r="I143">
-        <v>3.935</v>
+        <v>7.232</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -4260,7 +4260,7 @@
         <v>16</v>
       </c>
       <c r="B144">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C144" t="s">
         <v>11</v>
@@ -4272,13 +4272,13 @@
         <v>2</v>
       </c>
       <c r="G144">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H144">
-        <v>1.127</v>
+        <v>1.135</v>
       </c>
       <c r="I144">
-        <v>4.82</v>
+        <v>7.183</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -4286,7 +4286,7 @@
         <v>16</v>
       </c>
       <c r="B145">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C145" t="s">
         <v>11</v>
@@ -4295,19 +4295,19 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F145">
-        <v>9.14164619158197</v>
+        <v>1.3709</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H145">
-        <v>1.047</v>
+        <v>1.089</v>
       </c>
       <c r="I145">
-        <v>3.296</v>
+        <v>2.424</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -4315,7 +4315,7 @@
         <v>17</v>
       </c>
       <c r="B146">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C146" t="s">
         <v>9</v>
@@ -4327,13 +4327,13 @@
         <v>2</v>
       </c>
       <c r="G146">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H146">
-        <v>1.118</v>
+        <v>1.108</v>
       </c>
       <c r="I146">
-        <v>9.406000000000001</v>
+        <v>7.716</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -4341,7 +4341,7 @@
         <v>17</v>
       </c>
       <c r="B147">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C147" t="s">
         <v>9</v>
@@ -4353,13 +4353,13 @@
         <v>2</v>
       </c>
       <c r="G147">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H147">
-        <v>1.147</v>
+        <v>1.139</v>
       </c>
       <c r="I147">
-        <v>8.196999999999999</v>
+        <v>7.558</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -4367,7 +4367,7 @@
         <v>17</v>
       </c>
       <c r="B148">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C148" t="s">
         <v>9</v>
@@ -4376,19 +4376,19 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F148">
-        <v>14.03894759773972</v>
+        <v>1.3695</v>
       </c>
       <c r="G148">
-        <v>-0.003</v>
+        <v>0.01</v>
       </c>
       <c r="H148">
-        <v>1.046</v>
+        <v>1.081</v>
       </c>
       <c r="I148">
-        <v>3.771</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -4396,7 +4396,7 @@
         <v>17</v>
       </c>
       <c r="B149">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C149" t="s">
         <v>10</v>
@@ -4408,13 +4408,13 @@
         <v>2</v>
       </c>
       <c r="G149">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H149">
-        <v>1.118</v>
+        <v>1.108</v>
       </c>
       <c r="I149">
-        <v>9.406000000000001</v>
+        <v>7.716</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -4422,7 +4422,7 @@
         <v>17</v>
       </c>
       <c r="B150">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C150" t="s">
         <v>10</v>
@@ -4434,13 +4434,13 @@
         <v>2</v>
       </c>
       <c r="G150">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H150">
-        <v>1.147</v>
+        <v>1.139</v>
       </c>
       <c r="I150">
-        <v>8.196999999999999</v>
+        <v>7.558</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -4448,7 +4448,7 @@
         <v>17</v>
       </c>
       <c r="B151">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C151" t="s">
         <v>10</v>
@@ -4457,19 +4457,19 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F151">
-        <v>14.03894759773972</v>
+        <v>1.3695</v>
       </c>
       <c r="G151">
-        <v>-0.003</v>
+        <v>0.01</v>
       </c>
       <c r="H151">
-        <v>1.046</v>
+        <v>1.081</v>
       </c>
       <c r="I151">
-        <v>3.771</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -4477,7 +4477,7 @@
         <v>17</v>
       </c>
       <c r="B152">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C152" t="s">
         <v>11</v>
@@ -4489,13 +4489,13 @@
         <v>2</v>
       </c>
       <c r="G152">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H152">
-        <v>1.118</v>
+        <v>1.108</v>
       </c>
       <c r="I152">
-        <v>9.406000000000001</v>
+        <v>7.716</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -4503,7 +4503,7 @@
         <v>17</v>
       </c>
       <c r="B153">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C153" t="s">
         <v>11</v>
@@ -4515,13 +4515,13 @@
         <v>2</v>
       </c>
       <c r="G153">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H153">
-        <v>1.147</v>
+        <v>1.139</v>
       </c>
       <c r="I153">
-        <v>8.196999999999999</v>
+        <v>7.558</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -4529,7 +4529,7 @@
         <v>17</v>
       </c>
       <c r="B154">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C154" t="s">
         <v>11</v>
@@ -4538,19 +4538,19 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F154">
-        <v>14.03894759773972</v>
+        <v>1.3695</v>
       </c>
       <c r="G154">
-        <v>-0.003</v>
+        <v>0.01</v>
       </c>
       <c r="H154">
-        <v>1.046</v>
+        <v>1.081</v>
       </c>
       <c r="I154">
-        <v>3.771</v>
+        <v>2.125</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -4558,7 +4558,7 @@
         <v>18</v>
       </c>
       <c r="B155">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C155" t="s">
         <v>9</v>
@@ -4567,16 +4567,16 @@
         <v>12</v>
       </c>
       <c r="E155">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G155">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H155">
-        <v>1.07</v>
+        <v>1.086</v>
       </c>
       <c r="I155">
-        <v>4.778</v>
+        <v>5.246</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -4584,7 +4584,7 @@
         <v>18</v>
       </c>
       <c r="B156">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C156" t="s">
         <v>9</v>
@@ -4599,10 +4599,10 @@
         <v>0.003</v>
       </c>
       <c r="H156">
-        <v>1.106</v>
+        <v>1.09</v>
       </c>
       <c r="I156">
-        <v>5.003</v>
+        <v>3.678</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -4610,7 +4610,7 @@
         <v>18</v>
       </c>
       <c r="B157">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C157" t="s">
         <v>9</v>
@@ -4619,19 +4619,19 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F157">
-        <v>8.826018331994739</v>
+        <v>1.3774</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H157">
-        <v>1.043</v>
+        <v>1.084</v>
       </c>
       <c r="I157">
-        <v>3.709</v>
+        <v>2.828</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -4639,7 +4639,7 @@
         <v>18</v>
       </c>
       <c r="B158">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C158" t="s">
         <v>10</v>
@@ -4648,16 +4648,16 @@
         <v>12</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G158">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H158">
-        <v>1.07</v>
+        <v>1.086</v>
       </c>
       <c r="I158">
-        <v>4.778</v>
+        <v>5.246</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -4665,7 +4665,7 @@
         <v>18</v>
       </c>
       <c r="B159">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C159" t="s">
         <v>10</v>
@@ -4680,10 +4680,10 @@
         <v>0.003</v>
       </c>
       <c r="H159">
-        <v>1.106</v>
+        <v>1.09</v>
       </c>
       <c r="I159">
-        <v>5.003</v>
+        <v>3.678</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -4691,7 +4691,7 @@
         <v>18</v>
       </c>
       <c r="B160">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C160" t="s">
         <v>10</v>
@@ -4700,19 +4700,19 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F160">
-        <v>8.826018331994739</v>
+        <v>1.3774</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H160">
-        <v>1.043</v>
+        <v>1.084</v>
       </c>
       <c r="I160">
-        <v>3.709</v>
+        <v>2.828</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -4720,7 +4720,7 @@
         <v>18</v>
       </c>
       <c r="B161">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C161" t="s">
         <v>11</v>
@@ -4729,16 +4729,16 @@
         <v>12</v>
       </c>
       <c r="E161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G161">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H161">
-        <v>1.07</v>
+        <v>1.086</v>
       </c>
       <c r="I161">
-        <v>4.778</v>
+        <v>5.246</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -4746,7 +4746,7 @@
         <v>18</v>
       </c>
       <c r="B162">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C162" t="s">
         <v>11</v>
@@ -4761,10 +4761,10 @@
         <v>0.003</v>
       </c>
       <c r="H162">
-        <v>1.106</v>
+        <v>1.09</v>
       </c>
       <c r="I162">
-        <v>5.003</v>
+        <v>3.678</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -4772,7 +4772,7 @@
         <v>18</v>
       </c>
       <c r="B163">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C163" t="s">
         <v>11</v>
@@ -4781,19 +4781,19 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F163">
-        <v>8.826018331994739</v>
+        <v>1.3774</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H163">
-        <v>1.043</v>
+        <v>1.084</v>
       </c>
       <c r="I163">
-        <v>3.709</v>
+        <v>2.828</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -4801,7 +4801,7 @@
         <v>19</v>
       </c>
       <c r="B164">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C164" t="s">
         <v>9</v>
@@ -4810,16 +4810,16 @@
         <v>12</v>
       </c>
       <c r="E164">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G164">
         <v>0.001</v>
       </c>
       <c r="H164">
-        <v>1.081</v>
+        <v>1.094</v>
       </c>
       <c r="I164">
-        <v>5.63</v>
+        <v>8.848000000000001</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -4827,7 +4827,7 @@
         <v>19</v>
       </c>
       <c r="B165">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C165" t="s">
         <v>9</v>
@@ -4842,10 +4842,10 @@
         <v>0.002</v>
       </c>
       <c r="H165">
-        <v>1.139</v>
+        <v>1.145</v>
       </c>
       <c r="I165">
-        <v>7.581</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -4853,7 +4853,7 @@
         <v>19</v>
       </c>
       <c r="B166">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C166" t="s">
         <v>9</v>
@@ -4862,19 +4862,19 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F166">
-        <v>11.56470485610042</v>
+        <v>1.3683</v>
       </c>
       <c r="G166">
-        <v>-0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H166">
-        <v>1.047</v>
+        <v>1.103</v>
       </c>
       <c r="I166">
-        <v>3.307</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -4882,7 +4882,7 @@
         <v>19</v>
       </c>
       <c r="B167">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C167" t="s">
         <v>10</v>
@@ -4891,16 +4891,16 @@
         <v>12</v>
       </c>
       <c r="E167">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G167">
         <v>0.001</v>
       </c>
       <c r="H167">
-        <v>1.081</v>
+        <v>1.094</v>
       </c>
       <c r="I167">
-        <v>5.63</v>
+        <v>8.848000000000001</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -4908,7 +4908,7 @@
         <v>19</v>
       </c>
       <c r="B168">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C168" t="s">
         <v>10</v>
@@ -4923,10 +4923,10 @@
         <v>0.002</v>
       </c>
       <c r="H168">
-        <v>1.139</v>
+        <v>1.145</v>
       </c>
       <c r="I168">
-        <v>7.581</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -4934,7 +4934,7 @@
         <v>19</v>
       </c>
       <c r="B169">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C169" t="s">
         <v>10</v>
@@ -4943,19 +4943,19 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F169">
-        <v>11.56470485610042</v>
+        <v>1.3683</v>
       </c>
       <c r="G169">
-        <v>-0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H169">
-        <v>1.047</v>
+        <v>1.103</v>
       </c>
       <c r="I169">
-        <v>3.307</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -4963,7 +4963,7 @@
         <v>19</v>
       </c>
       <c r="B170">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C170" t="s">
         <v>11</v>
@@ -4972,16 +4972,16 @@
         <v>12</v>
       </c>
       <c r="E170">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G170">
         <v>0.001</v>
       </c>
       <c r="H170">
-        <v>1.081</v>
+        <v>1.094</v>
       </c>
       <c r="I170">
-        <v>5.63</v>
+        <v>8.848000000000001</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -4989,7 +4989,7 @@
         <v>19</v>
       </c>
       <c r="B171">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C171" t="s">
         <v>11</v>
@@ -5004,10 +5004,10 @@
         <v>0.002</v>
       </c>
       <c r="H171">
-        <v>1.139</v>
+        <v>1.145</v>
       </c>
       <c r="I171">
-        <v>7.581</v>
+        <v>8.368</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -5015,7 +5015,7 @@
         <v>19</v>
       </c>
       <c r="B172">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C172" t="s">
         <v>11</v>
@@ -5024,19 +5024,19 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F172">
-        <v>11.56470485610042</v>
+        <v>1.3683</v>
       </c>
       <c r="G172">
-        <v>-0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H172">
-        <v>1.047</v>
+        <v>1.103</v>
       </c>
       <c r="I172">
-        <v>3.307</v>
+        <v>2.314</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -5044,7 +5044,7 @@
         <v>20</v>
       </c>
       <c r="B173">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C173" t="s">
         <v>9</v>
@@ -5053,16 +5053,16 @@
         <v>12</v>
       </c>
       <c r="E173">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G173">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H173">
-        <v>1.061</v>
+        <v>1.081</v>
       </c>
       <c r="I173">
-        <v>3.311</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -5070,7 +5070,7 @@
         <v>20</v>
       </c>
       <c r="B174">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C174" t="s">
         <v>9</v>
@@ -5079,16 +5079,16 @@
         <v>13</v>
       </c>
       <c r="E174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G174">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H174">
-        <v>1.1</v>
+        <v>1.156</v>
       </c>
       <c r="I174">
-        <v>5.091</v>
+        <v>6.808</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -5096,7 +5096,7 @@
         <v>20</v>
       </c>
       <c r="B175">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C175" t="s">
         <v>9</v>
@@ -5105,19 +5105,19 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F175">
-        <v>8.50062431642713</v>
+        <v>1.3704</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H175">
-        <v>1.009</v>
+        <v>1.087</v>
       </c>
       <c r="I175">
-        <v>4.978</v>
+        <v>3.214</v>
       </c>
     </row>
     <row r="176" spans="1:9">
@@ -5125,7 +5125,7 @@
         <v>20</v>
       </c>
       <c r="B176">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C176" t="s">
         <v>10</v>
@@ -5134,16 +5134,16 @@
         <v>12</v>
       </c>
       <c r="E176">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G176">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H176">
-        <v>1.061</v>
+        <v>1.081</v>
       </c>
       <c r="I176">
-        <v>3.311</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="177" spans="1:9">
@@ -5151,7 +5151,7 @@
         <v>20</v>
       </c>
       <c r="B177">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C177" t="s">
         <v>10</v>
@@ -5160,16 +5160,16 @@
         <v>13</v>
       </c>
       <c r="E177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G177">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H177">
-        <v>1.1</v>
+        <v>1.156</v>
       </c>
       <c r="I177">
-        <v>5.091</v>
+        <v>6.808</v>
       </c>
     </row>
     <row r="178" spans="1:9">
@@ -5177,7 +5177,7 @@
         <v>20</v>
       </c>
       <c r="B178">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C178" t="s">
         <v>10</v>
@@ -5186,19 +5186,19 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F178">
-        <v>8.50062431642713</v>
+        <v>1.3704</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H178">
-        <v>1.009</v>
+        <v>1.087</v>
       </c>
       <c r="I178">
-        <v>4.978</v>
+        <v>3.214</v>
       </c>
     </row>
     <row r="179" spans="1:9">
@@ -5206,7 +5206,7 @@
         <v>20</v>
       </c>
       <c r="B179">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C179" t="s">
         <v>11</v>
@@ -5215,16 +5215,16 @@
         <v>12</v>
       </c>
       <c r="E179">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G179">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H179">
-        <v>1.061</v>
+        <v>1.081</v>
       </c>
       <c r="I179">
-        <v>3.311</v>
+        <v>6.732</v>
       </c>
     </row>
     <row r="180" spans="1:9">
@@ -5232,7 +5232,7 @@
         <v>20</v>
       </c>
       <c r="B180">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C180" t="s">
         <v>11</v>
@@ -5241,16 +5241,16 @@
         <v>13</v>
       </c>
       <c r="E180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G180">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H180">
-        <v>1.1</v>
+        <v>1.156</v>
       </c>
       <c r="I180">
-        <v>5.091</v>
+        <v>6.808</v>
       </c>
     </row>
     <row r="181" spans="1:9">
@@ -5258,7 +5258,7 @@
         <v>20</v>
       </c>
       <c r="B181">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="C181" t="s">
         <v>11</v>
@@ -5267,19 +5267,19 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F181">
-        <v>8.50062431642713</v>
+        <v>1.3704</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H181">
-        <v>1.009</v>
+        <v>1.087</v>
       </c>
       <c r="I181">
-        <v>4.978</v>
+        <v>3.214</v>
       </c>
     </row>
     <row r="182" spans="1:9">
@@ -5287,7 +5287,7 @@
         <v>21</v>
       </c>
       <c r="B182">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C182" t="s">
         <v>9</v>
@@ -5296,16 +5296,16 @@
         <v>12</v>
       </c>
       <c r="E182">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G182">
         <v>0.001</v>
       </c>
       <c r="H182">
-        <v>1.074</v>
+        <v>1.082</v>
       </c>
       <c r="I182">
-        <v>5.755</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="183" spans="1:9">
@@ -5313,7 +5313,7 @@
         <v>21</v>
       </c>
       <c r="B183">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C183" t="s">
         <v>9</v>
@@ -5328,10 +5328,10 @@
         <v>0.002</v>
       </c>
       <c r="H183">
-        <v>1.142</v>
+        <v>1.148</v>
       </c>
       <c r="I183">
-        <v>6.853</v>
+        <v>8.324</v>
       </c>
     </row>
     <row r="184" spans="1:9">
@@ -5339,7 +5339,7 @@
         <v>21</v>
       </c>
       <c r="B184">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C184" t="s">
         <v>9</v>
@@ -5348,19 +5348,19 @@
         <v>14</v>
       </c>
       <c r="E184">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F184">
-        <v>11.79094280391565</v>
+        <v>1.3712</v>
       </c>
       <c r="G184">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H184">
-        <v>1.069</v>
+        <v>1.076</v>
       </c>
       <c r="I184">
-        <v>2.949</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="185" spans="1:9">
@@ -5368,7 +5368,7 @@
         <v>21</v>
       </c>
       <c r="B185">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C185" t="s">
         <v>10</v>
@@ -5377,16 +5377,16 @@
         <v>12</v>
       </c>
       <c r="E185">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G185">
         <v>0.001</v>
       </c>
       <c r="H185">
-        <v>1.074</v>
+        <v>1.082</v>
       </c>
       <c r="I185">
-        <v>5.755</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="186" spans="1:9">
@@ -5394,7 +5394,7 @@
         <v>21</v>
       </c>
       <c r="B186">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C186" t="s">
         <v>10</v>
@@ -5409,10 +5409,10 @@
         <v>0.002</v>
       </c>
       <c r="H186">
-        <v>1.142</v>
+        <v>1.148</v>
       </c>
       <c r="I186">
-        <v>6.853</v>
+        <v>8.324</v>
       </c>
     </row>
     <row r="187" spans="1:9">
@@ -5420,7 +5420,7 @@
         <v>21</v>
       </c>
       <c r="B187">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C187" t="s">
         <v>10</v>
@@ -5429,19 +5429,19 @@
         <v>14</v>
       </c>
       <c r="E187">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F187">
-        <v>11.79094280391565</v>
+        <v>1.3712</v>
       </c>
       <c r="G187">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H187">
-        <v>1.069</v>
+        <v>1.076</v>
       </c>
       <c r="I187">
-        <v>2.949</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="188" spans="1:9">
@@ -5449,7 +5449,7 @@
         <v>21</v>
       </c>
       <c r="B188">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C188" t="s">
         <v>11</v>
@@ -5458,16 +5458,16 @@
         <v>12</v>
       </c>
       <c r="E188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G188">
         <v>0.001</v>
       </c>
       <c r="H188">
-        <v>1.074</v>
+        <v>1.082</v>
       </c>
       <c r="I188">
-        <v>5.755</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -5475,7 +5475,7 @@
         <v>21</v>
       </c>
       <c r="B189">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
@@ -5490,10 +5490,10 @@
         <v>0.002</v>
       </c>
       <c r="H189">
-        <v>1.142</v>
+        <v>1.148</v>
       </c>
       <c r="I189">
-        <v>6.853</v>
+        <v>8.324</v>
       </c>
     </row>
     <row r="190" spans="1:9">
@@ -5501,7 +5501,7 @@
         <v>21</v>
       </c>
       <c r="B190">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C190" t="s">
         <v>11</v>
@@ -5510,19 +5510,19 @@
         <v>14</v>
       </c>
       <c r="E190">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F190">
-        <v>11.79094280391565</v>
+        <v>1.3712</v>
       </c>
       <c r="G190">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H190">
-        <v>1.069</v>
+        <v>1.076</v>
       </c>
       <c r="I190">
-        <v>2.949</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="191" spans="1:9">
@@ -5571,10 +5571,10 @@
         <v>0.003</v>
       </c>
       <c r="H192">
-        <v>1.122</v>
+        <v>1.121</v>
       </c>
       <c r="I192">
-        <v>5.58</v>
+        <v>6.193</v>
       </c>
     </row>
     <row r="193" spans="1:9">
@@ -5591,19 +5591,19 @@
         <v>14</v>
       </c>
       <c r="E193">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F193">
-        <v>9.448579323164944</v>
+        <v>1.3748</v>
       </c>
       <c r="G193">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H193">
-        <v>1.067</v>
+        <v>1.082</v>
       </c>
       <c r="I193">
-        <v>2.469</v>
+        <v>2.539</v>
       </c>
     </row>
     <row r="194" spans="1:9">
@@ -5652,10 +5652,10 @@
         <v>0.003</v>
       </c>
       <c r="H195">
-        <v>1.122</v>
+        <v>1.121</v>
       </c>
       <c r="I195">
-        <v>5.58</v>
+        <v>6.193</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -5672,19 +5672,19 @@
         <v>14</v>
       </c>
       <c r="E196">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F196">
-        <v>9.448579323164944</v>
+        <v>1.3748</v>
       </c>
       <c r="G196">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H196">
-        <v>1.067</v>
+        <v>1.082</v>
       </c>
       <c r="I196">
-        <v>2.469</v>
+        <v>2.539</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -5733,10 +5733,10 @@
         <v>0.003</v>
       </c>
       <c r="H198">
-        <v>1.122</v>
+        <v>1.121</v>
       </c>
       <c r="I198">
-        <v>5.58</v>
+        <v>6.193</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -5753,19 +5753,19 @@
         <v>14</v>
       </c>
       <c r="E199">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F199">
-        <v>9.448579323164944</v>
+        <v>1.3748</v>
       </c>
       <c r="G199">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="H199">
-        <v>1.067</v>
+        <v>1.082</v>
       </c>
       <c r="I199">
-        <v>2.469</v>
+        <v>2.539</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -5785,13 +5785,13 @@
         <v>2</v>
       </c>
       <c r="G200">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H200">
-        <v>1.084</v>
+        <v>1.091</v>
       </c>
       <c r="I200">
-        <v>5.423</v>
+        <v>5.416</v>
       </c>
     </row>
     <row r="201" spans="1:9">
@@ -5814,10 +5814,10 @@
         <v>0.003</v>
       </c>
       <c r="H201">
-        <v>1.115</v>
+        <v>1.104</v>
       </c>
       <c r="I201">
-        <v>5.316</v>
+        <v>4.269</v>
       </c>
     </row>
     <row r="202" spans="1:9">
@@ -5834,19 +5834,19 @@
         <v>14</v>
       </c>
       <c r="E202">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F202">
-        <v>8.26762639165878</v>
+        <v>1.3743</v>
       </c>
       <c r="G202">
-        <v>-0.001</v>
+        <v>0.011</v>
       </c>
       <c r="H202">
-        <v>1.031</v>
+        <v>1.096</v>
       </c>
       <c r="I202">
-        <v>3.636</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="203" spans="1:9">
@@ -5866,13 +5866,13 @@
         <v>2</v>
       </c>
       <c r="G203">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H203">
-        <v>1.084</v>
+        <v>1.091</v>
       </c>
       <c r="I203">
-        <v>5.423</v>
+        <v>5.416</v>
       </c>
     </row>
     <row r="204" spans="1:9">
@@ -5895,10 +5895,10 @@
         <v>0.003</v>
       </c>
       <c r="H204">
-        <v>1.115</v>
+        <v>1.104</v>
       </c>
       <c r="I204">
-        <v>5.316</v>
+        <v>4.269</v>
       </c>
     </row>
     <row r="205" spans="1:9">
@@ -5915,19 +5915,19 @@
         <v>14</v>
       </c>
       <c r="E205">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F205">
-        <v>8.26762639165878</v>
+        <v>1.3743</v>
       </c>
       <c r="G205">
-        <v>-0.001</v>
+        <v>0.011</v>
       </c>
       <c r="H205">
-        <v>1.031</v>
+        <v>1.096</v>
       </c>
       <c r="I205">
-        <v>3.636</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="206" spans="1:9">
@@ -5947,13 +5947,13 @@
         <v>2</v>
       </c>
       <c r="G206">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="H206">
-        <v>1.084</v>
+        <v>1.091</v>
       </c>
       <c r="I206">
-        <v>5.423</v>
+        <v>5.416</v>
       </c>
     </row>
     <row r="207" spans="1:9">
@@ -5976,10 +5976,10 @@
         <v>0.003</v>
       </c>
       <c r="H207">
-        <v>1.115</v>
+        <v>1.104</v>
       </c>
       <c r="I207">
-        <v>5.316</v>
+        <v>4.269</v>
       </c>
     </row>
     <row r="208" spans="1:9">
@@ -5996,19 +5996,19 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F208">
-        <v>8.26762639165878</v>
+        <v>1.3743</v>
       </c>
       <c r="G208">
-        <v>-0.001</v>
+        <v>0.011</v>
       </c>
       <c r="H208">
-        <v>1.031</v>
+        <v>1.096</v>
       </c>
       <c r="I208">
-        <v>3.636</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="209" spans="1:9">
@@ -6025,16 +6025,16 @@
         <v>12</v>
       </c>
       <c r="E209">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G209">
         <v>0.001</v>
       </c>
       <c r="H209">
-        <v>1.074</v>
+        <v>1.08</v>
       </c>
       <c r="I209">
-        <v>4.709</v>
+        <v>7.786</v>
       </c>
     </row>
     <row r="210" spans="1:9">
@@ -6057,10 +6057,10 @@
         <v>0.002</v>
       </c>
       <c r="H210">
-        <v>1.136</v>
+        <v>1.123</v>
       </c>
       <c r="I210">
-        <v>7.608</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="211" spans="1:9">
@@ -6080,16 +6080,16 @@
         <v>7</v>
       </c>
       <c r="F211">
-        <v>11.56216139309612</v>
+        <v>1.3722</v>
       </c>
       <c r="G211">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H211">
-        <v>1.053</v>
+        <v>1.088</v>
       </c>
       <c r="I211">
-        <v>3.67</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="212" spans="1:9">
@@ -6106,16 +6106,16 @@
         <v>12</v>
       </c>
       <c r="E212">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G212">
         <v>0.001</v>
       </c>
       <c r="H212">
-        <v>1.074</v>
+        <v>1.08</v>
       </c>
       <c r="I212">
-        <v>4.709</v>
+        <v>7.786</v>
       </c>
     </row>
     <row r="213" spans="1:9">
@@ -6138,10 +6138,10 @@
         <v>0.002</v>
       </c>
       <c r="H213">
-        <v>1.136</v>
+        <v>1.123</v>
       </c>
       <c r="I213">
-        <v>7.608</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="214" spans="1:9">
@@ -6161,16 +6161,16 @@
         <v>7</v>
       </c>
       <c r="F214">
-        <v>11.56216139309612</v>
+        <v>1.3722</v>
       </c>
       <c r="G214">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H214">
-        <v>1.053</v>
+        <v>1.088</v>
       </c>
       <c r="I214">
-        <v>3.67</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="215" spans="1:9">
@@ -6187,16 +6187,16 @@
         <v>12</v>
       </c>
       <c r="E215">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G215">
         <v>0.001</v>
       </c>
       <c r="H215">
-        <v>1.074</v>
+        <v>1.08</v>
       </c>
       <c r="I215">
-        <v>4.709</v>
+        <v>7.786</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -6219,10 +6219,10 @@
         <v>0.002</v>
       </c>
       <c r="H216">
-        <v>1.136</v>
+        <v>1.123</v>
       </c>
       <c r="I216">
-        <v>7.608</v>
+        <v>5.962</v>
       </c>
     </row>
     <row r="217" spans="1:9">
@@ -6242,16 +6242,16 @@
         <v>7</v>
       </c>
       <c r="F217">
-        <v>11.56216139309612</v>
+        <v>1.3722</v>
       </c>
       <c r="G217">
-        <v>-0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H217">
-        <v>1.053</v>
+        <v>1.088</v>
       </c>
       <c r="I217">
-        <v>3.67</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="218" spans="1:9">
@@ -6268,16 +6268,16 @@
         <v>12</v>
       </c>
       <c r="E218">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H218">
-        <v>1.065</v>
+        <v>1.079</v>
       </c>
       <c r="I218">
-        <v>6.906</v>
+        <v>6.039</v>
       </c>
     </row>
     <row r="219" spans="1:9">
@@ -6300,10 +6300,10 @@
         <v>0.002</v>
       </c>
       <c r="H219">
-        <v>1.118</v>
+        <v>1.126</v>
       </c>
       <c r="I219">
-        <v>7.982</v>
+        <v>6.727</v>
       </c>
     </row>
     <row r="220" spans="1:9">
@@ -6320,19 +6320,19 @@
         <v>14</v>
       </c>
       <c r="E220">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F220">
-        <v>12.28814752963171</v>
+        <v>1.3719</v>
       </c>
       <c r="G220">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H220">
-        <v>1.05</v>
+        <v>1.083</v>
       </c>
       <c r="I220">
-        <v>3.534</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="221" spans="1:9">
@@ -6349,16 +6349,16 @@
         <v>12</v>
       </c>
       <c r="E221">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H221">
-        <v>1.065</v>
+        <v>1.079</v>
       </c>
       <c r="I221">
-        <v>6.906</v>
+        <v>6.039</v>
       </c>
     </row>
     <row r="222" spans="1:9">
@@ -6381,10 +6381,10 @@
         <v>0.002</v>
       </c>
       <c r="H222">
-        <v>1.118</v>
+        <v>1.126</v>
       </c>
       <c r="I222">
-        <v>7.982</v>
+        <v>6.727</v>
       </c>
     </row>
     <row r="223" spans="1:9">
@@ -6401,19 +6401,19 @@
         <v>14</v>
       </c>
       <c r="E223">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F223">
-        <v>12.28814752963171</v>
+        <v>1.3719</v>
       </c>
       <c r="G223">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H223">
-        <v>1.05</v>
+        <v>1.083</v>
       </c>
       <c r="I223">
-        <v>3.534</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="224" spans="1:9">
@@ -6430,16 +6430,16 @@
         <v>12</v>
       </c>
       <c r="E224">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G224">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H224">
-        <v>1.065</v>
+        <v>1.079</v>
       </c>
       <c r="I224">
-        <v>6.906</v>
+        <v>6.039</v>
       </c>
     </row>
     <row r="225" spans="1:9">
@@ -6462,10 +6462,10 @@
         <v>0.002</v>
       </c>
       <c r="H225">
-        <v>1.118</v>
+        <v>1.126</v>
       </c>
       <c r="I225">
-        <v>7.982</v>
+        <v>6.727</v>
       </c>
     </row>
     <row r="226" spans="1:9">
@@ -6482,19 +6482,19 @@
         <v>14</v>
       </c>
       <c r="E226">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F226">
-        <v>12.28814752963171</v>
+        <v>1.3719</v>
       </c>
       <c r="G226">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="H226">
-        <v>1.05</v>
+        <v>1.083</v>
       </c>
       <c r="I226">
-        <v>3.534</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="227" spans="1:9">
@@ -6511,16 +6511,16 @@
         <v>12</v>
       </c>
       <c r="E227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G227">
         <v>0.001</v>
       </c>
       <c r="H227">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I227">
-        <v>9.531000000000001</v>
+        <v>7.926</v>
       </c>
     </row>
     <row r="228" spans="1:9">
@@ -6540,13 +6540,13 @@
         <v>2</v>
       </c>
       <c r="G228">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H228">
-        <v>1.141</v>
+        <v>1.155</v>
       </c>
       <c r="I228">
-        <v>9.31</v>
+        <v>9.221</v>
       </c>
     </row>
     <row r="229" spans="1:9">
@@ -6563,19 +6563,19 @@
         <v>14</v>
       </c>
       <c r="E229">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F229">
-        <v>14.03932446499019</v>
+        <v>1.3694</v>
       </c>
       <c r="G229">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="H229">
-        <v>1.046</v>
+        <v>1.085</v>
       </c>
       <c r="I229">
-        <v>3.754</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="230" spans="1:9">
@@ -6592,16 +6592,16 @@
         <v>12</v>
       </c>
       <c r="E230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G230">
         <v>0.001</v>
       </c>
       <c r="H230">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I230">
-        <v>9.531000000000001</v>
+        <v>7.926</v>
       </c>
     </row>
     <row r="231" spans="1:9">
@@ -6621,13 +6621,13 @@
         <v>2</v>
       </c>
       <c r="G231">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H231">
-        <v>1.141</v>
+        <v>1.155</v>
       </c>
       <c r="I231">
-        <v>9.31</v>
+        <v>9.221</v>
       </c>
     </row>
     <row r="232" spans="1:9">
@@ -6644,19 +6644,19 @@
         <v>14</v>
       </c>
       <c r="E232">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F232">
-        <v>14.03932446499019</v>
+        <v>1.3694</v>
       </c>
       <c r="G232">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="H232">
-        <v>1.046</v>
+        <v>1.085</v>
       </c>
       <c r="I232">
-        <v>3.754</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="233" spans="1:9">
@@ -6673,16 +6673,16 @@
         <v>12</v>
       </c>
       <c r="E233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G233">
         <v>0.001</v>
       </c>
       <c r="H233">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I233">
-        <v>9.531000000000001</v>
+        <v>7.926</v>
       </c>
     </row>
     <row r="234" spans="1:9">
@@ -6702,13 +6702,13 @@
         <v>2</v>
       </c>
       <c r="G234">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H234">
-        <v>1.141</v>
+        <v>1.155</v>
       </c>
       <c r="I234">
-        <v>9.31</v>
+        <v>9.221</v>
       </c>
     </row>
     <row r="235" spans="1:9">
@@ -6725,19 +6725,19 @@
         <v>14</v>
       </c>
       <c r="E235">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F235">
-        <v>14.03932446499019</v>
+        <v>1.3694</v>
       </c>
       <c r="G235">
-        <v>-0.003</v>
+        <v>0.003</v>
       </c>
       <c r="H235">
-        <v>1.046</v>
+        <v>1.085</v>
       </c>
       <c r="I235">
-        <v>3.754</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="236" spans="1:9">
@@ -6763,7 +6763,7 @@
         <v>1.079</v>
       </c>
       <c r="I236">
-        <v>6.38</v>
+        <v>6.381</v>
       </c>
     </row>
     <row r="237" spans="1:9">
@@ -6780,16 +6780,16 @@
         <v>13</v>
       </c>
       <c r="E237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G237">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H237">
-        <v>1.104</v>
+        <v>1.106</v>
       </c>
       <c r="I237">
-        <v>5.233</v>
+        <v>6.148</v>
       </c>
     </row>
     <row r="238" spans="1:9">
@@ -6806,19 +6806,19 @@
         <v>14</v>
       </c>
       <c r="E238">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F238">
-        <v>9.557547689441687</v>
+        <v>1.3756</v>
       </c>
       <c r="G238">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="H238">
-        <v>1.048</v>
+        <v>1.085</v>
       </c>
       <c r="I238">
-        <v>3.328</v>
+        <v>4.112</v>
       </c>
     </row>
     <row r="239" spans="1:9">
@@ -6844,7 +6844,7 @@
         <v>1.079</v>
       </c>
       <c r="I239">
-        <v>6.38</v>
+        <v>6.381</v>
       </c>
     </row>
     <row r="240" spans="1:9">
@@ -6861,16 +6861,16 @@
         <v>13</v>
       </c>
       <c r="E240">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G240">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H240">
-        <v>1.104</v>
+        <v>1.106</v>
       </c>
       <c r="I240">
-        <v>5.233</v>
+        <v>6.148</v>
       </c>
     </row>
     <row r="241" spans="1:9">
@@ -6887,19 +6887,19 @@
         <v>14</v>
       </c>
       <c r="E241">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F241">
-        <v>9.557547689441687</v>
+        <v>1.3756</v>
       </c>
       <c r="G241">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="H241">
-        <v>1.048</v>
+        <v>1.085</v>
       </c>
       <c r="I241">
-        <v>3.328</v>
+        <v>4.112</v>
       </c>
     </row>
     <row r="242" spans="1:9">
@@ -6925,7 +6925,7 @@
         <v>1.079</v>
       </c>
       <c r="I242">
-        <v>6.38</v>
+        <v>6.381</v>
       </c>
     </row>
     <row r="243" spans="1:9">
@@ -6942,16 +6942,16 @@
         <v>13</v>
       </c>
       <c r="E243">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G243">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H243">
-        <v>1.104</v>
+        <v>1.106</v>
       </c>
       <c r="I243">
-        <v>5.233</v>
+        <v>6.148</v>
       </c>
     </row>
     <row r="244" spans="1:9">
@@ -6968,19 +6968,19 @@
         <v>14</v>
       </c>
       <c r="E244">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F244">
-        <v>9.557547689441687</v>
+        <v>1.3756</v>
       </c>
       <c r="G244">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="H244">
-        <v>1.048</v>
+        <v>1.085</v>
       </c>
       <c r="I244">
-        <v>3.328</v>
+        <v>4.112</v>
       </c>
     </row>
     <row r="245" spans="1:9">
@@ -6997,16 +6997,16 @@
         <v>12</v>
       </c>
       <c r="E245">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G245">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H245">
-        <v>1.058</v>
+        <v>1.057</v>
       </c>
       <c r="I245">
-        <v>2.487</v>
+        <v>3.477</v>
       </c>
     </row>
     <row r="246" spans="1:9">
@@ -7032,7 +7032,7 @@
         <v>1.083</v>
       </c>
       <c r="I246">
-        <v>3.619</v>
+        <v>4.348</v>
       </c>
     </row>
     <row r="247" spans="1:9">
@@ -7049,19 +7049,19 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F247">
-        <v>7.4040992227928</v>
+        <v>1.3806</v>
       </c>
       <c r="G247">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H247">
-        <v>1.042</v>
+        <v>1.077</v>
       </c>
       <c r="I247">
-        <v>3.46</v>
+        <v>2.726</v>
       </c>
     </row>
     <row r="248" spans="1:9">
@@ -7078,16 +7078,16 @@
         <v>12</v>
       </c>
       <c r="E248">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G248">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H248">
-        <v>1.058</v>
+        <v>1.057</v>
       </c>
       <c r="I248">
-        <v>2.487</v>
+        <v>3.477</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -7113,7 +7113,7 @@
         <v>1.083</v>
       </c>
       <c r="I249">
-        <v>3.619</v>
+        <v>4.348</v>
       </c>
     </row>
     <row r="250" spans="1:9">
@@ -7130,19 +7130,19 @@
         <v>14</v>
       </c>
       <c r="E250">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F250">
-        <v>7.4040992227928</v>
+        <v>1.3806</v>
       </c>
       <c r="G250">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H250">
-        <v>1.042</v>
+        <v>1.077</v>
       </c>
       <c r="I250">
-        <v>3.46</v>
+        <v>2.726</v>
       </c>
     </row>
     <row r="251" spans="1:9">
@@ -7159,16 +7159,16 @@
         <v>12</v>
       </c>
       <c r="E251">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G251">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H251">
-        <v>1.058</v>
+        <v>1.057</v>
       </c>
       <c r="I251">
-        <v>2.487</v>
+        <v>3.477</v>
       </c>
     </row>
     <row r="252" spans="1:9">
@@ -7194,7 +7194,7 @@
         <v>1.083</v>
       </c>
       <c r="I252">
-        <v>3.619</v>
+        <v>4.348</v>
       </c>
     </row>
     <row r="253" spans="1:9">
@@ -7211,19 +7211,19 @@
         <v>14</v>
       </c>
       <c r="E253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F253">
-        <v>7.4040992227928</v>
+        <v>1.3806</v>
       </c>
       <c r="G253">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H253">
-        <v>1.042</v>
+        <v>1.077</v>
       </c>
       <c r="I253">
-        <v>3.46</v>
+        <v>2.726</v>
       </c>
     </row>
     <row r="254" spans="1:9">
@@ -7240,16 +7240,16 @@
         <v>12</v>
       </c>
       <c r="E254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G254">
         <v>0.001</v>
       </c>
       <c r="H254">
-        <v>1.081</v>
+        <v>1.083</v>
       </c>
       <c r="I254">
-        <v>7.585</v>
+        <v>9.151</v>
       </c>
     </row>
     <row r="255" spans="1:9">
@@ -7272,10 +7272,10 @@
         <v>0.002</v>
       </c>
       <c r="H255">
-        <v>1.16</v>
+        <v>1.153</v>
       </c>
       <c r="I255">
-        <v>8.666</v>
+        <v>7.389</v>
       </c>
     </row>
     <row r="256" spans="1:9">
@@ -7292,19 +7292,19 @@
         <v>14</v>
       </c>
       <c r="E256">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F256">
-        <v>13.46653697458217</v>
+        <v>1.3678</v>
       </c>
       <c r="G256">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H256">
-        <v>1.067</v>
+        <v>1.095</v>
       </c>
       <c r="I256">
-        <v>3.42</v>
+        <v>2.545</v>
       </c>
     </row>
     <row r="257" spans="1:9">
@@ -7321,16 +7321,16 @@
         <v>12</v>
       </c>
       <c r="E257">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G257">
         <v>0.001</v>
       </c>
       <c r="H257">
-        <v>1.081</v>
+        <v>1.083</v>
       </c>
       <c r="I257">
-        <v>7.585</v>
+        <v>9.151</v>
       </c>
     </row>
     <row r="258" spans="1:9">
@@ -7353,10 +7353,10 @@
         <v>0.002</v>
       </c>
       <c r="H258">
-        <v>1.16</v>
+        <v>1.153</v>
       </c>
       <c r="I258">
-        <v>8.666</v>
+        <v>7.389</v>
       </c>
     </row>
     <row r="259" spans="1:9">
@@ -7373,19 +7373,19 @@
         <v>14</v>
       </c>
       <c r="E259">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F259">
-        <v>13.46653697458217</v>
+        <v>1.3678</v>
       </c>
       <c r="G259">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H259">
-        <v>1.067</v>
+        <v>1.095</v>
       </c>
       <c r="I259">
-        <v>3.42</v>
+        <v>2.545</v>
       </c>
     </row>
     <row r="260" spans="1:9">
@@ -7402,16 +7402,16 @@
         <v>12</v>
       </c>
       <c r="E260">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G260">
         <v>0.001</v>
       </c>
       <c r="H260">
-        <v>1.081</v>
+        <v>1.083</v>
       </c>
       <c r="I260">
-        <v>7.585</v>
+        <v>9.151</v>
       </c>
     </row>
     <row r="261" spans="1:9">
@@ -7434,10 +7434,10 @@
         <v>0.002</v>
       </c>
       <c r="H261">
-        <v>1.16</v>
+        <v>1.153</v>
       </c>
       <c r="I261">
-        <v>8.666</v>
+        <v>7.389</v>
       </c>
     </row>
     <row r="262" spans="1:9">
@@ -7454,19 +7454,19 @@
         <v>14</v>
       </c>
       <c r="E262">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F262">
-        <v>13.46653697458217</v>
+        <v>1.3678</v>
       </c>
       <c r="G262">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H262">
-        <v>1.067</v>
+        <v>1.095</v>
       </c>
       <c r="I262">
-        <v>3.42</v>
+        <v>2.545</v>
       </c>
     </row>
     <row r="263" spans="1:9">
@@ -7489,10 +7489,10 @@
         <v>0.001</v>
       </c>
       <c r="H263">
-        <v>1.099</v>
+        <v>1.088</v>
       </c>
       <c r="I263">
-        <v>7.683</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="264" spans="1:9">
@@ -7515,10 +7515,10 @@
         <v>0.002</v>
       </c>
       <c r="H264">
-        <v>1.144</v>
+        <v>1.153</v>
       </c>
       <c r="I264">
-        <v>7.061</v>
+        <v>7.189</v>
       </c>
     </row>
     <row r="265" spans="1:9">
@@ -7535,19 +7535,19 @@
         <v>14</v>
       </c>
       <c r="E265">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F265">
-        <v>11.47407353110164</v>
+        <v>1.3697</v>
       </c>
       <c r="G265">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H265">
-        <v>1.071</v>
+        <v>1.095</v>
       </c>
       <c r="I265">
-        <v>3.189</v>
+        <v>2.195</v>
       </c>
     </row>
     <row r="266" spans="1:9">
@@ -7570,10 +7570,10 @@
         <v>0.001</v>
       </c>
       <c r="H266">
-        <v>1.099</v>
+        <v>1.088</v>
       </c>
       <c r="I266">
-        <v>7.683</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="267" spans="1:9">
@@ -7596,10 +7596,10 @@
         <v>0.002</v>
       </c>
       <c r="H267">
-        <v>1.144</v>
+        <v>1.153</v>
       </c>
       <c r="I267">
-        <v>7.061</v>
+        <v>7.189</v>
       </c>
     </row>
     <row r="268" spans="1:9">
@@ -7616,19 +7616,19 @@
         <v>14</v>
       </c>
       <c r="E268">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F268">
-        <v>11.47407353110164</v>
+        <v>1.3697</v>
       </c>
       <c r="G268">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H268">
-        <v>1.071</v>
+        <v>1.095</v>
       </c>
       <c r="I268">
-        <v>3.189</v>
+        <v>2.195</v>
       </c>
     </row>
     <row r="269" spans="1:9">
@@ -7651,10 +7651,10 @@
         <v>0.001</v>
       </c>
       <c r="H269">
-        <v>1.099</v>
+        <v>1.088</v>
       </c>
       <c r="I269">
-        <v>7.683</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="270" spans="1:9">
@@ -7677,10 +7677,10 @@
         <v>0.002</v>
       </c>
       <c r="H270">
-        <v>1.144</v>
+        <v>1.153</v>
       </c>
       <c r="I270">
-        <v>7.061</v>
+        <v>7.189</v>
       </c>
     </row>
     <row r="271" spans="1:9">
@@ -7697,19 +7697,19 @@
         <v>14</v>
       </c>
       <c r="E271">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F271">
-        <v>11.47407353110164</v>
+        <v>1.3697</v>
       </c>
       <c r="G271">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H271">
-        <v>1.071</v>
+        <v>1.095</v>
       </c>
       <c r="I271">
-        <v>3.189</v>
+        <v>2.195</v>
       </c>
     </row>
   </sheetData>

--- a/output/resultado_resumen_final.xlsx
+++ b/output/resultado_resumen_final.xlsx
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -439,13 +439,13 @@
         <v>2</v>
       </c>
       <c r="G2">
-        <v>0.08699999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="H2">
-        <v>3.802</v>
+        <v>2.689</v>
       </c>
       <c r="I2">
-        <v>2.572</v>
+        <v>3.318</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -465,13 +465,13 @@
         <v>2</v>
       </c>
       <c r="G3">
-        <v>0.081</v>
+        <v>0.043</v>
       </c>
       <c r="H3">
-        <v>3.571</v>
+        <v>2.52</v>
       </c>
       <c r="I3">
-        <v>2.688</v>
+        <v>3.389</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -479,7 +479,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -488,19 +488,19 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>1.1693</v>
+        <v>1.2573</v>
       </c>
       <c r="G4">
-        <v>0.185</v>
+        <v>0.066</v>
       </c>
       <c r="H4">
-        <v>2.589</v>
+        <v>1.89</v>
       </c>
       <c r="I4">
-        <v>1.236</v>
+        <v>2.122</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -508,7 +508,7 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -520,13 +520,13 @@
         <v>2</v>
       </c>
       <c r="G5">
-        <v>0.079</v>
+        <v>0.045</v>
       </c>
       <c r="H5">
-        <v>3.509</v>
+        <v>2.576</v>
       </c>
       <c r="I5">
-        <v>2.707</v>
+        <v>3.392</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -534,7 +534,7 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -546,13 +546,13 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>0.082</v>
+        <v>0.053</v>
       </c>
       <c r="H6">
-        <v>3.601</v>
+        <v>2.545</v>
       </c>
       <c r="I6">
-        <v>2.604</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="B7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
@@ -569,19 +569,19 @@
         <v>14</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2.219</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1.839</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -601,13 +601,13 @@
         <v>2</v>
       </c>
       <c r="G8">
-        <v>0.077</v>
+        <v>0.06</v>
       </c>
       <c r="H8">
-        <v>3.464</v>
+        <v>2.907</v>
       </c>
       <c r="I8">
-        <v>2.733</v>
+        <v>2.942</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -615,7 +615,7 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -627,13 +627,13 @@
         <v>2</v>
       </c>
       <c r="G9">
-        <v>0.082</v>
+        <v>0.058</v>
       </c>
       <c r="H9">
-        <v>3.63</v>
+        <v>2.838</v>
       </c>
       <c r="I9">
-        <v>2.594</v>
+        <v>2.865</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -641,7 +641,7 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -653,16 +653,16 @@
         <v>2</v>
       </c>
       <c r="F10">
-        <v>1.1362</v>
+        <v>1.2223</v>
       </c>
       <c r="G10">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
       <c r="H10">
-        <v>1.84</v>
+        <v>2.344</v>
       </c>
       <c r="I10">
-        <v>1.468</v>
+        <v>1.681</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -670,7 +670,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
@@ -682,13 +682,13 @@
         <v>2</v>
       </c>
       <c r="G11">
-        <v>0.081</v>
+        <v>0.04</v>
       </c>
       <c r="H11">
-        <v>3.69</v>
+        <v>2.834</v>
       </c>
       <c r="I11">
-        <v>2.635</v>
+        <v>3.737</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
@@ -705,16 +705,16 @@
         <v>13</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>0.077</v>
+        <v>0.045</v>
       </c>
       <c r="H12">
-        <v>3.3</v>
+        <v>2.686</v>
       </c>
       <c r="I12">
-        <v>2.312</v>
+        <v>3.752</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
       <c r="B13">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
@@ -731,19 +731,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>1.1878</v>
+        <v>1.3778</v>
       </c>
       <c r="G13">
-        <v>0.142</v>
+        <v>0.039</v>
       </c>
       <c r="H13">
-        <v>3.458</v>
+        <v>1.782</v>
       </c>
       <c r="I13">
-        <v>1.782</v>
+        <v>2.426</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -751,7 +751,7 @@
         <v>2</v>
       </c>
       <c r="B14">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>10</v>
@@ -763,13 +763,13 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>0.056</v>
+        <v>0.043</v>
       </c>
       <c r="H14">
-        <v>2.815</v>
+        <v>2.937</v>
       </c>
       <c r="I14">
-        <v>3.049</v>
+        <v>3.676</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -777,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
@@ -789,13 +789,13 @@
         <v>2</v>
       </c>
       <c r="G15">
-        <v>0.065</v>
+        <v>0.041</v>
       </c>
       <c r="H15">
-        <v>3.062</v>
+        <v>2.618</v>
       </c>
       <c r="I15">
-        <v>2.958</v>
+        <v>3.787</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -803,7 +803,7 @@
         <v>2</v>
       </c>
       <c r="B16">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -812,19 +812,19 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>1.1239</v>
+        <v>1.2927</v>
       </c>
       <c r="G16">
-        <v>0.136</v>
+        <v>0.046</v>
       </c>
       <c r="H16">
-        <v>2.813</v>
+        <v>1.69</v>
       </c>
       <c r="I16">
-        <v>1.767</v>
+        <v>2.097</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -832,7 +832,7 @@
         <v>2</v>
       </c>
       <c r="B17">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -844,13 +844,13 @@
         <v>2</v>
       </c>
       <c r="G17">
-        <v>0.07099999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="H17">
-        <v>3.141</v>
+        <v>2.899</v>
       </c>
       <c r="I17">
-        <v>2.547</v>
+        <v>3.694</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -858,7 +858,7 @@
         <v>2</v>
       </c>
       <c r="B18">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -870,13 +870,13 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>0.08400000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H18">
-        <v>3.177</v>
+        <v>3.087</v>
       </c>
       <c r="I18">
-        <v>2.584</v>
+        <v>3.485</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -884,7 +884,7 @@
         <v>2</v>
       </c>
       <c r="B19">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -893,19 +893,19 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19">
-        <v>1.1227</v>
+        <v>1.2873</v>
       </c>
       <c r="G19">
-        <v>0.212</v>
+        <v>0.056</v>
       </c>
       <c r="H19">
-        <v>3.4</v>
+        <v>2.151</v>
       </c>
       <c r="I19">
-        <v>1.263</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -913,7 +913,7 @@
         <v>3</v>
       </c>
       <c r="B20">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
@@ -925,13 +925,13 @@
         <v>2</v>
       </c>
       <c r="G20">
-        <v>0.032</v>
+        <v>0.058</v>
       </c>
       <c r="H20">
-        <v>3.786</v>
+        <v>3.043</v>
       </c>
       <c r="I20">
-        <v>4.383</v>
+        <v>3.076</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -939,7 +939,7 @@
         <v>3</v>
       </c>
       <c r="B21">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
@@ -948,16 +948,16 @@
         <v>13</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>0.036</v>
+        <v>0.049</v>
       </c>
       <c r="H21">
-        <v>3.568</v>
+        <v>2.661</v>
       </c>
       <c r="I21">
-        <v>4.534</v>
+        <v>2.743</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -965,7 +965,7 @@
         <v>3</v>
       </c>
       <c r="B22">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -974,19 +974,19 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1.2398</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2.397</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1.682</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -994,7 +994,7 @@
         <v>3</v>
       </c>
       <c r="B23">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -1006,13 +1006,13 @@
         <v>2</v>
       </c>
       <c r="G23">
-        <v>0.03</v>
+        <v>0.074</v>
       </c>
       <c r="H23">
-        <v>3.562</v>
+        <v>3.248</v>
       </c>
       <c r="I23">
-        <v>4.188</v>
+        <v>2.859</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1020,7 +1020,7 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
@@ -1032,13 +1032,13 @@
         <v>2</v>
       </c>
       <c r="G24">
-        <v>0.018</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H24">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="I24">
-        <v>3.882</v>
+        <v>2.681</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1046,7 +1046,7 @@
         <v>3</v>
       </c>
       <c r="B25">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
         <v>10</v>
@@ -1055,19 +1055,19 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1.1394</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2.087</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1.863</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1075,7 +1075,7 @@
         <v>3</v>
       </c>
       <c r="B26">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1087,13 +1087,13 @@
         <v>2</v>
       </c>
       <c r="G26">
-        <v>0.027</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H26">
-        <v>3.342</v>
+        <v>3.157</v>
       </c>
       <c r="I26">
-        <v>4.508</v>
+        <v>2.999</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1101,7 +1101,7 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1113,13 +1113,13 @@
         <v>2</v>
       </c>
       <c r="G27">
-        <v>0.024</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H27">
-        <v>3.222</v>
+        <v>2.963</v>
       </c>
       <c r="I27">
-        <v>4.276</v>
+        <v>2.816</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1127,7 +1127,7 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1136,19 +1136,19 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1.152</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2.576</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1.621</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1156,7 +1156,7 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
@@ -1165,16 +1165,16 @@
         <v>12</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H29">
-        <v>2.887</v>
+        <v>3.196</v>
       </c>
       <c r="I29">
-        <v>1.967</v>
+        <v>2.607</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1182,7 +1182,7 @@
         <v>4</v>
       </c>
       <c r="B30">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
@@ -1191,16 +1191,16 @@
         <v>13</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>0.08500000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="H30">
-        <v>2.678</v>
+        <v>3.297</v>
       </c>
       <c r="I30">
-        <v>2.477</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1208,7 +1208,7 @@
         <v>4</v>
       </c>
       <c r="B31">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
@@ -1220,16 +1220,16 @@
         <v>2</v>
       </c>
       <c r="F31">
-        <v>1.049</v>
+        <v>1.0813</v>
       </c>
       <c r="G31">
-        <v>0.179</v>
+        <v>0.172</v>
       </c>
       <c r="H31">
-        <v>2.85</v>
+        <v>2.519</v>
       </c>
       <c r="I31">
-        <v>1.363</v>
+        <v>1.358</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1237,7 +1237,7 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
@@ -1249,13 +1249,13 @@
         <v>2</v>
       </c>
       <c r="G32">
-        <v>0.101</v>
+        <v>0.082</v>
       </c>
       <c r="H32">
-        <v>3.213</v>
+        <v>3.162</v>
       </c>
       <c r="I32">
-        <v>2.29</v>
+        <v>2.581</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1263,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="B33">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
         <v>10</v>
@@ -1272,16 +1272,16 @@
         <v>13</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>0.099</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H33">
-        <v>2.893</v>
+        <v>3.04</v>
       </c>
       <c r="I33">
-        <v>1.914</v>
+        <v>2.739</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1289,7 +1289,7 @@
         <v>4</v>
       </c>
       <c r="B34">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
         <v>10</v>
@@ -1298,19 +1298,19 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>1.0453</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1.112</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1318,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="B35">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -1330,13 +1330,13 @@
         <v>2</v>
       </c>
       <c r="G35">
-        <v>0.08400000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="H35">
-        <v>2.815</v>
+        <v>2.742</v>
       </c>
       <c r="I35">
-        <v>2.41</v>
+        <v>2.887</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1344,7 +1344,7 @@
         <v>4</v>
       </c>
       <c r="B36">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
         <v>11</v>
@@ -1353,16 +1353,16 @@
         <v>13</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>0.093</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H36">
-        <v>2.753</v>
+        <v>2.63</v>
       </c>
       <c r="I36">
-        <v>2.034</v>
+        <v>2.002</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1370,7 +1370,7 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
         <v>11</v>
@@ -1379,19 +1379,19 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>1.0494</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>3.111</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1.228</v>
       </c>
     </row>
   </sheetData>

--- a/output/resultado_resumen_final.xlsx
+++ b/output/resultado_resumen_final.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="17">
   <si>
     <t>Instancia</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>Davies</t>
+  </si>
+  <si>
+    <t>Ruido_DBSCAN</t>
+  </si>
+  <si>
+    <t>%_Ruido_DBSCAN</t>
   </si>
   <si>
     <t>tiempo</t>
@@ -390,10 +396,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -421,977 +427,2621 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="G2">
-        <v>0.049</v>
+        <v>0.035</v>
       </c>
       <c r="H2">
-        <v>2.689</v>
+        <v>4.741</v>
       </c>
       <c r="I2">
-        <v>3.318</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>4.714</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="H3">
-        <v>2.52</v>
+        <v>3.599</v>
       </c>
       <c r="I3">
-        <v>3.389</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1.2573</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.066</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>2.122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>108</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>2</v>
       </c>
       <c r="G5">
-        <v>0.045</v>
+        <v>0.026</v>
       </c>
       <c r="H5">
-        <v>2.576</v>
+        <v>3.929</v>
       </c>
       <c r="I5">
-        <v>3.392</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>5.183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
       <c r="G6">
-        <v>0.053</v>
+        <v>0.015</v>
       </c>
       <c r="H6">
-        <v>2.545</v>
+        <v>3.111</v>
       </c>
       <c r="I6">
-        <v>3.157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>5.647</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>2.219</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>1.839</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>108</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="G8">
-        <v>0.06</v>
+        <v>0.027</v>
       </c>
       <c r="H8">
-        <v>2.907</v>
+        <v>4.125</v>
       </c>
       <c r="I8">
-        <v>2.942</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>5.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>2</v>
       </c>
       <c r="G9">
-        <v>0.058</v>
+        <v>0.015</v>
       </c>
       <c r="H9">
-        <v>2.838</v>
+        <v>3.137</v>
       </c>
       <c r="I9">
-        <v>2.865</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>5.382</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>108</v>
+      </c>
+      <c r="K10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>37</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>1.2223</v>
-      </c>
-      <c r="G10">
-        <v>0.111</v>
-      </c>
-      <c r="H10">
-        <v>2.344</v>
-      </c>
-      <c r="I10">
-        <v>1.681</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>42</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="G11">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="H11">
-        <v>2.834</v>
+        <v>3.062</v>
       </c>
       <c r="I11">
-        <v>3.737</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>3.333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>2</v>
       </c>
       <c r="B12">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>0.048</v>
+      </c>
+      <c r="H12">
+        <v>2.888</v>
+      </c>
+      <c r="I12">
+        <v>3.463</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1.3006</v>
+      </c>
+      <c r="G13">
+        <v>0.02</v>
+      </c>
+      <c r="H13">
+        <v>1.462</v>
+      </c>
+      <c r="I13">
+        <v>2.214</v>
+      </c>
+      <c r="J13">
+        <v>19</v>
+      </c>
+      <c r="K13">
+        <v>51.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>0.058</v>
+      </c>
+      <c r="H14">
+        <v>3.302</v>
+      </c>
+      <c r="I14">
+        <v>3.217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>0.055</v>
+      </c>
+      <c r="H15">
+        <v>3.258</v>
+      </c>
+      <c r="I15">
+        <v>3.229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>1.2653</v>
+      </c>
+      <c r="G16">
+        <v>0.048</v>
+      </c>
+      <c r="H16">
+        <v>1.502</v>
+      </c>
+      <c r="I16">
+        <v>2.051</v>
+      </c>
+      <c r="J16">
+        <v>26</v>
+      </c>
+      <c r="K16">
+        <v>70.27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>0.045</v>
-      </c>
-      <c r="H12">
-        <v>2.686</v>
-      </c>
-      <c r="I12">
-        <v>3.752</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="E13">
-        <v>3</v>
-      </c>
-      <c r="F13">
-        <v>1.3778</v>
-      </c>
-      <c r="G13">
-        <v>0.039</v>
-      </c>
-      <c r="H13">
-        <v>1.782</v>
-      </c>
-      <c r="I13">
-        <v>2.426</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="B14">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <v>2</v>
-      </c>
-      <c r="G14">
-        <v>0.043</v>
-      </c>
-      <c r="H14">
-        <v>2.937</v>
-      </c>
-      <c r="I14">
-        <v>3.676</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="G17">
+        <v>0.052</v>
+      </c>
+      <c r="H17">
+        <v>3.154</v>
+      </c>
+      <c r="I17">
+        <v>3.308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
         <v>13</v>
       </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="G15">
-        <v>0.041</v>
-      </c>
-      <c r="H15">
-        <v>2.618</v>
-      </c>
-      <c r="I15">
-        <v>3.787</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>42</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>1.2927</v>
-      </c>
-      <c r="G16">
-        <v>0.046</v>
-      </c>
-      <c r="H16">
-        <v>1.69</v>
-      </c>
-      <c r="I16">
-        <v>2.097</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17">
-        <v>42</v>
-      </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>0.044</v>
-      </c>
-      <c r="H17">
-        <v>2.899</v>
-      </c>
-      <c r="I17">
-        <v>3.694</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18">
-        <v>42</v>
-      </c>
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
       <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="G18">
+        <v>0.047</v>
+      </c>
+      <c r="H18">
+        <v>3.04</v>
+      </c>
+      <c r="I18">
+        <v>3.298</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
         <v>13</v>
       </c>
-      <c r="E18">
-        <v>2</v>
-      </c>
-      <c r="G18">
-        <v>0.05</v>
-      </c>
-      <c r="H18">
-        <v>3.087</v>
-      </c>
-      <c r="I18">
-        <v>3.485</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="B19">
-        <v>42</v>
-      </c>
-      <c r="C19" t="s">
-        <v>11</v>
-      </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="F19">
-        <v>1.2873</v>
+        <v>1.2761</v>
       </c>
       <c r="G19">
-        <v>0.056</v>
+        <v>0.095</v>
       </c>
       <c r="H19">
-        <v>2.151</v>
+        <v>2.342</v>
       </c>
       <c r="I19">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>1.759</v>
+      </c>
+      <c r="J19">
+        <v>25</v>
+      </c>
+      <c r="K19">
+        <v>67.56999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>3</v>
       </c>
       <c r="B20">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="G20">
-        <v>0.058</v>
+        <v>0.03</v>
       </c>
       <c r="H20">
-        <v>3.043</v>
+        <v>4.064</v>
       </c>
       <c r="I20">
-        <v>3.076</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>5.056</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>3</v>
       </c>
       <c r="B21">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>0.049</v>
+        <v>0.027</v>
       </c>
       <c r="H21">
-        <v>2.661</v>
+        <v>3.17</v>
       </c>
       <c r="I21">
-        <v>2.743</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>3</v>
       </c>
       <c r="B22">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>1.2398</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>0.126</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>2.397</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>1.682</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>107</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>3</v>
       </c>
       <c r="B23">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="G23">
-        <v>0.074</v>
+        <v>0.026</v>
       </c>
       <c r="H23">
-        <v>3.248</v>
+        <v>4.03</v>
       </c>
       <c r="I23">
-        <v>2.859</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>4.366</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>3</v>
       </c>
       <c r="B24">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24">
         <v>2</v>
       </c>
       <c r="G24">
-        <v>0.06900000000000001</v>
+        <v>0.018</v>
       </c>
       <c r="H24">
-        <v>2.71</v>
+        <v>3.358</v>
       </c>
       <c r="I24">
-        <v>2.681</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>5.446</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>3</v>
       </c>
       <c r="B25">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>1.1394</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>2.087</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>1.863</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>107</v>
+      </c>
+      <c r="K25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>3</v>
       </c>
       <c r="B26">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="G26">
-        <v>0.06900000000000001</v>
+        <v>0.026</v>
       </c>
       <c r="H26">
-        <v>3.157</v>
+        <v>4.172</v>
       </c>
       <c r="I26">
-        <v>2.999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>4.914</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>3</v>
       </c>
       <c r="B27">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="G27">
-        <v>0.06900000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="H27">
-        <v>2.963</v>
+        <v>3.425</v>
       </c>
       <c r="I27">
-        <v>2.816</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>5.276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>3</v>
       </c>
       <c r="B28">
-        <v>31</v>
+        <v>107</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>1.152</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>2.576</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>1.621</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>107</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>4</v>
       </c>
       <c r="B29">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E29">
         <v>2</v>
       </c>
       <c r="G29">
-        <v>0.08</v>
+        <v>0.033</v>
       </c>
       <c r="H29">
-        <v>3.196</v>
+        <v>3.236</v>
       </c>
       <c r="I29">
-        <v>2.607</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>4</v>
       </c>
       <c r="B30">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G30">
-        <v>0.096</v>
+        <v>0.021</v>
       </c>
       <c r="H30">
-        <v>3.297</v>
+        <v>2.775</v>
       </c>
       <c r="I30">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>4.559</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>4</v>
       </c>
       <c r="B31">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E31">
         <v>2</v>
       </c>
       <c r="F31">
-        <v>1.0813</v>
+        <v>1.6047</v>
       </c>
       <c r="G31">
-        <v>0.172</v>
+        <v>0.046</v>
       </c>
       <c r="H31">
-        <v>2.519</v>
+        <v>1.978</v>
       </c>
       <c r="I31">
-        <v>1.358</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>2.378</v>
+      </c>
+      <c r="J31">
+        <v>35</v>
+      </c>
+      <c r="K31">
+        <v>53.03</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>4</v>
       </c>
       <c r="B32">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="G32">
-        <v>0.082</v>
+        <v>0.032</v>
       </c>
       <c r="H32">
-        <v>3.162</v>
+        <v>3.318</v>
       </c>
       <c r="I32">
-        <v>2.581</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>4.345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>4</v>
       </c>
       <c r="B33">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="G33">
-        <v>0.07099999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="H33">
-        <v>3.04</v>
+        <v>2.882</v>
       </c>
       <c r="I33">
-        <v>2.739</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>4.679</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>4</v>
       </c>
       <c r="B34">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34">
-        <v>1.0453</v>
+        <v>1.4825</v>
       </c>
       <c r="G34">
-        <v>0.237</v>
+        <v>0.044</v>
       </c>
       <c r="H34">
-        <v>3.21</v>
+        <v>1.907</v>
       </c>
       <c r="I34">
-        <v>1.112</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>2.399</v>
+      </c>
+      <c r="J34">
+        <v>37</v>
+      </c>
+      <c r="K34">
+        <v>56.06</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>4</v>
       </c>
       <c r="B35">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="G35">
-        <v>0.064</v>
+        <v>0.033</v>
       </c>
       <c r="H35">
-        <v>2.742</v>
+        <v>3.396</v>
       </c>
       <c r="I35">
-        <v>2.887</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>4.272</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>4</v>
       </c>
       <c r="B36">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="G36">
-        <v>0.08500000000000001</v>
+        <v>0.022</v>
       </c>
       <c r="H36">
-        <v>2.63</v>
+        <v>2.876</v>
       </c>
       <c r="I36">
-        <v>2.002</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>4.266</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>4</v>
       </c>
       <c r="B37">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="F37">
+        <v>1.4753</v>
+      </c>
+      <c r="G37">
+        <v>0.048</v>
+      </c>
+      <c r="H37">
+        <v>2.073</v>
+      </c>
+      <c r="I37">
+        <v>2.577</v>
+      </c>
+      <c r="J37">
+        <v>37</v>
+      </c>
+      <c r="K37">
+        <v>56.06</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>5</v>
+      </c>
+      <c r="B38">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
         <v>11</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>14</v>
       </c>
-      <c r="E37">
-        <v>2</v>
-      </c>
-      <c r="F37">
-        <v>1.0494</v>
-      </c>
-      <c r="G37">
-        <v>0.217</v>
-      </c>
-      <c r="H37">
-        <v>3.111</v>
-      </c>
-      <c r="I37">
-        <v>1.228</v>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="G38">
+        <v>0.082</v>
+      </c>
+      <c r="H38">
+        <v>3.628</v>
+      </c>
+      <c r="I38">
+        <v>2.647</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39">
+        <v>5</v>
+      </c>
+      <c r="B39">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="G39">
+        <v>0.066</v>
+      </c>
+      <c r="H39">
+        <v>2.89</v>
+      </c>
+      <c r="I39">
+        <v>2.901</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40">
+        <v>5</v>
+      </c>
+      <c r="B40">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40">
+        <v>1.1434</v>
+      </c>
+      <c r="G40">
+        <v>0.139</v>
+      </c>
+      <c r="H40">
+        <v>2.716</v>
+      </c>
+      <c r="I40">
+        <v>1.652</v>
+      </c>
+      <c r="J40">
+        <v>18</v>
+      </c>
+      <c r="K40">
+        <v>64.29000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41">
+        <v>5</v>
+      </c>
+      <c r="B41">
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="G41">
+        <v>0.057</v>
+      </c>
+      <c r="H41">
+        <v>2.744</v>
+      </c>
+      <c r="I41">
+        <v>3.069</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42">
+        <v>5</v>
+      </c>
+      <c r="B42">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>0.056</v>
+      </c>
+      <c r="H42">
+        <v>2.483</v>
+      </c>
+      <c r="I42">
+        <v>2.725</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43">
+        <v>5</v>
+      </c>
+      <c r="B43">
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>28</v>
+      </c>
+      <c r="K43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44">
+        <v>5</v>
+      </c>
+      <c r="B44">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="G44">
+        <v>0.062</v>
+      </c>
+      <c r="H44">
+        <v>2.899</v>
+      </c>
+      <c r="I44">
+        <v>2.955</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45">
+        <v>5</v>
+      </c>
+      <c r="B45">
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="G45">
+        <v>0.052</v>
+      </c>
+      <c r="H45">
+        <v>2.494</v>
+      </c>
+      <c r="I45">
+        <v>2.842</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46">
+        <v>5</v>
+      </c>
+      <c r="B46">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>1.1624</v>
+      </c>
+      <c r="G46">
+        <v>0.101</v>
+      </c>
+      <c r="H46">
+        <v>2.059</v>
+      </c>
+      <c r="I46">
+        <v>1.688</v>
+      </c>
+      <c r="J46">
+        <v>18</v>
+      </c>
+      <c r="K46">
+        <v>64.29000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47">
+        <v>6</v>
+      </c>
+      <c r="B47">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47">
+        <v>4</v>
+      </c>
+      <c r="G47">
+        <v>0.155</v>
+      </c>
+      <c r="H47">
+        <v>2.664</v>
+      </c>
+      <c r="I47">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48">
+        <v>6</v>
+      </c>
+      <c r="B48">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48">
+        <v>2</v>
+      </c>
+      <c r="G48">
+        <v>0.122</v>
+      </c>
+      <c r="H48">
+        <v>2.74</v>
+      </c>
+      <c r="I48">
+        <v>1.898</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49">
+        <v>6</v>
+      </c>
+      <c r="B49">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>12</v>
+      </c>
+      <c r="K49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50">
+        <v>6</v>
+      </c>
+      <c r="B50">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50">
+        <v>2</v>
+      </c>
+      <c r="G50">
+        <v>0.172</v>
+      </c>
+      <c r="H50">
+        <v>3.708</v>
+      </c>
+      <c r="I50">
+        <v>1.597</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51">
+        <v>6</v>
+      </c>
+      <c r="B51">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="G51">
+        <v>0.155</v>
+      </c>
+      <c r="H51">
+        <v>2.829</v>
+      </c>
+      <c r="I51">
+        <v>1.361</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52">
+        <v>6</v>
+      </c>
+      <c r="B52">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>12</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53">
+        <v>6</v>
+      </c>
+      <c r="B53">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53">
+        <v>2</v>
+      </c>
+      <c r="G53">
+        <v>0.174</v>
+      </c>
+      <c r="H53">
+        <v>3.729</v>
+      </c>
+      <c r="I53">
+        <v>1.593</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54">
+        <v>6</v>
+      </c>
+      <c r="B54">
+        <v>12</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>0.157</v>
+      </c>
+      <c r="H54">
+        <v>3.432</v>
+      </c>
+      <c r="I54">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55">
+        <v>6</v>
+      </c>
+      <c r="B55">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>12</v>
+      </c>
+      <c r="K55">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>7</v>
+      </c>
+      <c r="B56">
+        <v>41</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>0.057</v>
+      </c>
+      <c r="H56">
+        <v>2.869</v>
+      </c>
+      <c r="I56">
+        <v>3.434</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57">
+        <v>41</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
+      </c>
+      <c r="G57">
+        <v>0.048</v>
+      </c>
+      <c r="H57">
+        <v>2.942</v>
+      </c>
+      <c r="I57">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>7</v>
+      </c>
+      <c r="B58">
+        <v>41</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58">
+        <v>2</v>
+      </c>
+      <c r="F58">
+        <v>1.337</v>
+      </c>
+      <c r="G58">
+        <v>0.078</v>
+      </c>
+      <c r="H58">
+        <v>2.046</v>
+      </c>
+      <c r="I58">
+        <v>1.842</v>
+      </c>
+      <c r="J58">
+        <v>26</v>
+      </c>
+      <c r="K58">
+        <v>63.41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>7</v>
+      </c>
+      <c r="B59">
+        <v>41</v>
+      </c>
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>0.051</v>
+      </c>
+      <c r="H59">
+        <v>3.255</v>
+      </c>
+      <c r="I59">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>7</v>
+      </c>
+      <c r="B60">
+        <v>41</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="G60">
+        <v>0.054</v>
+      </c>
+      <c r="H60">
+        <v>3.179</v>
+      </c>
+      <c r="I60">
+        <v>2.885</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>7</v>
+      </c>
+      <c r="B61">
+        <v>41</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61">
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <v>1.2257</v>
+      </c>
+      <c r="G61">
+        <v>0.175</v>
+      </c>
+      <c r="H61">
+        <v>2.864</v>
+      </c>
+      <c r="I61">
+        <v>1.443</v>
+      </c>
+      <c r="J61">
+        <v>33</v>
+      </c>
+      <c r="K61">
+        <v>80.48999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>7</v>
+      </c>
+      <c r="B62">
+        <v>41</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
+      </c>
+      <c r="G62">
+        <v>0.052</v>
+      </c>
+      <c r="H62">
+        <v>3.294</v>
+      </c>
+      <c r="I62">
+        <v>3.405</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>7</v>
+      </c>
+      <c r="B63">
+        <v>41</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="G63">
+        <v>0.044</v>
+      </c>
+      <c r="H63">
+        <v>2.892</v>
+      </c>
+      <c r="I63">
+        <v>3.365</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>7</v>
+      </c>
+      <c r="B64">
+        <v>41</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>16</v>
+      </c>
+      <c r="E64">
+        <v>3</v>
+      </c>
+      <c r="F64">
+        <v>1.2176</v>
+      </c>
+      <c r="G64">
+        <v>0.179</v>
+      </c>
+      <c r="H64">
+        <v>2.804</v>
+      </c>
+      <c r="I64">
+        <v>1.273</v>
+      </c>
+      <c r="J64">
+        <v>32</v>
+      </c>
+      <c r="K64">
+        <v>78.05</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>8</v>
+      </c>
+      <c r="B65">
+        <v>37</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="G65">
+        <v>0.061</v>
+      </c>
+      <c r="H65">
+        <v>3.497</v>
+      </c>
+      <c r="I65">
+        <v>3.122</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>8</v>
+      </c>
+      <c r="B66">
+        <v>37</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="G66">
+        <v>0.049</v>
+      </c>
+      <c r="H66">
+        <v>2.951</v>
+      </c>
+      <c r="I66">
+        <v>3.424</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>8</v>
+      </c>
+      <c r="B67">
+        <v>37</v>
+      </c>
+      <c r="C67" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" t="s">
+        <v>16</v>
+      </c>
+      <c r="E67">
+        <v>3</v>
+      </c>
+      <c r="F67">
+        <v>1.2984</v>
+      </c>
+      <c r="G67">
+        <v>0.041</v>
+      </c>
+      <c r="H67">
+        <v>1.879</v>
+      </c>
+      <c r="I67">
+        <v>1.945</v>
+      </c>
+      <c r="J67">
+        <v>18</v>
+      </c>
+      <c r="K67">
+        <v>48.65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>8</v>
+      </c>
+      <c r="B68">
+        <v>37</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>0.057</v>
+      </c>
+      <c r="H68">
+        <v>3.317</v>
+      </c>
+      <c r="I68">
+        <v>3.168</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>8</v>
+      </c>
+      <c r="B69">
+        <v>37</v>
+      </c>
+      <c r="C69" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="G69">
+        <v>0.048</v>
+      </c>
+      <c r="H69">
+        <v>3.179</v>
+      </c>
+      <c r="I69">
+        <v>3.163</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>8</v>
+      </c>
+      <c r="B70">
+        <v>37</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>16</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
+      </c>
+      <c r="F70">
+        <v>1.2069</v>
+      </c>
+      <c r="G70">
+        <v>0.093</v>
+      </c>
+      <c r="H70">
+        <v>2.367</v>
+      </c>
+      <c r="I70">
+        <v>1.932</v>
+      </c>
+      <c r="J70">
+        <v>23</v>
+      </c>
+      <c r="K70">
+        <v>62.16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>8</v>
+      </c>
+      <c r="B71">
+        <v>37</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
+      </c>
+      <c r="G71">
+        <v>0.058</v>
+      </c>
+      <c r="H71">
+        <v>3.435</v>
+      </c>
+      <c r="I71">
+        <v>3.136</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>8</v>
+      </c>
+      <c r="B72">
+        <v>37</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>0.057</v>
+      </c>
+      <c r="H72">
+        <v>3.171</v>
+      </c>
+      <c r="I72">
+        <v>3.308</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>8</v>
+      </c>
+      <c r="B73">
+        <v>37</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s">
+        <v>16</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73">
+        <v>1.1639</v>
+      </c>
+      <c r="G73">
+        <v>0.221</v>
+      </c>
+      <c r="H73">
+        <v>3.865</v>
+      </c>
+      <c r="I73">
+        <v>1.326</v>
+      </c>
+      <c r="J73">
+        <v>28</v>
+      </c>
+      <c r="K73">
+        <v>75.68000000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>9</v>
+      </c>
+      <c r="B74">
+        <v>91</v>
+      </c>
+      <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" t="s">
+        <v>14</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="G74">
+        <v>0.034</v>
+      </c>
+      <c r="H74">
+        <v>4.218</v>
+      </c>
+      <c r="I74">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>9</v>
+      </c>
+      <c r="B75">
+        <v>91</v>
+      </c>
+      <c r="C75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>0.039</v>
+      </c>
+      <c r="H75">
+        <v>3.806</v>
+      </c>
+      <c r="I75">
+        <v>4.515</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>9</v>
+      </c>
+      <c r="B76">
+        <v>91</v>
+      </c>
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>91</v>
+      </c>
+      <c r="K76">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>9</v>
+      </c>
+      <c r="B77">
+        <v>91</v>
+      </c>
+      <c r="C77" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>0.027</v>
+      </c>
+      <c r="H77">
+        <v>3.503</v>
+      </c>
+      <c r="I77">
+        <v>5.029</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78">
+        <v>9</v>
+      </c>
+      <c r="B78">
+        <v>91</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78">
+        <v>2</v>
+      </c>
+      <c r="G78">
+        <v>0.023</v>
+      </c>
+      <c r="H78">
+        <v>2.94</v>
+      </c>
+      <c r="I78">
+        <v>5.485</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79">
+        <v>9</v>
+      </c>
+      <c r="B79">
+        <v>91</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>91</v>
+      </c>
+      <c r="K79">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>9</v>
+      </c>
+      <c r="B80">
+        <v>91</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80">
+        <v>2</v>
+      </c>
+      <c r="G80">
+        <v>0.031</v>
+      </c>
+      <c r="H80">
+        <v>3.38</v>
+      </c>
+      <c r="I80">
+        <v>4.906</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81">
+        <v>9</v>
+      </c>
+      <c r="B81">
+        <v>91</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>15</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
+      </c>
+      <c r="G81">
+        <v>0.023</v>
+      </c>
+      <c r="H81">
+        <v>3.177</v>
+      </c>
+      <c r="I81">
+        <v>5.277</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>9</v>
+      </c>
+      <c r="B82">
+        <v>91</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>91</v>
+      </c>
+      <c r="K82">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>10</v>
+      </c>
+      <c r="B83">
+        <v>111</v>
+      </c>
+      <c r="C83" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>0.037</v>
+      </c>
+      <c r="H83">
+        <v>5.117</v>
+      </c>
+      <c r="I83">
+        <v>4.599</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>10</v>
+      </c>
+      <c r="B84">
+        <v>111</v>
+      </c>
+      <c r="C84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" t="s">
+        <v>15</v>
+      </c>
+      <c r="E84">
+        <v>2</v>
+      </c>
+      <c r="G84">
+        <v>0.039</v>
+      </c>
+      <c r="H84">
+        <v>4.299</v>
+      </c>
+      <c r="I84">
+        <v>4.736</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85">
+        <v>10</v>
+      </c>
+      <c r="B85">
+        <v>111</v>
+      </c>
+      <c r="C85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" t="s">
+        <v>16</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>111</v>
+      </c>
+      <c r="K85">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86">
+        <v>10</v>
+      </c>
+      <c r="B86">
+        <v>111</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>0.03</v>
+      </c>
+      <c r="H86">
+        <v>4.411</v>
+      </c>
+      <c r="I86">
+        <v>4.953</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87">
+        <v>10</v>
+      </c>
+      <c r="B87">
+        <v>111</v>
+      </c>
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87">
+        <v>2</v>
+      </c>
+      <c r="G87">
+        <v>0.024</v>
+      </c>
+      <c r="H87">
+        <v>3.96</v>
+      </c>
+      <c r="I87">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88">
+        <v>10</v>
+      </c>
+      <c r="B88">
+        <v>111</v>
+      </c>
+      <c r="C88" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" t="s">
+        <v>16</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>111</v>
+      </c>
+      <c r="K88">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89">
+        <v>10</v>
+      </c>
+      <c r="B89">
+        <v>111</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="G89">
+        <v>0.03</v>
+      </c>
+      <c r="H89">
+        <v>4.432</v>
+      </c>
+      <c r="I89">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90">
+        <v>10</v>
+      </c>
+      <c r="B90">
+        <v>111</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>15</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+      <c r="G90">
+        <v>0.025</v>
+      </c>
+      <c r="H90">
+        <v>3.511</v>
+      </c>
+      <c r="I90">
+        <v>5.474</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91">
+        <v>10</v>
+      </c>
+      <c r="B91">
+        <v>111</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>111</v>
+      </c>
+      <c r="K91">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
